--- a/Financial Analysis/DUOL.xlsx
+++ b/Financial Analysis/DUOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C37B03BF-D09A-449D-B3EA-B76B13FFFDC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3DC4FF-FA95-4FE0-9864-E1D3E6973C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9EA5A098-45C5-472E-8765-EE9A7145AF0E}"/>
   </bookViews>
@@ -290,7 +290,7 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Heavily overvalued</t>
   </si>
 </sst>
 </file>
@@ -827,14 +827,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>486.42</v>
+        <v>528.66999999999996</v>
       </c>
       <c r="E3" s="3">
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="3">
         <v>45875</v>
@@ -858,7 +858,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>22132.11</v>
+        <v>24054.484999999997</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -899,7 +899,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>21049.510000000002</v>
+        <v>22971.884999999998</v>
       </c>
     </row>
   </sheetData>
@@ -915,7 +915,8 @@
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="8.88671875" customWidth="1"/>
-    <col min="43" max="44" width="12" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="16.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:139" x14ac:dyDescent="0.3">
@@ -3348,47 +3349,47 @@
         <v>44.9</v>
       </c>
       <c r="AD16" s="5">
-        <f>39.3+6.2</f>
+        <f t="shared" ref="AD16:AN16" si="82">39.3+6.2</f>
         <v>45.5</v>
       </c>
       <c r="AE16" s="5">
-        <f>39.3+6.2</f>
+        <f t="shared" si="82"/>
         <v>45.5</v>
       </c>
       <c r="AF16" s="5">
-        <f>39.3+6.2</f>
+        <f t="shared" si="82"/>
         <v>45.5</v>
       </c>
       <c r="AG16" s="5">
-        <f>39.3+6.2</f>
+        <f t="shared" si="82"/>
         <v>45.5</v>
       </c>
       <c r="AH16" s="5">
-        <f>39.3+6.2</f>
+        <f t="shared" si="82"/>
         <v>45.5</v>
       </c>
       <c r="AI16" s="5">
-        <f>39.3+6.2</f>
+        <f t="shared" si="82"/>
         <v>45.5</v>
       </c>
       <c r="AJ16" s="5">
-        <f>39.3+6.2</f>
+        <f t="shared" si="82"/>
         <v>45.5</v>
       </c>
       <c r="AK16" s="5">
-        <f>39.3+6.2</f>
+        <f t="shared" si="82"/>
         <v>45.5</v>
       </c>
       <c r="AL16" s="5">
-        <f>39.3+6.2</f>
+        <f t="shared" si="82"/>
         <v>45.5</v>
       </c>
       <c r="AM16" s="5">
-        <f>39.3+6.2</f>
+        <f t="shared" si="82"/>
         <v>45.5</v>
       </c>
       <c r="AN16" s="5">
-        <f>39.3+6.2</f>
+        <f t="shared" si="82"/>
         <v>45.5</v>
       </c>
     </row>
@@ -3397,151 +3398,151 @@
         <v>23</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:R17" si="82">C15/C16</f>
+        <f t="shared" ref="C17:R17" si="83">C15/C16</f>
         <v>-0.29844097995545654</v>
       </c>
       <c r="D17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-2.2271714922050267E-3</v>
       </c>
       <c r="E17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-0.64587973273942101</v>
       </c>
       <c r="F17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-0.38975501113585764</v>
       </c>
       <c r="G17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-0.27171492204899761</v>
       </c>
       <c r="H17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-0.33630289532293978</v>
       </c>
       <c r="I17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-0.40979955456570177</v>
       </c>
       <c r="J17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-0.30957683741648112</v>
       </c>
       <c r="K17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>-5.5679287305122331E-2</v>
       </c>
       <c r="L17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>8.2405345211581355E-2</v>
       </c>
       <c r="M17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>6.236080178173712E-2</v>
       </c>
       <c r="N17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.27171492204899772</v>
       </c>
       <c r="O17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.60133630289532269</v>
       </c>
       <c r="P17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.5412026726057908</v>
       </c>
       <c r="Q17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.51893095768374098</v>
       </c>
       <c r="R17" s="7">
-        <f t="shared" si="82"/>
+        <f t="shared" si="83"/>
         <v>0.3140311804008909</v>
       </c>
       <c r="S17" s="7">
-        <f t="shared" ref="S17" si="83">S15/S16</f>
+        <f t="shared" ref="S17" si="84">S15/S16</f>
         <v>0.76923076923076861</v>
       </c>
       <c r="T17" s="7">
-        <f t="shared" ref="T17" si="84">T15/T16</f>
+        <f t="shared" ref="T17" si="85">T15/T16</f>
         <v>0.65250109890109864</v>
       </c>
       <c r="U17" s="7">
-        <f t="shared" ref="U17" si="85">U15/U16</f>
+        <f t="shared" ref="U17" si="86">U15/U16</f>
         <v>0.64385912087912134</v>
       </c>
       <c r="V17" s="7">
-        <f t="shared" ref="V17" si="86">V15/V16</f>
+        <f t="shared" ref="V17" si="87">V15/V16</f>
         <v>0.68205120879120873</v>
       </c>
       <c r="X17" s="7">
-        <f t="shared" ref="X17:AE17" si="87">X15/X16</f>
+        <f t="shared" ref="X17:AE17" si="88">X15/X16</f>
         <v>-0.2739420935412028</v>
       </c>
       <c r="Y17" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>-0.35189309576837413</v>
       </c>
       <c r="Z17" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>-1.3363028953229408</v>
       </c>
       <c r="AA17" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>-1.3273942093541193</v>
       </c>
       <c r="AB17" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>0.36080178173719457</v>
       </c>
       <c r="AC17" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>1.9755011135857456</v>
       </c>
       <c r="AD17" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>2.747642197802199</v>
       </c>
       <c r="AE17" s="7">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>4.0649874587912098</v>
       </c>
       <c r="AF17" s="7">
-        <f t="shared" ref="AF17" si="88">AF15/AF16</f>
+        <f t="shared" ref="AF17" si="89">AF15/AF16</f>
         <v>5.9394509208791204</v>
       </c>
       <c r="AG17" s="7">
-        <f t="shared" ref="AG17" si="89">AG15/AG16</f>
+        <f t="shared" ref="AG17" si="90">AG15/AG16</f>
         <v>7.7852356306813144</v>
       </c>
       <c r="AH17" s="7">
-        <f t="shared" ref="AH17" si="90">AH15/AH16</f>
+        <f t="shared" ref="AH17" si="91">AH15/AH16</f>
         <v>9.2904352811475786</v>
       </c>
       <c r="AI17" s="7">
-        <f t="shared" ref="AI17" si="91">AI15/AI16</f>
+        <f t="shared" ref="AI17" si="92">AI15/AI16</f>
         <v>10.674365370478984</v>
       </c>
       <c r="AJ17" s="7">
-        <f t="shared" ref="AJ17" si="92">AJ15/AJ16</f>
+        <f t="shared" ref="AJ17" si="93">AJ15/AJ16</f>
         <v>11.856525301572237</v>
       </c>
       <c r="AK17" s="7">
-        <f t="shared" ref="AK17" si="93">AK15/AK16</f>
+        <f t="shared" ref="AK17" si="94">AK15/AK16</f>
         <v>12.926351293205428</v>
       </c>
       <c r="AL17" s="7">
-        <f t="shared" ref="AL17" si="94">AL15/AL16</f>
+        <f t="shared" ref="AL17" si="95">AL15/AL16</f>
         <v>14.057015570726829</v>
       </c>
       <c r="AM17" s="7">
-        <f t="shared" ref="AM17" si="95">AM15/AM16</f>
+        <f t="shared" ref="AM17" si="96">AM15/AM16</f>
         <v>15.25168505807474</v>
       </c>
       <c r="AN17" s="7">
-        <f t="shared" ref="AN17" si="96">AN15/AN16</f>
+        <f t="shared" ref="AN17" si="97">AN15/AN16</f>
         <v>16.51368730627642</v>
       </c>
     </row>
@@ -3554,47 +3555,47 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9">
-        <f t="shared" ref="G19:Q19" si="97">G3/C3-1</f>
+        <f t="shared" ref="G19:Q19" si="98">G3/C3-1</f>
         <v>0.46570397111913375</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.5034013605442178</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.51100628930817593</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.42191780821917813</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.42487684729064035</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.434389140271493</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.43184183142559829</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.4547206165703277</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.44857389801210013</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.40615141955835976</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="98"/>
         <v>0.39970930232558133</v>
       </c>
       <c r="R19" s="9">
@@ -3602,36 +3603,36 @@
         <v>0.38807947019867539</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19:V19" si="98">S3/O3-1</f>
+        <f t="shared" ref="S19:V19" si="99">S3/O3-1</f>
         <v>0.37649164677804303</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.35000000000000009</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.29000000000000004</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="99"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="X19" s="9"/>
       <c r="Y19" s="9">
-        <f t="shared" ref="Y19" si="99">Y3/X3-1</f>
+        <f t="shared" ref="Y19" si="100">Y3/X3-1</f>
         <v>1.2838983050847457</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" ref="Z19:AB19" si="100">Z3/Y3-1</f>
+        <f t="shared" ref="Z19:AB19" si="101">Z3/Y3-1</f>
         <v>0.55102040816326525</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.47328548644338153</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="101"/>
         <v>0.43734776725304458</v>
       </c>
       <c r="AC19" s="9">
@@ -3639,47 +3640,47 @@
         <v>0.40858595368103923</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" ref="AD19:AN19" si="101">AD3/AC3-1</f>
+        <f t="shared" ref="AD19:AN19" si="102">AD3/AC3-1</f>
         <v>0.32087555139687218</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.25</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.19999999999999996</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AJ19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AK19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="102"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -3688,63 +3689,63 @@
         <v>46</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:Q20" si="102">C5/C3</f>
+        <f t="shared" ref="C20:Q20" si="103">C5/C3</f>
         <v>0.72924187725631773</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.72619047619047616</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.71540880503144655</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.72602739726027399</v>
       </c>
       <c r="G20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.73522167487684731</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.72963800904977372</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.72632674297606659</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.73217726396917149</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.72774416594641311</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.7334384858044164</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.73619186046511631</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.73112582781456958</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.73031026252983289</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.73471676948962417</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="103"/>
         <v>0.72897196261682229</v>
       </c>
       <c r="R20" s="9">
@@ -3752,39 +3753,39 @@
         <v>0.71898854961832059</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" ref="S20:V20" si="103">S5/S3</f>
+        <f t="shared" ref="S20:V20" si="104">S5/S3</f>
         <v>0.71131339401820548</v>
       </c>
       <c r="T20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.71</v>
       </c>
       <c r="U20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.71</v>
       </c>
       <c r="V20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="104"/>
         <v>0.71</v>
       </c>
       <c r="X20" s="9">
-        <f t="shared" ref="X20:Y20" si="104">X5/X3</f>
+        <f t="shared" ref="X20:Y20" si="105">X5/X3</f>
         <v>0.7076271186440678</v>
       </c>
       <c r="Y20" s="9">
-        <f t="shared" si="104"/>
+        <f t="shared" si="105"/>
         <v>0.71552257266542973</v>
       </c>
       <c r="Z20" s="9">
-        <f t="shared" ref="Z20:AB20" si="105">Z5/Z3</f>
+        <f t="shared" ref="Z20:AB20" si="106">Z5/Z3</f>
         <v>0.72408293460925033</v>
       </c>
       <c r="AA20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.73071718538565633</v>
       </c>
       <c r="AB20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="106"/>
         <v>0.73225381284127289</v>
       </c>
       <c r="AC20" s="9">
@@ -3792,47 +3793,47 @@
         <v>0.72784387114022187</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20:AN20" si="106">AD5/AD3</f>
+        <f t="shared" ref="AD20:AN20" si="107">AD5/AD3</f>
         <v>0.71030663453919307</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.71</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.71</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.71</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.71</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.71</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.71</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.71</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.71</v>
       </c>
       <c r="AM20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.71</v>
       </c>
       <c r="AN20" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="107"/>
         <v>0.71</v>
       </c>
     </row>
@@ -3845,47 +3846,47 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9">
-        <f t="shared" ref="G21:Q21" si="107">G6/C6-1</f>
+        <f t="shared" ref="G21:Q21" si="108">G6/C6-1</f>
         <v>0.32444444444444454</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.5616438356164386</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.43344709897610922</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.48333333333333339</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.53691275167785224</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.40058479532163727</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.19761904761904758</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.13033707865168531</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.11135371179039311</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.1503131524008352</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="108"/>
         <v>0.25049701789264422</v>
       </c>
       <c r="R21" s="9">
@@ -3893,36 +3894,36 @@
         <v>0.32007952286282326</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21:V21" si="108">S6/O6-1</f>
+        <f t="shared" ref="S21:V21" si="109">S6/O6-1</f>
         <v>0.38310412573673891</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="109"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="X21" s="9"/>
       <c r="Y21" s="9">
-        <f t="shared" ref="Y21" si="109">Y6/X6-1</f>
+        <f t="shared" ref="Y21" si="110">Y6/X6-1</f>
         <v>0.67721518987341756</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" ref="Z21:AB21" si="110">Z6/Y6-1</f>
+        <f t="shared" ref="Z21:AB21" si="111">Z6/Y6-1</f>
         <v>0.95660377358490578</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.45130183220829312</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="111"/>
         <v>0.29102990033222609</v>
       </c>
       <c r="AC21" s="9">
@@ -3930,47 +3931,47 @@
         <v>0.211013896037056</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" ref="AD21:AN21" si="111">AD6/AC6-1</f>
+        <f t="shared" ref="AD21:AN21" si="112">AD6/AC6-1</f>
         <v>0.27668933276668084</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.17999999999999994</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="112"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AQ21" t="s">
@@ -3985,63 +3986,63 @@
         <v>48</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:Q22" si="112">C7/C3</f>
+        <f t="shared" ref="C22:Q22" si="113">C7/C3</f>
         <v>0.35740072202166068</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.16326530612244899</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.24056603773584906</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.19863013698630136</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.18349753694581281</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.17307692307692307</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.18418314255983351</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.18304431599229287</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.14347450302506484</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.13958990536277602</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.1620639534883721</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.12649006622516556</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.11873508353221957</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.11329220415030845</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="113"/>
         <v>0.13291796469366565</v>
       </c>
       <c r="R22" s="9">
@@ -4049,39 +4050,39 @@
         <v>0.1183206106870229</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22:V22" si="113">S7/S3</f>
+        <f t="shared" ref="S22:V22" si="114">S7/S3</f>
         <v>0.11573472041612484</v>
       </c>
       <c r="T22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.11</v>
       </c>
       <c r="U22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.11</v>
       </c>
       <c r="V22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="114"/>
         <v>0.11</v>
       </c>
       <c r="X22" s="9">
-        <f t="shared" ref="X22:Y22" si="114">X7/X3</f>
+        <f t="shared" ref="X22:Y22" si="115">X7/X3</f>
         <v>0.21186440677966104</v>
       </c>
       <c r="Y22" s="9">
-        <f t="shared" si="114"/>
+        <f t="shared" si="115"/>
         <v>0.21645021645021648</v>
       </c>
       <c r="Z22" s="9">
-        <f t="shared" ref="Z22:AB22" si="115">Z7/Z3</f>
+        <f t="shared" ref="Z22:AB22" si="116">Z7/Z3</f>
         <v>0.2360446570972887</v>
       </c>
       <c r="AA22" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.18105548037889038</v>
       </c>
       <c r="AB22" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="116"/>
         <v>0.14253436264356992</v>
       </c>
       <c r="AC22" s="9">
@@ -4089,47 +4090,47 @@
         <v>0.12097313193423337</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22:AN22" si="116">AD7/AD3</f>
+        <f t="shared" ref="AD22:AN22" si="117">AD7/AD3</f>
         <v>0.11133886962162512</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.1</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.09</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.09</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.09</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.09</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.09</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.09</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.09</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.09</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="117"/>
         <v>0.09</v>
       </c>
       <c r="AQ22" t="s">
@@ -4148,47 +4149,47 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9">
-        <f t="shared" ref="G23:Q23" si="117">G8/C8-1</f>
+        <f t="shared" ref="G23:Q23" si="118">G8/C8-1</f>
         <v>1.3391304347826085</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>1.5948275862068968</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>2.0270270270270174E-2</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.1853281853281854</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.12267657992565062</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>6.976744186046524E-2</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.10596026490066213</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.1791530944625408</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.16225165562913912</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.1490683229813663</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="118"/>
         <v>0.14970059880239517</v>
       </c>
       <c r="R23" s="9">
@@ -4196,36 +4197,36 @@
         <v>0.25690607734806625</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23:V23" si="118">S8/O8-1</f>
+        <f t="shared" ref="S23:V23" si="119">S8/O8-1</f>
         <v>0.23931623931623935</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.30000000000000004</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.25</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="119"/>
         <v>0.17999999999999994</v>
       </c>
       <c r="X23" s="9"/>
       <c r="Y23" s="9">
-        <f t="shared" ref="Y23" si="119">Y8/X8-1</f>
+        <f t="shared" ref="Y23" si="120">Y8/X8-1</f>
         <v>1.6646341463414638</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" ref="Z23:AB23" si="120">Z8/Y8-1</f>
+        <f t="shared" ref="Z23:AB23" si="121">Z8/Y8-1</f>
         <v>0.79862700228832928</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.50000000000000022</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="121"/>
         <v>0.11959287531806617</v>
       </c>
       <c r="AC23" s="9">
@@ -4233,47 +4234,47 @@
         <v>0.18181818181818188</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" ref="AD23:AN23" si="121">AD8/AC8-1</f>
+        <f t="shared" ref="AD23:AN23" si="122">AD8/AC8-1</f>
         <v>0.23903846153846153</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.16999999999999993</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>0.1100000000000001</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="122"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ23" t="s">
@@ -4289,63 +4290,63 @@
         <v>50</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:Q24" si="122">C10/C3</f>
+        <f t="shared" ref="C24:Q24" si="123">C10/C3</f>
         <v>-0.2418772563176895</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-6.802721088435471E-3</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-0.45125786163522014</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-0.23835616438356172</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-0.14655172413793091</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-0.17081447963800897</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-0.20915712799167543</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-0.17533718689788058</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-7.2601555747623087E-2</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-3.7854889589905343E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>-3.4156976744186066E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>3.1788079470198655E-2</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>9.8448687350835243E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>0.10487941671340438</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="123"/>
         <v>7.0093457943925089E-2</v>
       </c>
       <c r="R24" s="9">
@@ -4353,39 +4354,39 @@
         <v>6.6793893129770993E-2</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24:V24" si="123">S10/S3</f>
+        <f t="shared" ref="S24:V24" si="124">S10/S3</f>
         <v>0.10186389250108353</v>
       </c>
       <c r="T24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>0.10258615317504821</v>
       </c>
       <c r="U24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>9.5411625492042892E-2</v>
       </c>
       <c r="V24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="124"/>
         <v>9.7935054866412199E-2</v>
       </c>
       <c r="X24" s="9">
-        <f t="shared" ref="X24:Y24" si="124">X10/X3</f>
+        <f t="shared" ref="X24:Y24" si="125">X10/X3</f>
         <v>-0.18220338983050857</v>
       </c>
       <c r="Y24" s="9">
-        <f t="shared" si="124"/>
+        <f t="shared" si="125"/>
         <v>-9.894867037724181E-2</v>
       </c>
       <c r="Z24" s="9">
-        <f t="shared" ref="Z24:AB24" si="125">Z10/Z3</f>
+        <f t="shared" ref="Z24:AB24" si="126">Z10/Z3</f>
         <v>-0.2388357256778311</v>
       </c>
       <c r="AA24" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>-0.17672530446549375</v>
       </c>
       <c r="AB24" s="9">
-        <f t="shared" si="125"/>
+        <f t="shared" si="126"/>
         <v>-2.4665787987196319E-2</v>
       </c>
       <c r="AC24" s="9">
@@ -4393,47 +4394,47 @@
         <v>8.381232455554069E-2</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" ref="AD24:AN24" si="126">AD10/AD3</f>
+        <f t="shared" ref="AD24:AN24" si="127">AD10/AD3</f>
         <v>9.9350805092764602E-2</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.13992645831035264</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.18279044109833861</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.21553416413444196</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.23759593699983605</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.25529982880539914</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.26906209941651621</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.28039101498596242</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.29134664274257049</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.30194153774807297</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="127"/>
         <v>0.31218782435974735</v>
       </c>
       <c r="AQ24" t="s">
@@ -4449,63 +4450,63 @@
         <v>21</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:Q25" si="127">C14/C13</f>
+        <f t="shared" ref="C25:Q25" si="128">C14/C13</f>
         <v>0</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-3.4602076124567475E-3</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-5.7471264367816074E-3</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-6.6666666666666697E-3</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-5.4644808743169382E-3</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-5.3030303030303018E-2</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>3.8461538461538575E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-0.54166666666666596</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>3.4482758620689696E-2</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.19736842105263161</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>-4.2471042471042497E-2</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>0.15331010452961671</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="127"/>
+        <f t="shared" si="128"/>
         <v>7.9051383399209585E-2</v>
       </c>
       <c r="R25" s="9">
@@ -4513,39 +4514,39 @@
         <v>0.37333333333333335</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:V25" si="128">S14/S13</f>
+        <f t="shared" ref="S25:V25" si="129">S14/S13</f>
         <v>-2.8653295128939853E-3</v>
       </c>
       <c r="T25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.15</v>
       </c>
       <c r="U25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.15</v>
       </c>
       <c r="V25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="129"/>
         <v>0.15</v>
       </c>
       <c r="X25" s="9">
-        <f t="shared" ref="X25:Y25" si="129">X14/X13</f>
+        <f t="shared" ref="X25:Y25" si="130">X14/X13</f>
         <v>0</v>
       </c>
       <c r="Y25" s="9">
-        <f t="shared" si="129"/>
+        <f t="shared" si="130"/>
         <v>-6.369426751592357E-3</v>
       </c>
       <c r="Z25" s="9">
-        <f t="shared" ref="Z25:AB25" si="130">Z14/Z13</f>
+        <f t="shared" ref="Z25:AB25" si="131">Z14/Z13</f>
         <v>-3.3444816053511688E-3</v>
       </c>
       <c r="AA25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>-1.5332197614991491E-2</v>
       </c>
       <c r="AB25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="131"/>
         <v>9.4972067039105962E-2</v>
       </c>
       <c r="AC25" s="9">
@@ -4553,47 +4554,47 @@
         <v>0.13378906250000003</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" ref="AD25:AN25" si="131">AD14/AD13</f>
+        <f t="shared" ref="AD25:AN25" si="132">AD14/AD13</f>
         <v>0.11211023613099698</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="132"/>
         <v>0.15</v>
       </c>
       <c r="AQ25" t="s">
@@ -4609,63 +4610,63 @@
         <v>51</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:Q26" si="132">C15/C3</f>
+        <f t="shared" ref="C26:Q26" si="133">C15/C3</f>
         <v>-0.2418772563176895</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-1.7006802721089404E-3</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-0.45597484276729566</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-0.23972602739726037</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-0.15024630541871911</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-0.17081447963800897</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-0.19146722164412081</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-0.13391136801541428</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>-2.1607605877268732E-2</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>2.9179810725552074E-2</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>2.0348837209302303E-2</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>8.0794701986754952E-2</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.16109785202863955</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.13628715647784634</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="133"/>
         <v>0.12097611630321894</v>
       </c>
       <c r="R26" s="9">
@@ -4673,39 +4674,39 @@
         <v>6.7270992366412208E-2</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" ref="S26:V26" si="133">S15/S3</f>
+        <f t="shared" ref="S26:V26" si="134">S15/S3</f>
         <v>0.15171218032076278</v>
       </c>
       <c r="T26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.1233410190897571</v>
       </c>
       <c r="U26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.11791152486979488</v>
       </c>
       <c r="V26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.11567170354246183</v>
       </c>
       <c r="X26" s="9">
-        <f t="shared" ref="X26:Y26" si="134">X15/X3</f>
+        <f t="shared" ref="X26:Y26" si="135">X15/X3</f>
         <v>-0.17372881355932213</v>
       </c>
       <c r="Y26" s="9">
-        <f t="shared" si="134"/>
+        <f t="shared" si="135"/>
         <v>-9.7711811997526279E-2</v>
       </c>
       <c r="Z26" s="9">
-        <f t="shared" ref="Z26:AB26" si="135">Z15/Z3</f>
+        <f t="shared" ref="Z26:AB26" si="136">Z15/Z3</f>
         <v>-0.23923444976076572</v>
       </c>
       <c r="AA26" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>-0.16129905277401882</v>
       </c>
       <c r="AB26" s="9">
-        <f t="shared" si="135"/>
+        <f t="shared" si="136"/>
         <v>3.0502730182639867E-2</v>
       </c>
       <c r="AC26" s="9">
@@ -4713,47 +4714,47 @@
         <v>0.1185670364924475</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" ref="AD26:AN26" si="136">AD15/AD3</f>
+        <f t="shared" ref="AD26:AN26" si="137">AD15/AD3</f>
         <v>0.12651732991144035</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.14974041665865506</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.18232443614158619</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.20781289974766551</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.22544682212718731</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.23984262250421243</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.25132510188196738</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.26095468011599671</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.27026696370911357</v>
       </c>
       <c r="AM26" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.27927262446379064</v>
       </c>
       <c r="AN26" s="9">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>0.28798196808371385</v>
       </c>
       <c r="AQ26" t="s">
@@ -4770,7 +4771,7 @@
       </c>
       <c r="AR27" s="4">
         <f>Main!D3</f>
-        <v>486.42</v>
+        <v>528.66999999999996</v>
       </c>
     </row>
     <row r="28" spans="2:44" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4790,59 +4791,59 @@
         <v>-60.000000000000036</v>
       </c>
       <c r="AA28" s="8">
-        <f t="shared" ref="AA28:AN28" si="137">AA15</f>
+        <f t="shared" ref="AA28:AN28" si="138">AA15</f>
         <v>-59.599999999999959</v>
       </c>
       <c r="AB28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>16.200000000000035</v>
       </c>
       <c r="AC28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>88.699999999999974</v>
       </c>
       <c r="AD28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>125.01772000000005</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>184.95692937500004</v>
       </c>
       <c r="AF28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>270.2450169</v>
       </c>
       <c r="AG28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>354.22822119599982</v>
       </c>
       <c r="AH28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>422.71480529221486</v>
       </c>
       <c r="AI28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>485.68362435679376</v>
       </c>
       <c r="AJ28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>539.47190122153677</v>
       </c>
       <c r="AK28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>588.148983840847</v>
       </c>
       <c r="AL28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>639.59420846807075</v>
       </c>
       <c r="AM28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>693.95167014240064</v>
       </c>
       <c r="AN28" s="8">
-        <f t="shared" si="137"/>
+        <f t="shared" si="138"/>
         <v>751.37277243557719</v>
       </c>
       <c r="AQ28" s="1" t="s">
@@ -4850,7 +4851,7 @@
       </c>
       <c r="AR28" s="10">
         <f>AR26/AR27-1</f>
-        <v>-0.65814945001941016</v>
+        <v>-0.68546930122466088</v>
       </c>
     </row>
     <row r="29" spans="2:44" x14ac:dyDescent="0.3">
@@ -4878,43 +4879,43 @@
         <v>11.445</v>
       </c>
       <c r="AE29" s="5">
-        <f t="shared" ref="AE29:AN29" si="138">AD29*1.05</f>
+        <f t="shared" ref="AE29:AN29" si="139">AD29*1.05</f>
         <v>12.017250000000001</v>
       </c>
       <c r="AF29" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>12.618112500000001</v>
       </c>
       <c r="AG29" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>13.249018125000001</v>
       </c>
       <c r="AH29" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>13.911469031250002</v>
       </c>
       <c r="AI29" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>14.607042482812503</v>
       </c>
       <c r="AJ29" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>15.337394606953129</v>
       </c>
       <c r="AK29" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>16.104264337300787</v>
       </c>
       <c r="AL29" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>16.909477554165829</v>
       </c>
       <c r="AM29" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>17.754951431874122</v>
       </c>
       <c r="AN29" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="139"/>
         <v>18.642699003467829</v>
       </c>
       <c r="AQ29" t="s">
@@ -4949,19 +4950,19 @@
         <v>121.55000000000001</v>
       </c>
       <c r="AE30" s="5">
-        <f t="shared" ref="AE30:AH30" si="139">AD30*1.1</f>
+        <f t="shared" ref="AE30:AH30" si="140">AD30*1.1</f>
         <v>133.70500000000001</v>
       </c>
       <c r="AF30" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>147.07550000000003</v>
       </c>
       <c r="AG30" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>161.78305000000006</v>
       </c>
       <c r="AH30" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>177.96135500000008</v>
       </c>
       <c r="AI30" s="5">
@@ -4969,23 +4970,23 @@
         <v>181.5205821000001</v>
       </c>
       <c r="AJ30" s="5">
-        <f t="shared" ref="AJ30:AN30" si="140">AI30*1.02</f>
+        <f t="shared" ref="AJ30:AN30" si="141">AI30*1.02</f>
         <v>185.15099374200011</v>
       </c>
       <c r="AK30" s="5">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>188.85401361684012</v>
       </c>
       <c r="AL30" s="5">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>192.63109388917692</v>
       </c>
       <c r="AM30" s="5">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>196.48371576696047</v>
       </c>
       <c r="AN30" s="5">
-        <f t="shared" si="140"/>
+        <f t="shared" si="141"/>
         <v>200.41339008229968</v>
       </c>
     </row>
@@ -5427,67 +5428,67 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="Y39" s="8">
-        <f t="shared" ref="Y39:AD39" si="141">Y28+SUM(Y29:Y38)</f>
+        <f t="shared" ref="Y39:AD39" si="142">Y28+SUM(Y29:Y38)</f>
         <v>17.700000000000003</v>
       </c>
       <c r="Z39" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>9.3999999999999702</v>
       </c>
       <c r="AA39" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>53.600000000000044</v>
       </c>
       <c r="AB39" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>153.60000000000005</v>
       </c>
       <c r="AC39" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>285.7</v>
       </c>
       <c r="AD39" s="8">
-        <f t="shared" si="141"/>
+        <f t="shared" si="142"/>
         <v>258.01272000000006</v>
       </c>
       <c r="AE39" s="8">
-        <f t="shared" ref="AE39:AN39" si="142">AE28+SUM(AE29:AE38)</f>
+        <f t="shared" ref="AE39:AN39" si="143">AE28+SUM(AE29:AE38)</f>
         <v>330.67917937500005</v>
       </c>
       <c r="AF39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>429.93862940000002</v>
       </c>
       <c r="AG39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>529.26028932099985</v>
       </c>
       <c r="AH39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>614.58762932346497</v>
       </c>
       <c r="AI39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>681.81124893960634</v>
       </c>
       <c r="AJ39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>739.96028957048998</v>
       </c>
       <c r="AK39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>793.10726179498783</v>
       </c>
       <c r="AL39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>849.13477991141349</v>
       </c>
       <c r="AM39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>908.19033734123525</v>
       </c>
       <c r="AN39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>970.42886152134474</v>
       </c>
     </row>
@@ -5516,43 +5517,43 @@
         <v>9.9</v>
       </c>
       <c r="AE40" s="5">
-        <f t="shared" ref="AE40:AN40" si="143">AD40*1.1</f>
+        <f t="shared" ref="AE40:AN40" si="144">AD40*1.1</f>
         <v>10.89</v>
       </c>
       <c r="AF40" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>11.979000000000001</v>
       </c>
       <c r="AG40" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>13.176900000000002</v>
       </c>
       <c r="AH40" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>14.494590000000002</v>
       </c>
       <c r="AI40" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>15.944049000000003</v>
       </c>
       <c r="AJ40" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>17.538453900000004</v>
       </c>
       <c r="AK40" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>19.292299290000006</v>
       </c>
       <c r="AL40" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>21.221529219000008</v>
       </c>
       <c r="AM40" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>23.343682140900011</v>
       </c>
       <c r="AN40" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>25.678050354990013</v>
       </c>
     </row>
@@ -5581,43 +5582,43 @@
         <v>13.31</v>
       </c>
       <c r="AE41" s="5">
-        <f t="shared" ref="AE41:AN41" si="144">AD41*1.1</f>
+        <f t="shared" ref="AE41:AN41" si="145">AD41*1.1</f>
         <v>14.641000000000002</v>
       </c>
       <c r="AF41" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>16.105100000000004</v>
       </c>
       <c r="AG41" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>17.715610000000005</v>
       </c>
       <c r="AH41" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>19.487171000000007</v>
       </c>
       <c r="AI41" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>21.43588810000001</v>
       </c>
       <c r="AJ41" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>23.579476910000015</v>
       </c>
       <c r="AK41" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>25.937424601000018</v>
       </c>
       <c r="AL41" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>28.531167061100021</v>
       </c>
       <c r="AM41" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>31.384283767210025</v>
       </c>
       <c r="AN41" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>34.522712143931031</v>
       </c>
     </row>
@@ -5630,67 +5631,67 @@
         <v>5.3000000000000007</v>
       </c>
       <c r="Y42" s="5">
-        <f t="shared" ref="Y42:AD42" si="145">SUM(Y40:Y41)</f>
+        <f t="shared" ref="Y42:AD42" si="146">SUM(Y40:Y41)</f>
         <v>4</v>
       </c>
       <c r="Z42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>6.2</v>
       </c>
       <c r="AA42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>10.199999999999999</v>
       </c>
       <c r="AB42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>13.7</v>
       </c>
       <c r="AC42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>21.1</v>
       </c>
       <c r="AD42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>23.21</v>
       </c>
       <c r="AE42" s="5">
-        <f t="shared" ref="AE42:AN42" si="146">SUM(AE40:AE41)</f>
+        <f t="shared" ref="AE42:AN42" si="147">SUM(AE40:AE41)</f>
         <v>25.531000000000002</v>
       </c>
       <c r="AF42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>28.084100000000007</v>
       </c>
       <c r="AG42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>30.892510000000009</v>
       </c>
       <c r="AH42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>33.981761000000006</v>
       </c>
       <c r="AI42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>37.379937100000014</v>
       </c>
       <c r="AJ42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>41.117930810000018</v>
       </c>
       <c r="AK42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>45.22972389100002</v>
       </c>
       <c r="AL42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>49.752696280100025</v>
       </c>
       <c r="AM42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>54.727965908110036</v>
       </c>
       <c r="AN42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>60.200762498921044</v>
       </c>
     </row>
@@ -5702,67 +5703,67 @@
         <v>-3.1</v>
       </c>
       <c r="Y43" s="8">
-        <f t="shared" ref="Y43:AD43" si="147">Y39-Y42</f>
+        <f t="shared" ref="Y43:AD43" si="148">Y39-Y42</f>
         <v>13.700000000000003</v>
       </c>
       <c r="Z43" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>3.19999999999997</v>
       </c>
       <c r="AA43" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>43.400000000000048</v>
       </c>
       <c r="AB43" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>139.90000000000006</v>
       </c>
       <c r="AC43" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>264.59999999999997</v>
       </c>
       <c r="AD43" s="8">
-        <f t="shared" si="147"/>
+        <f t="shared" si="148"/>
         <v>234.80272000000005</v>
       </c>
       <c r="AE43" s="8">
-        <f t="shared" ref="AE43:AN43" si="148">AE39-AE42</f>
+        <f t="shared" ref="AE43:AN43" si="149">AE39-AE42</f>
         <v>305.14817937500004</v>
       </c>
       <c r="AF43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>401.85452940000005</v>
       </c>
       <c r="AG43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>498.36777932099983</v>
       </c>
       <c r="AH43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>580.60586832346496</v>
       </c>
       <c r="AI43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>644.43131183960634</v>
       </c>
       <c r="AJ43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>698.84235876049001</v>
       </c>
       <c r="AK43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>747.87753790398779</v>
       </c>
       <c r="AL43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>799.38208363131344</v>
       </c>
       <c r="AM43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>853.46237143312521</v>
       </c>
       <c r="AN43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>910.22809902242375</v>
       </c>
       <c r="AO43" s="1">
@@ -5770,383 +5771,383 @@
         <v>901.1258180321995</v>
       </c>
       <c r="AP43" s="1">
-        <f t="shared" ref="AP43:DA43" si="149">AO43*(1+$AR$21)</f>
+        <f t="shared" ref="AP43:DA43" si="150">AO43*(1+$AR$21)</f>
         <v>892.11455985187752</v>
       </c>
       <c r="AQ43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>883.1934142533587</v>
       </c>
       <c r="AR43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>874.36148011082514</v>
       </c>
       <c r="AS43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>865.61786530971688</v>
       </c>
       <c r="AT43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>856.96168665661969</v>
       </c>
       <c r="AU43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>848.39206979005348</v>
       </c>
       <c r="AV43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>839.90814909215294</v>
       </c>
       <c r="AW43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>831.50906760123144</v>
       </c>
       <c r="AX43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>823.19397692521909</v>
       </c>
       <c r="AY43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>814.96203715596687</v>
       </c>
       <c r="AZ43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>806.81241678440722</v>
       </c>
       <c r="BA43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>798.74429261656314</v>
       </c>
       <c r="BB43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>790.75684969039753</v>
       </c>
       <c r="BC43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>782.84928119349354</v>
       </c>
       <c r="BD43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>775.02078838155865</v>
       </c>
       <c r="BE43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>767.27058049774303</v>
       </c>
       <c r="BF43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>759.59787469276557</v>
       </c>
       <c r="BG43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>752.00189594583787</v>
       </c>
       <c r="BH43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>744.48187698637946</v>
       </c>
       <c r="BI43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>737.03705821651567</v>
       </c>
       <c r="BJ43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>729.66668763435052</v>
       </c>
       <c r="BK43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>722.37002075800706</v>
       </c>
       <c r="BL43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>715.14632055042694</v>
       </c>
       <c r="BM43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>707.99485734492271</v>
       </c>
       <c r="BN43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>700.91490877147351</v>
       </c>
       <c r="BO43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>693.90575968375879</v>
       </c>
       <c r="BP43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>686.96670208692115</v>
       </c>
       <c r="BQ43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>680.09703506605194</v>
       </c>
       <c r="BR43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>673.29606471539137</v>
       </c>
       <c r="BS43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>666.56310406823741</v>
       </c>
       <c r="BT43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>659.89747302755507</v>
       </c>
       <c r="BU43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>653.29849829727948</v>
       </c>
       <c r="BV43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>646.76551331430665</v>
       </c>
       <c r="BW43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>640.29785818116352</v>
       </c>
       <c r="BX43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>633.89487959935184</v>
       </c>
       <c r="BY43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>627.55593080335836</v>
       </c>
       <c r="BZ43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>621.28037149532474</v>
       </c>
       <c r="CA43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>615.06756778037152</v>
       </c>
       <c r="CB43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>608.91689210256777</v>
       </c>
       <c r="CC43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>602.82772318154207</v>
       </c>
       <c r="CD43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>596.79944594972665</v>
       </c>
       <c r="CE43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>590.83145149022937</v>
       </c>
       <c r="CF43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>584.92313697532711</v>
       </c>
       <c r="CG43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>579.07390560557383</v>
       </c>
       <c r="CH43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>573.28316654951811</v>
       </c>
       <c r="CI43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>567.55033488402296</v>
       </c>
       <c r="CJ43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>561.87483153518269</v>
       </c>
       <c r="CK43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>556.25608321983088</v>
       </c>
       <c r="CL43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>550.69352238763258</v>
       </c>
       <c r="CM43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>545.18658716375626</v>
       </c>
       <c r="CN43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>539.73472129211871</v>
       </c>
       <c r="CO43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>534.3373740791975</v>
       </c>
       <c r="CP43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>528.9940003384055</v>
       </c>
       <c r="CQ43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>523.7040603350215</v>
       </c>
       <c r="CR43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>518.46701973167126</v>
       </c>
       <c r="CS43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>513.28234953435458</v>
       </c>
       <c r="CT43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>508.14952603901105</v>
       </c>
       <c r="CU43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>503.06803077862094</v>
       </c>
       <c r="CV43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>498.03735047083472</v>
       </c>
       <c r="CW43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>493.0569769661264</v>
       </c>
       <c r="CX43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>488.12640719646515</v>
       </c>
       <c r="CY43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>483.24514312450049</v>
       </c>
       <c r="CZ43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>478.41269169325545</v>
       </c>
       <c r="DA43" s="1">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>473.62856477632289</v>
       </c>
       <c r="DB43" s="1">
-        <f t="shared" ref="DB43:EF43" si="150">DA43*(1+$AR$21)</f>
+        <f t="shared" ref="DB43:EF43" si="151">DA43*(1+$AR$21)</f>
         <v>468.89227912855966</v>
       </c>
       <c r="DC43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>464.20335633727404</v>
       </c>
       <c r="DD43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>459.56132277390128</v>
       </c>
       <c r="DE43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>454.96570954616226</v>
       </c>
       <c r="DF43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>450.41605245070065</v>
       </c>
       <c r="DG43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>445.91189192619362</v>
       </c>
       <c r="DH43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>441.45277300693169</v>
       </c>
       <c r="DI43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>437.03824527686237</v>
       </c>
       <c r="DJ43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>432.66786282409373</v>
       </c>
       <c r="DK43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>428.3411841958528</v>
       </c>
       <c r="DL43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>424.05777235389428</v>
       </c>
       <c r="DM43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>419.81719463035535</v>
       </c>
       <c r="DN43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>415.6190226840518</v>
       </c>
       <c r="DO43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>411.46283245721128</v>
       </c>
       <c r="DP43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>407.34820413263918</v>
       </c>
       <c r="DQ43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>403.27472209131281</v>
       </c>
       <c r="DR43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>399.2419748703997</v>
       </c>
       <c r="DS43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>395.24955512169572</v>
       </c>
       <c r="DT43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>391.29705957047878</v>
       </c>
       <c r="DU43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>387.38408897477399</v>
       </c>
       <c r="DV43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>383.51024808502626</v>
       </c>
       <c r="DW43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>379.67514560417601</v>
       </c>
       <c r="DX43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>375.87839414813425</v>
       </c>
       <c r="DY43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>372.11961020665291</v>
       </c>
       <c r="DZ43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>368.39841410458638</v>
       </c>
       <c r="EA43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>364.71442996354051</v>
       </c>
       <c r="EB43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>361.06728566390512</v>
       </c>
       <c r="EC43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>357.45661280726608</v>
       </c>
       <c r="ED43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>353.88204667919342</v>
       </c>
       <c r="EE43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>350.34322621240148</v>
       </c>
       <c r="EF43" s="1">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>346.83979395027745</v>
       </c>
     </row>
@@ -6177,13 +6178,13 @@
     <row r="50" spans="44:44" x14ac:dyDescent="0.3">
       <c r="AR50" s="4">
         <f>Main!D3</f>
-        <v>486.42</v>
+        <v>528.66999999999996</v>
       </c>
     </row>
     <row r="51" spans="44:44" x14ac:dyDescent="0.3">
       <c r="AR51" s="10">
         <f>AR49/AR50-1</f>
-        <v>-0.57804334872964636</v>
+        <v>-0.61176508159924825</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/DUOL.xlsx
+++ b/Financial Analysis/DUOL.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3DC4FF-FA95-4FE0-9864-E1D3E6973C10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D951848-C802-4B5F-BD0D-5BF8FE77F8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9EA5A098-45C5-472E-8765-EE9A7145AF0E}"/>
   </bookViews>
@@ -290,7 +290,7 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Heavily overvalued</t>
+    <t>Overvalued</t>
   </si>
 </sst>
 </file>
@@ -403,14 +403,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
@@ -427,7 +427,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12473940" y="7620"/>
+          <a:off x="13091160" y="7620"/>
           <a:ext cx="0" cy="8145780"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -827,17 +827,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>528.66999999999996</v>
+        <v>278.74</v>
       </c>
       <c r="E3" s="3">
-        <v>45804</v>
+        <v>45909</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45909</v>
       </c>
       <c r="G3" s="3">
-        <v>45875</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -845,11 +845,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <f>39.3+6.2</f>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -858,7 +857,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>24054.484999999997</v>
+        <v>12766.291999999999</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -866,11 +865,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>884+115.3+83.3</f>
-        <v>1082.5999999999999</v>
+        <f>976.2+121.7</f>
+        <v>1097.9000000000001</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -881,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -890,7 +889,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>1082.5999999999999</v>
+        <v>1097.9000000000001</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -899,7 +898,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>22971.884999999998</v>
+        <v>11668.392</v>
       </c>
     </row>
   </sheetData>
@@ -1088,16 +1087,15 @@
         <v>230.7</v>
       </c>
       <c r="T3" s="8">
-        <f>P3*1.35</f>
-        <v>240.70500000000004</v>
+        <v>252.3</v>
       </c>
       <c r="U3" s="8">
-        <f>Q3*1.29</f>
-        <v>248.45400000000001</v>
+        <f>Q3*1.4</f>
+        <v>269.64</v>
       </c>
       <c r="V3" s="8">
-        <f>R3*1.28</f>
-        <v>268.28800000000001</v>
+        <f>R3*1.35</f>
+        <v>282.96000000000004</v>
       </c>
       <c r="X3" s="8">
         <v>70.8</v>
@@ -1123,47 +1121,47 @@
       </c>
       <c r="AD3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>988.14700000000005</v>
+        <v>1035.5999999999999</v>
       </c>
       <c r="AE3" s="8">
-        <f>AD3*1.25</f>
-        <v>1235.1837500000001</v>
+        <f>AD3*1.28</f>
+        <v>1325.568</v>
       </c>
       <c r="AF3" s="8">
-        <f>AE3*1.2</f>
-        <v>1482.2205000000001</v>
+        <f>AE3*1.22</f>
+        <v>1617.1929599999999</v>
       </c>
       <c r="AG3" s="8">
         <f>AF3*1.15</f>
-        <v>1704.5535749999999</v>
+        <v>1859.7719039999997</v>
       </c>
       <c r="AH3" s="8">
         <f>AG3*1.1</f>
-        <v>1875.0089325000001</v>
+        <v>2045.7490943999999</v>
       </c>
       <c r="AI3" s="8">
         <f>AH3*1.08</f>
-        <v>2025.0096471000002</v>
+        <v>2209.4090219519999</v>
       </c>
       <c r="AJ3" s="8">
         <f>AI3*1.06</f>
-        <v>2146.5102259260002</v>
+        <v>2341.9735632691199</v>
       </c>
       <c r="AK3" s="8">
         <f>AJ3*1.05</f>
-        <v>2253.8357372223004</v>
+        <v>2459.072241432576</v>
       </c>
       <c r="AL3" s="8">
         <f t="shared" ref="AL3:AN3" si="0">AK3*1.05</f>
-        <v>2366.5275240834153</v>
+        <v>2582.0258535042049</v>
       </c>
       <c r="AM3" s="8">
         <f t="shared" si="0"/>
-        <v>2484.8539002875864</v>
+        <v>2711.1271461794154</v>
       </c>
       <c r="AN3" s="8">
         <f t="shared" si="0"/>
-        <v>2609.0965953019659</v>
+        <v>2846.6835034883861</v>
       </c>
     </row>
     <row r="4" spans="2:139" x14ac:dyDescent="0.3">
@@ -1222,16 +1220,15 @@
         <v>66.599999999999994</v>
       </c>
       <c r="T4" s="5">
-        <f t="shared" ref="T4:V4" si="1">T3-T5</f>
-        <v>69.804450000000031</v>
+        <v>69.7</v>
       </c>
       <c r="U4" s="5">
-        <f t="shared" si="1"/>
-        <v>72.051659999999998</v>
+        <f t="shared" ref="U4:V4" si="1">U3-U5</f>
+        <v>78.195600000000013</v>
       </c>
       <c r="V4" s="5">
         <f t="shared" si="1"/>
-        <v>77.80352000000002</v>
+        <v>82.058400000000034</v>
       </c>
       <c r="X4" s="5">
         <v>20.7</v>
@@ -1257,47 +1254,47 @@
       </c>
       <c r="AD4" s="5">
         <f>SUM(S4:V4)</f>
-        <v>286.25963000000002</v>
+        <v>296.55400000000009</v>
       </c>
       <c r="AE4" s="5">
         <f>AE3-AE5</f>
-        <v>358.2032875000001</v>
+        <v>384.41471999999999</v>
       </c>
       <c r="AF4" s="5">
         <f t="shared" ref="AF4:AN4" si="2">AF3-AF5</f>
-        <v>429.84394500000008</v>
+        <v>468.98595840000007</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="2"/>
-        <v>494.32053674999997</v>
+        <v>539.33385215999988</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="2"/>
-        <v>543.75259042500011</v>
+        <v>593.26723737600014</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="2"/>
-        <v>587.25279765900018</v>
+        <v>640.72861636608013</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="2"/>
-        <v>622.48796551854002</v>
+        <v>679.17233334804496</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="2"/>
-        <v>653.61236379446723</v>
+        <v>713.13095001544707</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="2"/>
-        <v>686.29298198419042</v>
+        <v>748.78749751621945</v>
       </c>
       <c r="AM4" s="5">
         <f t="shared" si="2"/>
-        <v>720.60763108340007</v>
+        <v>786.2268723920306</v>
       </c>
       <c r="AN4" s="5">
         <f t="shared" si="2"/>
-        <v>756.63801263757023</v>
+        <v>825.53821601163213</v>
       </c>
     </row>
     <row r="5" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1305,7 +1302,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:S5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:T5" si="3">C3-C4</f>
         <v>40.4</v>
       </c>
       <c r="D5" s="8">
@@ -1373,16 +1370,16 @@
         <v>164.1</v>
       </c>
       <c r="T5" s="8">
-        <f>T3*0.71</f>
-        <v>170.90055000000001</v>
+        <f t="shared" si="3"/>
+        <v>182.60000000000002</v>
       </c>
       <c r="U5" s="8">
         <f t="shared" ref="U5:V5" si="4">U3*0.71</f>
-        <v>176.40234000000001</v>
+        <v>191.44439999999997</v>
       </c>
       <c r="V5" s="8">
         <f t="shared" si="4"/>
-        <v>190.48447999999999</v>
+        <v>200.9016</v>
       </c>
       <c r="X5" s="8">
         <f t="shared" ref="X5:AD5" si="5">X3-X4</f>
@@ -1410,47 +1407,47 @@
       </c>
       <c r="AD5" s="8">
         <f t="shared" si="5"/>
-        <v>701.88737000000003</v>
+        <v>739.04599999999982</v>
       </c>
       <c r="AE5" s="8">
         <f>AE3*0.71</f>
-        <v>876.98046250000004</v>
+        <v>941.15328</v>
       </c>
       <c r="AF5" s="8">
         <f t="shared" ref="AF5:AN5" si="6">AF3*0.71</f>
-        <v>1052.3765550000001</v>
+        <v>1148.2070015999998</v>
       </c>
       <c r="AG5" s="8">
         <f t="shared" si="6"/>
-        <v>1210.2330382499999</v>
+        <v>1320.4380518399998</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="6"/>
-        <v>1331.256342075</v>
+        <v>1452.4818570239997</v>
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="6"/>
-        <v>1437.756849441</v>
+        <v>1568.6804055859197</v>
       </c>
       <c r="AJ5" s="8">
         <f t="shared" si="6"/>
-        <v>1524.0222604074602</v>
+        <v>1662.801229921075</v>
       </c>
       <c r="AK5" s="8">
         <f t="shared" si="6"/>
-        <v>1600.2233734278332</v>
+        <v>1745.9412914171289</v>
       </c>
       <c r="AL5" s="8">
         <f t="shared" si="6"/>
-        <v>1680.2345420992249</v>
+        <v>1833.2383559879854</v>
       </c>
       <c r="AM5" s="8">
         <f t="shared" si="6"/>
-        <v>1764.2462692041863</v>
+        <v>1924.9002737873848</v>
       </c>
       <c r="AN5" s="8">
         <f t="shared" si="6"/>
-        <v>1852.4585826643956</v>
+        <v>2021.145287476754</v>
       </c>
     </row>
     <row r="6" spans="2:139" x14ac:dyDescent="0.3">
@@ -1509,8 +1506,7 @@
         <v>70.400000000000006</v>
       </c>
       <c r="T6" s="5">
-        <f t="shared" ref="T6" si="7">P6*1.3</f>
-        <v>71.63000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="U6" s="5">
         <f>Q6*1.23</f>
@@ -1544,47 +1540,47 @@
       </c>
       <c r="AD6" s="5">
         <f>SUM(S6:V6)</f>
-        <v>300.40500000000003</v>
+        <v>302.47500000000002</v>
       </c>
       <c r="AE6" s="5">
         <f>AD6*1.18</f>
-        <v>354.47790000000003</v>
+        <v>356.9205</v>
       </c>
       <c r="AF6" s="5">
         <f>AE6*1.12</f>
-        <v>397.0152480000001</v>
+        <v>399.75096000000002</v>
       </c>
       <c r="AG6" s="5">
         <f>AF6*1.06</f>
-        <v>420.83616288000013</v>
+        <v>423.73601760000003</v>
       </c>
       <c r="AH6" s="5">
         <f>AG6*1.04</f>
-        <v>437.66960939520015</v>
+        <v>440.68545830400006</v>
       </c>
       <c r="AI6" s="5">
         <f>AH6*1.03</f>
-        <v>450.79969767705614</v>
+        <v>453.90602205312007</v>
       </c>
       <c r="AJ6" s="5">
         <f>AI6*1.02</f>
-        <v>459.81569163059726</v>
+        <v>462.98414249418249</v>
       </c>
       <c r="AK6" s="5">
-        <f t="shared" ref="AK6:AN6" si="8">AJ6*1.02</f>
-        <v>469.01200546320922</v>
+        <f t="shared" ref="AK6:AN6" si="7">AJ6*1.02</f>
+        <v>472.24382534406612</v>
       </c>
       <c r="AL6" s="5">
-        <f t="shared" si="8"/>
-        <v>478.39224557247343</v>
+        <f t="shared" si="7"/>
+        <v>481.68870185094744</v>
       </c>
       <c r="AM6" s="5">
-        <f t="shared" si="8"/>
-        <v>487.9600904839229</v>
+        <f t="shared" si="7"/>
+        <v>491.32247588796639</v>
       </c>
       <c r="AN6" s="5">
-        <f t="shared" si="8"/>
-        <v>497.71929229360137</v>
+        <f t="shared" si="7"/>
+        <v>501.14892540572572</v>
       </c>
     </row>
     <row r="7" spans="2:139" x14ac:dyDescent="0.3">
@@ -1643,16 +1639,15 @@
         <v>26.7</v>
       </c>
       <c r="T7" s="5">
-        <f t="shared" ref="T7:V7" si="9">T3*0.11</f>
-        <v>26.477550000000004</v>
+        <v>29.6</v>
       </c>
       <c r="U7" s="5">
-        <f t="shared" si="9"/>
-        <v>27.329940000000001</v>
+        <f t="shared" ref="U7:V7" si="8">U3*0.11</f>
+        <v>29.660399999999999</v>
       </c>
       <c r="V7" s="5">
-        <f t="shared" si="9"/>
-        <v>29.511680000000002</v>
+        <f t="shared" si="8"/>
+        <v>31.125600000000006</v>
       </c>
       <c r="X7" s="5">
         <v>15</v>
@@ -1678,47 +1673,47 @@
       </c>
       <c r="AD7" s="5">
         <f>SUM(S7:V7)</f>
-        <v>110.01917</v>
+        <v>117.086</v>
       </c>
       <c r="AE7" s="5">
         <f>AE3*0.1</f>
-        <v>123.51837500000002</v>
+        <v>132.55680000000001</v>
       </c>
       <c r="AF7" s="5">
         <f>AF3*0.09</f>
-        <v>133.399845</v>
+        <v>145.54736639999999</v>
       </c>
       <c r="AG7" s="5">
         <f>AG3*0.09</f>
-        <v>153.40982174999999</v>
+        <v>167.37947135999997</v>
       </c>
       <c r="AH7" s="5">
-        <f t="shared" ref="AH7:AN7" si="10">AH3*0.09</f>
-        <v>168.75080392500001</v>
+        <f t="shared" ref="AH7:AN7" si="9">AH3*0.09</f>
+        <v>184.11741849599997</v>
       </c>
       <c r="AI7" s="5">
-        <f t="shared" si="10"/>
-        <v>182.250868239</v>
+        <f t="shared" si="9"/>
+        <v>198.84681197567997</v>
       </c>
       <c r="AJ7" s="5">
-        <f t="shared" si="10"/>
-        <v>193.18592033334002</v>
+        <f t="shared" si="9"/>
+        <v>210.77762069422079</v>
       </c>
       <c r="AK7" s="5">
-        <f t="shared" si="10"/>
-        <v>202.84521635000704</v>
+        <f t="shared" si="9"/>
+        <v>221.31650172893183</v>
       </c>
       <c r="AL7" s="5">
-        <f t="shared" si="10"/>
-        <v>212.98747716750736</v>
+        <f t="shared" si="9"/>
+        <v>232.38232681537843</v>
       </c>
       <c r="AM7" s="5">
-        <f t="shared" si="10"/>
-        <v>223.63685102588278</v>
+        <f t="shared" si="9"/>
+        <v>244.00144315614739</v>
       </c>
       <c r="AN7" s="5">
-        <f t="shared" si="10"/>
-        <v>234.81869357717693</v>
+        <f t="shared" si="9"/>
+        <v>256.20151531395476</v>
       </c>
     </row>
     <row r="8" spans="2:139" x14ac:dyDescent="0.3">
@@ -1777,11 +1772,10 @@
         <v>43.5</v>
       </c>
       <c r="T8" s="5">
-        <f>P8*1.3</f>
-        <v>48.1</v>
+        <v>46</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" ref="U8" si="11">Q8*1.25</f>
+        <f t="shared" ref="U8" si="10">Q8*1.25</f>
         <v>48</v>
       </c>
       <c r="V8" s="5">
@@ -1812,47 +1806,47 @@
       </c>
       <c r="AD8" s="5">
         <f>SUM(S8:V8)</f>
-        <v>193.29</v>
+        <v>191.19</v>
       </c>
       <c r="AE8" s="5">
         <f>AD8*1.17</f>
-        <v>226.14929999999998</v>
+        <v>223.69229999999999</v>
       </c>
       <c r="AF8" s="5">
         <f>AE8*1.11</f>
-        <v>251.025723</v>
+        <v>248.29845300000002</v>
       </c>
       <c r="AG8" s="5">
         <f>AF8*1.07</f>
-        <v>268.59752361</v>
+        <v>265.67934471000007</v>
       </c>
       <c r="AH8" s="5">
         <f>AG8*1.04</f>
-        <v>279.34142455440002</v>
+        <v>276.30651849840007</v>
       </c>
       <c r="AI8" s="5">
         <f>AH8*1.03</f>
-        <v>287.72166729103202</v>
+        <v>284.59571405335208</v>
       </c>
       <c r="AJ8" s="5">
         <f>AI8*1.02</f>
-        <v>293.47610063685266</v>
+        <v>290.28762833441914</v>
       </c>
       <c r="AK8" s="5">
         <f>AJ8*1.01</f>
-        <v>296.41086164322121</v>
+        <v>293.19050461776334</v>
       </c>
       <c r="AL8" s="5">
-        <f t="shared" ref="AL8:AN8" si="12">AK8*1.01</f>
-        <v>299.37497025965342</v>
+        <f t="shared" ref="AL8:AN8" si="11">AK8*1.01</f>
+        <v>296.12240966394097</v>
       </c>
       <c r="AM8" s="5">
-        <f t="shared" si="12"/>
-        <v>302.36871996224994</v>
+        <f t="shared" si="11"/>
+        <v>299.08363376058037</v>
       </c>
       <c r="AN8" s="5">
-        <f t="shared" si="12"/>
-        <v>305.39240716187243</v>
+        <f t="shared" si="11"/>
+        <v>302.07447009818617</v>
       </c>
     </row>
     <row r="9" spans="2:139" x14ac:dyDescent="0.3">
@@ -1860,152 +1854,152 @@
         <v>17</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" ref="C9:R9" si="13">SUM(C6:C8)</f>
+        <f t="shared" ref="C9:R9" si="12">SUM(C6:C8)</f>
         <v>53.8</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>43.1</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>74.2</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>70.400000000000006</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>71.599999999999994</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>79.599999999999994</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>89.9</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>94.2</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>92.6</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>97.8</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>106</v>
       </c>
       <c r="N9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>105.60000000000001</v>
       </c>
       <c r="O9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>105.9</v>
       </c>
       <c r="P9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>112.3</v>
       </c>
       <c r="Q9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>126.9</v>
       </c>
       <c r="R9" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>136.69999999999999</v>
       </c>
       <c r="S9" s="5">
-        <f t="shared" ref="S9" si="14">SUM(S6:S8)</f>
+        <f t="shared" ref="S9" si="13">SUM(S6:S8)</f>
         <v>140.60000000000002</v>
       </c>
       <c r="T9" s="5">
-        <f t="shared" ref="T9" si="15">SUM(T6:T8)</f>
-        <v>146.20755000000003</v>
+        <f t="shared" ref="T9" si="14">SUM(T6:T8)</f>
+        <v>149.30000000000001</v>
       </c>
       <c r="U9" s="5">
-        <f t="shared" ref="U9" si="16">SUM(U6:U8)</f>
-        <v>152.69693999999998</v>
+        <f t="shared" ref="U9" si="15">SUM(U6:U8)</f>
+        <v>155.0274</v>
       </c>
       <c r="V9" s="5">
-        <f t="shared" ref="V9" si="17">SUM(V6:V8)</f>
-        <v>164.20967999999999</v>
+        <f t="shared" ref="V9" si="16">SUM(V6:V8)</f>
+        <v>165.8236</v>
       </c>
       <c r="X9" s="5">
-        <f t="shared" ref="X9:AD9" si="18">SUM(X6:X8)</f>
+        <f t="shared" ref="X9:AD9" si="17">SUM(X6:X8)</f>
         <v>63</v>
       </c>
       <c r="Y9" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>131.69999999999999</v>
       </c>
       <c r="Z9" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>241.5</v>
       </c>
       <c r="AA9" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>335.3</v>
       </c>
       <c r="AB9" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>402</v>
       </c>
       <c r="AC9" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>481.8</v>
       </c>
       <c r="AD9" s="5">
-        <f t="shared" si="18"/>
-        <v>603.71416999999997</v>
+        <f t="shared" si="17"/>
+        <v>610.75099999999998</v>
       </c>
       <c r="AE9" s="5">
-        <f t="shared" ref="AE9" si="19">SUM(AE6:AE8)</f>
-        <v>704.14557500000001</v>
+        <f t="shared" ref="AE9" si="18">SUM(AE6:AE8)</f>
+        <v>713.16959999999995</v>
       </c>
       <c r="AF9" s="5">
-        <f t="shared" ref="AF9" si="20">SUM(AF6:AF8)</f>
-        <v>781.44081600000004</v>
+        <f t="shared" ref="AF9" si="19">SUM(AF6:AF8)</f>
+        <v>793.59677939999995</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" ref="AG9" si="21">SUM(AG6:AG8)</f>
-        <v>842.84350824000012</v>
+        <f t="shared" ref="AG9" si="20">SUM(AG6:AG8)</f>
+        <v>856.79483367000012</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" ref="AH9" si="22">SUM(AH6:AH8)</f>
-        <v>885.76183787460013</v>
+        <f t="shared" ref="AH9" si="21">SUM(AH6:AH8)</f>
+        <v>901.10939529840016</v>
       </c>
       <c r="AI9" s="5">
-        <f t="shared" ref="AI9" si="23">SUM(AI6:AI8)</f>
-        <v>920.77223320708822</v>
+        <f t="shared" ref="AI9" si="22">SUM(AI6:AI8)</f>
+        <v>937.34854808215209</v>
       </c>
       <c r="AJ9" s="5">
-        <f t="shared" ref="AJ9" si="24">SUM(AJ6:AJ8)</f>
-        <v>946.47771260079003</v>
+        <f t="shared" ref="AJ9" si="23">SUM(AJ6:AJ8)</f>
+        <v>964.04939152282236</v>
       </c>
       <c r="AK9" s="5">
-        <f t="shared" ref="AK9" si="25">SUM(AK6:AK8)</f>
-        <v>968.26808345643747</v>
+        <f t="shared" ref="AK9" si="24">SUM(AK6:AK8)</f>
+        <v>986.75083169076129</v>
       </c>
       <c r="AL9" s="5">
-        <f t="shared" ref="AL9" si="26">SUM(AL6:AL8)</f>
-        <v>990.75469299963424</v>
+        <f t="shared" ref="AL9" si="25">SUM(AL6:AL8)</f>
+        <v>1010.1934383302669</v>
       </c>
       <c r="AM9" s="5">
-        <f t="shared" ref="AM9" si="27">SUM(AM6:AM8)</f>
-        <v>1013.9656614720557</v>
+        <f t="shared" ref="AM9" si="26">SUM(AM6:AM8)</f>
+        <v>1034.4075528046942</v>
       </c>
       <c r="AN9" s="5">
-        <f t="shared" ref="AN9" si="28">SUM(AN6:AN8)</f>
-        <v>1037.9303930326507</v>
+        <f t="shared" ref="AN9" si="27">SUM(AN6:AN8)</f>
+        <v>1059.4249108178667</v>
       </c>
     </row>
     <row r="10" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2013,152 +2007,152 @@
         <v>18</v>
       </c>
       <c r="C10" s="8">
-        <f t="shared" ref="C10:R10" si="29">C5-C9</f>
+        <f t="shared" ref="C10:R10" si="28">C5-C9</f>
         <v>-13.399999999999999</v>
       </c>
       <c r="D10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-0.40000000000000568</v>
       </c>
       <c r="E10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-28.700000000000003</v>
       </c>
       <c r="F10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-17.400000000000006</v>
       </c>
       <c r="G10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-11.899999999999991</v>
       </c>
       <c r="H10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-15.099999999999994</v>
       </c>
       <c r="I10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-20.100000000000009</v>
       </c>
       <c r="J10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-18.200000000000003</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-8.3999999999999915</v>
       </c>
       <c r="L10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-4.7999999999999972</v>
       </c>
       <c r="M10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>-4.7000000000000028</v>
       </c>
       <c r="N10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>4.7999999999999972</v>
       </c>
       <c r="O10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>16.499999999999986</v>
       </c>
       <c r="P10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>18.700000000000003</v>
       </c>
       <c r="Q10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>13.499999999999972</v>
       </c>
       <c r="R10" s="8">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
         <v>14</v>
       </c>
       <c r="S10" s="8">
-        <f t="shared" ref="S10" si="30">S5-S9</f>
+        <f t="shared" ref="S10" si="29">S5-S9</f>
         <v>23.499999999999972</v>
       </c>
       <c r="T10" s="8">
-        <f t="shared" ref="T10" si="31">T5-T9</f>
-        <v>24.692999999999984</v>
+        <f t="shared" ref="T10" si="30">T5-T9</f>
+        <v>33.300000000000011</v>
       </c>
       <c r="U10" s="8">
-        <f t="shared" ref="U10" si="32">U5-U9</f>
-        <v>23.705400000000026</v>
+        <f t="shared" ref="U10" si="31">U5-U9</f>
+        <v>36.416999999999973</v>
       </c>
       <c r="V10" s="8">
-        <f t="shared" ref="V10" si="33">V5-V9</f>
-        <v>26.274799999999999</v>
+        <f t="shared" ref="V10" si="32">V5-V9</f>
+        <v>35.078000000000003</v>
       </c>
       <c r="X10" s="8">
-        <f t="shared" ref="X10:AD10" si="34">X5-X9</f>
+        <f t="shared" ref="X10:AD10" si="33">X5-X9</f>
         <v>-12.900000000000006</v>
       </c>
       <c r="Y10" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>-16</v>
       </c>
       <c r="Z10" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>-59.900000000000034</v>
       </c>
       <c r="AA10" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>-65.299999999999955</v>
       </c>
       <c r="AB10" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>-13.099999999999966</v>
       </c>
       <c r="AC10" s="8">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>62.699999999999989</v>
       </c>
       <c r="AD10" s="8">
-        <f t="shared" si="34"/>
-        <v>98.173200000000065</v>
+        <f t="shared" si="33"/>
+        <v>128.29499999999985</v>
       </c>
       <c r="AE10" s="8">
-        <f t="shared" ref="AE10" si="35">AE5-AE9</f>
-        <v>172.83488750000004</v>
+        <f t="shared" ref="AE10" si="34">AE5-AE9</f>
+        <v>227.98368000000005</v>
       </c>
       <c r="AF10" s="8">
-        <f t="shared" ref="AF10" si="36">AF5-AF9</f>
-        <v>270.93573900000001</v>
+        <f t="shared" ref="AF10" si="35">AF5-AF9</f>
+        <v>354.61022219999984</v>
       </c>
       <c r="AG10" s="8">
-        <f t="shared" ref="AG10" si="37">AG5-AG9</f>
-        <v>367.38953000999982</v>
+        <f t="shared" ref="AG10" si="36">AG5-AG9</f>
+        <v>463.64321816999973</v>
       </c>
       <c r="AH10" s="8">
-        <f t="shared" ref="AH10" si="38">AH5-AH9</f>
-        <v>445.49450420039989</v>
+        <f t="shared" ref="AH10" si="37">AH5-AH9</f>
+        <v>551.37246172559958</v>
       </c>
       <c r="AI10" s="8">
-        <f t="shared" ref="AI10" si="39">AI5-AI9</f>
-        <v>516.98461623391177</v>
+        <f t="shared" ref="AI10" si="38">AI5-AI9</f>
+        <v>631.33185750376765</v>
       </c>
       <c r="AJ10" s="8">
-        <f t="shared" ref="AJ10" si="40">AJ5-AJ9</f>
-        <v>577.54454780667015</v>
+        <f t="shared" ref="AJ10" si="39">AJ5-AJ9</f>
+        <v>698.75183839825263</v>
       </c>
       <c r="AK10" s="8">
-        <f t="shared" ref="AK10" si="41">AK5-AK9</f>
-        <v>631.9552899713957</v>
+        <f t="shared" ref="AK10" si="40">AK5-AK9</f>
+        <v>759.19045972636764</v>
       </c>
       <c r="AL10" s="8">
-        <f t="shared" ref="AL10" si="42">AL5-AL9</f>
-        <v>689.47984909959064</v>
+        <f t="shared" ref="AL10" si="41">AL5-AL9</f>
+        <v>823.04491765771854</v>
       </c>
       <c r="AM10" s="8">
-        <f t="shared" ref="AM10" si="43">AM5-AM9</f>
-        <v>750.28060773213065</v>
+        <f t="shared" ref="AM10" si="42">AM5-AM9</f>
+        <v>890.49272098269057</v>
       </c>
       <c r="AN10" s="8">
-        <f t="shared" ref="AN10" si="44">AN5-AN9</f>
-        <v>814.52818963174491</v>
+        <f t="shared" ref="AN10" si="43">AN5-AN9</f>
+        <v>961.72037665888729</v>
       </c>
     </row>
     <row r="11" spans="2:139" x14ac:dyDescent="0.3">
@@ -2217,7 +2211,7 @@
         <v>-1</v>
       </c>
       <c r="T11" s="5">
-        <v>1</v>
+        <v>-1.7</v>
       </c>
       <c r="U11" s="5">
         <v>1</v>
@@ -2249,47 +2243,47 @@
       </c>
       <c r="AD11" s="5">
         <f>SUM(S11:V11)</f>
-        <v>2</v>
+        <v>-0.70000000000000018</v>
       </c>
       <c r="AE11" s="5">
         <f>AD11*1.05</f>
-        <v>2.1</v>
+        <v>-0.73500000000000021</v>
       </c>
       <c r="AF11" s="5">
-        <f t="shared" ref="AF11:AN11" si="45">AE11*1.05</f>
-        <v>2.2050000000000001</v>
+        <f t="shared" ref="AF11:AN11" si="44">AE11*1.05</f>
+        <v>-0.77175000000000027</v>
       </c>
       <c r="AG11" s="5">
-        <f t="shared" si="45"/>
-        <v>2.3152500000000003</v>
+        <f t="shared" si="44"/>
+        <v>-0.81033750000000027</v>
       </c>
       <c r="AH11" s="5">
-        <f t="shared" si="45"/>
-        <v>2.4310125000000005</v>
+        <f t="shared" si="44"/>
+        <v>-0.85085437500000027</v>
       </c>
       <c r="AI11" s="5">
-        <f t="shared" si="45"/>
-        <v>2.5525631250000007</v>
+        <f t="shared" si="44"/>
+        <v>-0.89339709375000032</v>
       </c>
       <c r="AJ11" s="5">
-        <f t="shared" si="45"/>
-        <v>2.6801912812500008</v>
+        <f t="shared" si="44"/>
+        <v>-0.93806694843750038</v>
       </c>
       <c r="AK11" s="5">
-        <f t="shared" si="45"/>
-        <v>2.8142008453125009</v>
+        <f t="shared" si="44"/>
+        <v>-0.98497029585937546</v>
       </c>
       <c r="AL11" s="5">
-        <f t="shared" si="45"/>
-        <v>2.954910887578126</v>
+        <f t="shared" si="44"/>
+        <v>-1.0342188106523442</v>
       </c>
       <c r="AM11" s="5">
-        <f t="shared" si="45"/>
-        <v>3.1026564319570324</v>
+        <f t="shared" si="44"/>
+        <v>-1.0859297511849615</v>
       </c>
       <c r="AN11" s="5">
-        <f t="shared" si="45"/>
-        <v>3.257789253554884</v>
+        <f t="shared" si="44"/>
+        <v>-1.1402262387442097</v>
       </c>
     </row>
     <row r="12" spans="2:139" x14ac:dyDescent="0.3">
@@ -2348,15 +2342,14 @@
         <v>-10.4</v>
       </c>
       <c r="T12" s="5">
-        <f t="shared" ref="T12:V12" si="46">P12*1.05</f>
-        <v>-11.234999999999999</v>
+        <v>-11.4</v>
       </c>
       <c r="U12" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" ref="U12:V12" si="45">Q12*1.05</f>
         <v>-11.76</v>
       </c>
       <c r="V12" s="5">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>-11.234999999999999</v>
       </c>
       <c r="X12" s="5">
@@ -2383,47 +2376,47 @@
       </c>
       <c r="AD12" s="5">
         <f>SUM(S12:V12)</f>
-        <v>-44.629999999999995</v>
+        <v>-44.795000000000002</v>
       </c>
       <c r="AE12" s="5">
         <f>AD12*1.05</f>
-        <v>-46.861499999999999</v>
+        <v>-47.034750000000003</v>
       </c>
       <c r="AF12" s="5">
-        <f t="shared" ref="AF12:AN12" si="47">AE12*1.05</f>
-        <v>-49.204574999999998</v>
+        <f t="shared" ref="AF12:AN12" si="46">AE12*1.05</f>
+        <v>-49.386487500000001</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" si="47"/>
-        <v>-51.664803749999997</v>
+        <f t="shared" si="46"/>
+        <v>-51.855811875000001</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="47"/>
-        <v>-54.2480439375</v>
+        <f t="shared" si="46"/>
+        <v>-54.448602468750003</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" si="47"/>
-        <v>-56.960446134375005</v>
+        <f t="shared" si="46"/>
+        <v>-57.171032592187508</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" si="47"/>
-        <v>-59.808468441093758</v>
+        <f t="shared" si="46"/>
+        <v>-60.029584221796888</v>
       </c>
       <c r="AK12" s="5">
-        <f t="shared" si="47"/>
-        <v>-62.798891863148448</v>
+        <f t="shared" si="46"/>
+        <v>-63.031063432886732</v>
       </c>
       <c r="AL12" s="5">
-        <f t="shared" si="47"/>
-        <v>-65.938836456305879</v>
+        <f t="shared" si="46"/>
+        <v>-66.182616604531077</v>
       </c>
       <c r="AM12" s="5">
-        <f t="shared" si="47"/>
-        <v>-69.235778279121178</v>
+        <f t="shared" si="46"/>
+        <v>-69.491747434757627</v>
       </c>
       <c r="AN12" s="5">
-        <f t="shared" si="47"/>
-        <v>-72.697567193077234</v>
+        <f t="shared" si="46"/>
+        <v>-72.96633480649551</v>
       </c>
     </row>
     <row r="13" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2431,152 +2424,152 @@
         <v>20</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:R13" si="48">C10-C11-C12</f>
+        <f t="shared" ref="C13:R13" si="47">C10-C11-C12</f>
         <v>-13.399999999999999</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>-0.1000000000000057</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>-28.900000000000002</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>-17.400000000000006</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>-12.199999999999992</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>-14.999999999999995</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>-18.300000000000008</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>-13.200000000000003</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>-2.5999999999999925</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>2.400000000000003</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>2.8999999999999968</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>15.199999999999998</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>25.899999999999984</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>28.700000000000003</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>25.299999999999969</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>22.5</v>
       </c>
       <c r="S13" s="8">
-        <f t="shared" ref="S13" si="49">S10-S11-S12</f>
+        <f t="shared" ref="S13" si="48">S10-S11-S12</f>
         <v>34.89999999999997</v>
       </c>
       <c r="T13" s="8">
-        <f t="shared" ref="T13" si="50">T10-T11-T12</f>
-        <v>34.927999999999983</v>
+        <f t="shared" ref="T13" si="49">T10-T11-T12</f>
+        <v>46.400000000000013</v>
       </c>
       <c r="U13" s="8">
-        <f t="shared" ref="U13" si="51">U10-U11-U12</f>
-        <v>34.465400000000024</v>
+        <f t="shared" ref="U13" si="50">U10-U11-U12</f>
+        <v>47.176999999999971</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" ref="V13" si="52">V10-V11-V12</f>
-        <v>36.509799999999998</v>
+        <f t="shared" ref="V13" si="51">V10-V11-V12</f>
+        <v>45.313000000000002</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" ref="X13:AE13" si="53">X10-X11-X12</f>
+        <f t="shared" ref="X13:AE13" si="52">X10-X11-X12</f>
         <v>-12.300000000000006</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>-15.7</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>-59.800000000000033</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>-58.69999999999996</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>17.900000000000034</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>102.39999999999998</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="53"/>
-        <v>140.80320000000006</v>
+        <f t="shared" si="52"/>
+        <v>173.78999999999985</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="53"/>
-        <v>217.59638750000005</v>
+        <f t="shared" si="52"/>
+        <v>275.75343000000009</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" ref="AF13" si="54">AF10-AF11-AF12</f>
-        <v>317.93531400000001</v>
+        <f t="shared" ref="AF13" si="53">AF10-AF11-AF12</f>
+        <v>404.76845969999982</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" ref="AG13" si="55">AG10-AG11-AG12</f>
-        <v>416.7390837599998</v>
+        <f t="shared" ref="AG13" si="54">AG10-AG11-AG12</f>
+        <v>516.30936754499976</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" ref="AH13" si="56">AH10-AH11-AH12</f>
-        <v>497.31153563789985</v>
+        <f t="shared" ref="AH13" si="55">AH10-AH11-AH12</f>
+        <v>606.6719185693496</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" ref="AI13" si="57">AI10-AI11-AI12</f>
-        <v>571.39249924328681</v>
+        <f t="shared" ref="AI13" si="56">AI10-AI11-AI12</f>
+        <v>689.39628718970516</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" ref="AJ13" si="58">AJ10-AJ11-AJ12</f>
-        <v>634.67282496651387</v>
+        <f t="shared" ref="AJ13" si="57">AJ10-AJ11-AJ12</f>
+        <v>759.71948956848701</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" ref="AK13" si="59">AK10-AK11-AK12</f>
-        <v>691.93998098923169</v>
+        <f t="shared" ref="AK13" si="58">AK10-AK11-AK12</f>
+        <v>823.20649345511379</v>
       </c>
       <c r="AL13" s="8">
-        <f t="shared" ref="AL13" si="60">AL10-AL11-AL12</f>
-        <v>752.46377466831848</v>
+        <f t="shared" ref="AL13" si="59">AL10-AL11-AL12</f>
+        <v>890.26175307290191</v>
       </c>
       <c r="AM13" s="8">
-        <f t="shared" ref="AM13" si="61">AM10-AM11-AM12</f>
-        <v>816.4137295792948</v>
+        <f t="shared" ref="AM13" si="60">AM10-AM11-AM12</f>
+        <v>961.07039816863312</v>
       </c>
       <c r="AN13" s="8">
-        <f t="shared" ref="AN13" si="62">AN10-AN11-AN12</f>
-        <v>883.96796757126731</v>
+        <f t="shared" ref="AN13" si="61">AN10-AN11-AN12</f>
+        <v>1035.826937704127</v>
       </c>
     </row>
     <row r="14" spans="2:139" x14ac:dyDescent="0.3">
@@ -2635,16 +2628,15 @@
         <v>-0.1</v>
       </c>
       <c r="T14" s="5">
-        <f t="shared" ref="T14:V14" si="63">T13*0.15</f>
-        <v>5.2391999999999976</v>
+        <v>1.7</v>
       </c>
       <c r="U14" s="5">
-        <f t="shared" si="63"/>
-        <v>5.1698100000000036</v>
+        <f t="shared" ref="U14:V14" si="62">U13*0.15</f>
+        <v>7.0765499999999957</v>
       </c>
       <c r="V14" s="5">
-        <f t="shared" si="63"/>
-        <v>5.4764699999999999</v>
+        <f t="shared" si="62"/>
+        <v>6.7969499999999998</v>
       </c>
       <c r="X14" s="5">
         <v>0</v>
@@ -2670,47 +2662,47 @@
       </c>
       <c r="AD14" s="5">
         <f>SUM(S14:V14)</f>
-        <v>15.78548</v>
+        <v>15.473499999999994</v>
       </c>
       <c r="AE14" s="5">
         <f>AE13*0.15</f>
-        <v>32.639458125000004</v>
+        <v>41.363014500000013</v>
       </c>
       <c r="AF14" s="5">
-        <f t="shared" ref="AF14:AN14" si="64">AF13*0.15</f>
-        <v>47.690297100000002</v>
+        <f t="shared" ref="AF14:AN14" si="63">AF13*0.15</f>
+        <v>60.715268954999971</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" si="64"/>
-        <v>62.510862563999964</v>
+        <f t="shared" si="63"/>
+        <v>77.446405131749955</v>
       </c>
       <c r="AH14" s="5">
-        <f t="shared" si="64"/>
-        <v>74.596730345684975</v>
+        <f t="shared" si="63"/>
+        <v>91.000787785402437</v>
       </c>
       <c r="AI14" s="5">
-        <f t="shared" si="64"/>
-        <v>85.708874886493021</v>
+        <f t="shared" si="63"/>
+        <v>103.40944307845577</v>
       </c>
       <c r="AJ14" s="5">
-        <f t="shared" si="64"/>
-        <v>95.200923744977075</v>
+        <f t="shared" si="63"/>
+        <v>113.95792343527305</v>
       </c>
       <c r="AK14" s="5">
-        <f t="shared" si="64"/>
-        <v>103.79099714838475</v>
+        <f t="shared" si="63"/>
+        <v>123.48097401826706</v>
       </c>
       <c r="AL14" s="5">
-        <f t="shared" si="64"/>
-        <v>112.86956620024777</v>
+        <f t="shared" si="63"/>
+        <v>133.53926296093528</v>
       </c>
       <c r="AM14" s="5">
-        <f t="shared" si="64"/>
-        <v>122.46205943689421</v>
+        <f t="shared" si="63"/>
+        <v>144.16055972529497</v>
       </c>
       <c r="AN14" s="5">
-        <f t="shared" si="64"/>
-        <v>132.59519513569009</v>
+        <f t="shared" si="63"/>
+        <v>155.37404065561904</v>
       </c>
     </row>
     <row r="15" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2718,548 +2710,548 @@
         <v>22</v>
       </c>
       <c r="C15" s="8">
-        <f t="shared" ref="C15:R15" si="65">C13-C14</f>
+        <f t="shared" ref="C15:R15" si="64">C13-C14</f>
         <v>-13.399999999999999</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>-0.1000000000000057</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>-29.000000000000004</v>
       </c>
       <c r="F15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>-17.500000000000007</v>
       </c>
       <c r="G15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>-12.199999999999992</v>
       </c>
       <c r="H15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>-15.099999999999994</v>
       </c>
       <c r="I15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>-18.400000000000009</v>
       </c>
       <c r="J15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>-13.900000000000002</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>-2.4999999999999925</v>
       </c>
       <c r="L15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>3.7000000000000028</v>
       </c>
       <c r="M15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>2.7999999999999967</v>
       </c>
       <c r="N15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>12.199999999999998</v>
       </c>
       <c r="O15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>26.999999999999986</v>
       </c>
       <c r="P15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>24.300000000000004</v>
       </c>
       <c r="Q15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>23.299999999999969</v>
       </c>
       <c r="R15" s="8">
-        <f t="shared" si="65"/>
+        <f t="shared" si="64"/>
         <v>14.1</v>
       </c>
       <c r="S15" s="8">
-        <f t="shared" ref="S15" si="66">S13-S14</f>
+        <f t="shared" ref="S15" si="65">S13-S14</f>
         <v>34.999999999999972</v>
       </c>
       <c r="T15" s="8">
-        <f t="shared" ref="T15" si="67">T13-T14</f>
-        <v>29.688799999999986</v>
+        <f t="shared" ref="T15" si="66">T13-T14</f>
+        <v>44.70000000000001</v>
       </c>
       <c r="U15" s="8">
-        <f t="shared" ref="U15" si="68">U13-U14</f>
-        <v>29.295590000000018</v>
+        <f t="shared" ref="U15" si="67">U13-U14</f>
+        <v>40.100449999999974</v>
       </c>
       <c r="V15" s="8">
-        <f t="shared" ref="V15" si="69">V13-V14</f>
-        <v>31.033329999999999</v>
+        <f t="shared" ref="V15" si="68">V13-V14</f>
+        <v>38.51605</v>
       </c>
       <c r="X15" s="8">
-        <f t="shared" ref="X15:AE15" si="70">X13-X14</f>
+        <f t="shared" ref="X15:AE15" si="69">X13-X14</f>
         <v>-12.300000000000006</v>
       </c>
       <c r="Y15" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>-15.799999999999999</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>-60.000000000000036</v>
       </c>
       <c r="AA15" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>-59.599999999999959</v>
       </c>
       <c r="AB15" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>16.200000000000035</v>
       </c>
       <c r="AC15" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>88.699999999999974</v>
       </c>
       <c r="AD15" s="8">
-        <f t="shared" si="70"/>
-        <v>125.01772000000005</v>
+        <f t="shared" si="69"/>
+        <v>158.31649999999985</v>
       </c>
       <c r="AE15" s="8">
-        <f t="shared" si="70"/>
-        <v>184.95692937500004</v>
+        <f t="shared" si="69"/>
+        <v>234.39041550000007</v>
       </c>
       <c r="AF15" s="8">
-        <f t="shared" ref="AF15" si="71">AF13-AF14</f>
-        <v>270.2450169</v>
+        <f t="shared" ref="AF15" si="70">AF13-AF14</f>
+        <v>344.05319074499982</v>
       </c>
       <c r="AG15" s="8">
-        <f t="shared" ref="AG15" si="72">AG13-AG14</f>
-        <v>354.22822119599982</v>
+        <f t="shared" ref="AG15" si="71">AG13-AG14</f>
+        <v>438.86296241324982</v>
       </c>
       <c r="AH15" s="8">
-        <f t="shared" ref="AH15" si="73">AH13-AH14</f>
-        <v>422.71480529221486</v>
+        <f t="shared" ref="AH15" si="72">AH13-AH14</f>
+        <v>515.67113078394721</v>
       </c>
       <c r="AI15" s="8">
-        <f t="shared" ref="AI15" si="74">AI13-AI14</f>
-        <v>485.68362435679376</v>
+        <f t="shared" ref="AI15" si="73">AI13-AI14</f>
+        <v>585.98684411124941</v>
       </c>
       <c r="AJ15" s="8">
-        <f t="shared" ref="AJ15" si="75">AJ13-AJ14</f>
-        <v>539.47190122153677</v>
+        <f t="shared" ref="AJ15" si="74">AJ13-AJ14</f>
+        <v>645.76156613321393</v>
       </c>
       <c r="AK15" s="8">
-        <f t="shared" ref="AK15" si="76">AK13-AK14</f>
-        <v>588.148983840847</v>
+        <f t="shared" ref="AK15" si="75">AK13-AK14</f>
+        <v>699.72551943684675</v>
       </c>
       <c r="AL15" s="8">
-        <f t="shared" ref="AL15" si="77">AL13-AL14</f>
-        <v>639.59420846807075</v>
+        <f t="shared" ref="AL15" si="76">AL13-AL14</f>
+        <v>756.72249011196664</v>
       </c>
       <c r="AM15" s="8">
-        <f t="shared" ref="AM15" si="78">AM13-AM14</f>
-        <v>693.95167014240064</v>
+        <f t="shared" ref="AM15" si="77">AM13-AM14</f>
+        <v>816.90983844333812</v>
       </c>
       <c r="AN15" s="8">
-        <f t="shared" ref="AN15" si="79">AN13-AN14</f>
-        <v>751.37277243557719</v>
+        <f t="shared" ref="AN15" si="78">AN13-AN14</f>
+        <v>880.45289704850791</v>
       </c>
       <c r="AO15" s="1">
         <f>AN15*(1+$AR$21)</f>
-        <v>743.85904471122137</v>
+        <v>871.64836807802283</v>
       </c>
       <c r="AP15" s="1">
-        <f t="shared" ref="AP15:DA15" si="80">AO15*(1+$AR$21)</f>
-        <v>736.42045426410914</v>
+        <f t="shared" ref="AP15:DA15" si="79">AO15*(1+$AR$21)</f>
+        <v>862.93188439724258</v>
       </c>
       <c r="AQ15" s="1">
+        <f t="shared" si="79"/>
+        <v>854.30256555327014</v>
+      </c>
+      <c r="AR15" s="1">
+        <f t="shared" si="79"/>
+        <v>845.75953989773745</v>
+      </c>
+      <c r="AS15" s="1">
+        <f t="shared" si="79"/>
+        <v>837.30194449876012</v>
+      </c>
+      <c r="AT15" s="1">
+        <f t="shared" si="79"/>
+        <v>828.92892505377256</v>
+      </c>
+      <c r="AU15" s="1">
+        <f t="shared" si="79"/>
+        <v>820.6396358032348</v>
+      </c>
+      <c r="AV15" s="1">
+        <f t="shared" si="79"/>
+        <v>812.43323944520239</v>
+      </c>
+      <c r="AW15" s="1">
+        <f t="shared" si="79"/>
+        <v>804.30890705075035</v>
+      </c>
+      <c r="AX15" s="1">
+        <f t="shared" si="79"/>
+        <v>796.26581798024279</v>
+      </c>
+      <c r="AY15" s="1">
+        <f t="shared" si="79"/>
+        <v>788.30315980044031</v>
+      </c>
+      <c r="AZ15" s="1">
+        <f t="shared" si="79"/>
+        <v>780.42012820243588</v>
+      </c>
+      <c r="BA15" s="1">
+        <f t="shared" si="79"/>
+        <v>772.61592692041154</v>
+      </c>
+      <c r="BB15" s="1">
+        <f t="shared" si="79"/>
+        <v>764.88976765120742</v>
+      </c>
+      <c r="BC15" s="1">
+        <f t="shared" si="79"/>
+        <v>757.24086997469533</v>
+      </c>
+      <c r="BD15" s="1">
+        <f t="shared" si="79"/>
+        <v>749.66846127494841</v>
+      </c>
+      <c r="BE15" s="1">
+        <f t="shared" si="79"/>
+        <v>742.17177666219891</v>
+      </c>
+      <c r="BF15" s="1">
+        <f t="shared" si="79"/>
+        <v>734.7500588955769</v>
+      </c>
+      <c r="BG15" s="1">
+        <f t="shared" si="79"/>
+        <v>727.40255830662113</v>
+      </c>
+      <c r="BH15" s="1">
+        <f t="shared" si="79"/>
+        <v>720.12853272355494</v>
+      </c>
+      <c r="BI15" s="1">
+        <f t="shared" si="79"/>
+        <v>712.92724739631933</v>
+      </c>
+      <c r="BJ15" s="1">
+        <f t="shared" si="79"/>
+        <v>705.79797492235616</v>
+      </c>
+      <c r="BK15" s="1">
+        <f t="shared" si="79"/>
+        <v>698.73999517313257</v>
+      </c>
+      <c r="BL15" s="1">
+        <f t="shared" si="79"/>
+        <v>691.75259522140129</v>
+      </c>
+      <c r="BM15" s="1">
+        <f t="shared" si="79"/>
+        <v>684.83506926918733</v>
+      </c>
+      <c r="BN15" s="1">
+        <f t="shared" si="79"/>
+        <v>677.98671857649549</v>
+      </c>
+      <c r="BO15" s="1">
+        <f t="shared" si="79"/>
+        <v>671.20685139073055</v>
+      </c>
+      <c r="BP15" s="1">
+        <f t="shared" si="79"/>
+        <v>664.49478287682325</v>
+      </c>
+      <c r="BQ15" s="1">
+        <f t="shared" si="79"/>
+        <v>657.84983504805496</v>
+      </c>
+      <c r="BR15" s="1">
+        <f t="shared" si="79"/>
+        <v>651.27133669757438</v>
+      </c>
+      <c r="BS15" s="1">
+        <f t="shared" si="79"/>
+        <v>644.75862333059865</v>
+      </c>
+      <c r="BT15" s="1">
+        <f t="shared" si="79"/>
+        <v>638.31103709729268</v>
+      </c>
+      <c r="BU15" s="1">
+        <f t="shared" si="79"/>
+        <v>631.9279267263197</v>
+      </c>
+      <c r="BV15" s="1">
+        <f t="shared" si="79"/>
+        <v>625.60864745905644</v>
+      </c>
+      <c r="BW15" s="1">
+        <f t="shared" si="79"/>
+        <v>619.35256098446587</v>
+      </c>
+      <c r="BX15" s="1">
+        <f t="shared" si="79"/>
+        <v>613.15903537462123</v>
+      </c>
+      <c r="BY15" s="1">
+        <f t="shared" si="79"/>
+        <v>607.02744502087501</v>
+      </c>
+      <c r="BZ15" s="1">
+        <f t="shared" si="79"/>
+        <v>600.95717057066622</v>
+      </c>
+      <c r="CA15" s="1">
+        <f t="shared" si="79"/>
+        <v>594.94759886495956</v>
+      </c>
+      <c r="CB15" s="1">
+        <f t="shared" si="79"/>
+        <v>588.99812287630994</v>
+      </c>
+      <c r="CC15" s="1">
+        <f t="shared" si="79"/>
+        <v>583.10814164754686</v>
+      </c>
+      <c r="CD15" s="1">
+        <f t="shared" si="79"/>
+        <v>577.27706023107135</v>
+      </c>
+      <c r="CE15" s="1">
+        <f t="shared" si="79"/>
+        <v>571.5042896287606</v>
+      </c>
+      <c r="CF15" s="1">
+        <f t="shared" si="79"/>
+        <v>565.78924673247298</v>
+      </c>
+      <c r="CG15" s="1">
+        <f t="shared" si="79"/>
+        <v>560.13135426514827</v>
+      </c>
+      <c r="CH15" s="1">
+        <f t="shared" si="79"/>
+        <v>554.53004072249678</v>
+      </c>
+      <c r="CI15" s="1">
+        <f t="shared" si="79"/>
+        <v>548.98474031527178</v>
+      </c>
+      <c r="CJ15" s="1">
+        <f t="shared" si="79"/>
+        <v>543.4948929121191</v>
+      </c>
+      <c r="CK15" s="1">
+        <f t="shared" si="79"/>
+        <v>538.05994398299788</v>
+      </c>
+      <c r="CL15" s="1">
+        <f t="shared" si="79"/>
+        <v>532.67934454316787</v>
+      </c>
+      <c r="CM15" s="1">
+        <f t="shared" si="79"/>
+        <v>527.35255109773618</v>
+      </c>
+      <c r="CN15" s="1">
+        <f t="shared" si="79"/>
+        <v>522.0790255867588</v>
+      </c>
+      <c r="CO15" s="1">
+        <f t="shared" si="79"/>
+        <v>516.85823533089126</v>
+      </c>
+      <c r="CP15" s="1">
+        <f t="shared" si="79"/>
+        <v>511.68965297758234</v>
+      </c>
+      <c r="CQ15" s="1">
+        <f t="shared" si="79"/>
+        <v>506.57275644780651</v>
+      </c>
+      <c r="CR15" s="1">
+        <f t="shared" si="79"/>
+        <v>501.50702888332842</v>
+      </c>
+      <c r="CS15" s="1">
+        <f t="shared" si="79"/>
+        <v>496.49195859449515</v>
+      </c>
+      <c r="CT15" s="1">
+        <f t="shared" si="79"/>
+        <v>491.52703900855016</v>
+      </c>
+      <c r="CU15" s="1">
+        <f t="shared" si="79"/>
+        <v>486.61176861846468</v>
+      </c>
+      <c r="CV15" s="1">
+        <f t="shared" si="79"/>
+        <v>481.74565093228006</v>
+      </c>
+      <c r="CW15" s="1">
+        <f t="shared" si="79"/>
+        <v>476.92819442295723</v>
+      </c>
+      <c r="CX15" s="1">
+        <f t="shared" si="79"/>
+        <v>472.15891247872764</v>
+      </c>
+      <c r="CY15" s="1">
+        <f t="shared" si="79"/>
+        <v>467.43732335394037</v>
+      </c>
+      <c r="CZ15" s="1">
+        <f t="shared" si="79"/>
+        <v>462.76295012040094</v>
+      </c>
+      <c r="DA15" s="1">
+        <f t="shared" si="79"/>
+        <v>458.13532061919693</v>
+      </c>
+      <c r="DB15" s="1">
+        <f t="shared" ref="DB15:EI15" si="80">DA15*(1+$AR$21)</f>
+        <v>453.55396741300495</v>
+      </c>
+      <c r="DC15" s="1">
         <f t="shared" si="80"/>
-        <v>729.05624972146802</v>
-      </c>
-      <c r="AR15" s="1">
+        <v>449.01842773887489</v>
+      </c>
+      <c r="DD15" s="1">
         <f t="shared" si="80"/>
-        <v>721.76568722425338</v>
-      </c>
-      <c r="AS15" s="1">
+        <v>444.52824346148611</v>
+      </c>
+      <c r="DE15" s="1">
         <f t="shared" si="80"/>
-        <v>714.54803035201087</v>
-      </c>
-      <c r="AT15" s="1">
+        <v>440.08296102687126</v>
+      </c>
+      <c r="DF15" s="1">
         <f t="shared" si="80"/>
-        <v>707.40255004849075</v>
-      </c>
-      <c r="AU15" s="1">
+        <v>435.68213141660254</v>
+      </c>
+      <c r="DG15" s="1">
         <f t="shared" si="80"/>
-        <v>700.32852454800582</v>
-      </c>
-      <c r="AV15" s="1">
+        <v>431.3253101024365</v>
+      </c>
+      <c r="DH15" s="1">
         <f t="shared" si="80"/>
-        <v>693.3252393025258</v>
-      </c>
-      <c r="AW15" s="1">
+        <v>427.01205700141213</v>
+      </c>
+      <c r="DI15" s="1">
         <f t="shared" si="80"/>
-        <v>686.39198690950059</v>
-      </c>
-      <c r="AX15" s="1">
+        <v>422.74193643139802</v>
+      </c>
+      <c r="DJ15" s="1">
         <f t="shared" si="80"/>
-        <v>679.52806704040563</v>
-      </c>
-      <c r="AY15" s="1">
+        <v>418.51451706708406</v>
+      </c>
+      <c r="DK15" s="1">
         <f t="shared" si="80"/>
-        <v>672.73278637000158</v>
-      </c>
-      <c r="AZ15" s="1">
+        <v>414.32937189641319</v>
+      </c>
+      <c r="DL15" s="1">
         <f t="shared" si="80"/>
-        <v>666.00545850630158</v>
-      </c>
-      <c r="BA15" s="1">
+        <v>410.18607817744908</v>
+      </c>
+      <c r="DM15" s="1">
         <f t="shared" si="80"/>
-        <v>659.34540392123859</v>
-      </c>
-      <c r="BB15" s="1">
+        <v>406.08421739567456</v>
+      </c>
+      <c r="DN15" s="1">
         <f t="shared" si="80"/>
-        <v>652.75194988202622</v>
-      </c>
-      <c r="BC15" s="1">
+        <v>402.0233752217178</v>
+      </c>
+      <c r="DO15" s="1">
         <f t="shared" si="80"/>
-        <v>646.22443038320591</v>
-      </c>
-      <c r="BD15" s="1">
+        <v>398.00314146950063</v>
+      </c>
+      <c r="DP15" s="1">
         <f t="shared" si="80"/>
-        <v>639.76218607937381</v>
-      </c>
-      <c r="BE15" s="1">
+        <v>394.02311005480561</v>
+      </c>
+      <c r="DQ15" s="1">
         <f t="shared" si="80"/>
-        <v>633.36456421858009</v>
-      </c>
-      <c r="BF15" s="1">
+        <v>390.08287895425758</v>
+      </c>
+      <c r="DR15" s="1">
         <f t="shared" si="80"/>
-        <v>627.03091857639424</v>
-      </c>
-      <c r="BG15" s="1">
+        <v>386.18205016471501</v>
+      </c>
+      <c r="DS15" s="1">
         <f t="shared" si="80"/>
-        <v>620.76060939063029</v>
-      </c>
-      <c r="BH15" s="1">
+        <v>382.32022966306783</v>
+      </c>
+      <c r="DT15" s="1">
         <f t="shared" si="80"/>
-        <v>614.553003296724</v>
-      </c>
-      <c r="BI15" s="1">
+        <v>378.49702736643718</v>
+      </c>
+      <c r="DU15" s="1">
         <f t="shared" si="80"/>
-        <v>608.40747326375674</v>
-      </c>
-      <c r="BJ15" s="1">
+        <v>374.7120570927728</v>
+      </c>
+      <c r="DV15" s="1">
         <f t="shared" si="80"/>
-        <v>602.32339853111921</v>
-      </c>
-      <c r="BK15" s="1">
+        <v>370.96493652184506</v>
+      </c>
+      <c r="DW15" s="1">
         <f t="shared" si="80"/>
-        <v>596.300164545808</v>
-      </c>
-      <c r="BL15" s="1">
+        <v>367.25528715662659</v>
+      </c>
+      <c r="DX15" s="1">
         <f t="shared" si="80"/>
-        <v>590.33716290034988</v>
-      </c>
-      <c r="BM15" s="1">
+        <v>363.58273428506033</v>
+      </c>
+      <c r="DY15" s="1">
         <f t="shared" si="80"/>
-        <v>584.43379127134642</v>
-      </c>
-      <c r="BN15" s="1">
+        <v>359.94690694220969</v>
+      </c>
+      <c r="DZ15" s="1">
         <f t="shared" si="80"/>
-        <v>578.58945335863291</v>
-      </c>
-      <c r="BO15" s="1">
+        <v>356.34743787278757</v>
+      </c>
+      <c r="EA15" s="1">
         <f t="shared" si="80"/>
-        <v>572.80355882504659</v>
-      </c>
-      <c r="BP15" s="1">
+        <v>352.78396349405966</v>
+      </c>
+      <c r="EB15" s="1">
         <f t="shared" si="80"/>
-        <v>567.07552323679613</v>
-      </c>
-      <c r="BQ15" s="1">
+        <v>349.25612385911904</v>
+      </c>
+      <c r="EC15" s="1">
         <f t="shared" si="80"/>
-        <v>561.40476800442821</v>
-      </c>
-      <c r="BR15" s="1">
+        <v>345.76356262052786</v>
+      </c>
+      <c r="ED15" s="1">
         <f t="shared" si="80"/>
-        <v>555.79072032438387</v>
-      </c>
-      <c r="BS15" s="1">
+        <v>342.30592699432259</v>
+      </c>
+      <c r="EE15" s="1">
         <f t="shared" si="80"/>
-        <v>550.23281312114</v>
-      </c>
-      <c r="BT15" s="1">
+        <v>338.88286772437937</v>
+      </c>
+      <c r="EF15" s="1">
         <f t="shared" si="80"/>
-        <v>544.73048498992864</v>
-      </c>
-      <c r="BU15" s="1">
+        <v>335.49403904713557</v>
+      </c>
+      <c r="EG15" s="1">
         <f t="shared" si="80"/>
-        <v>539.28318014002934</v>
-      </c>
-      <c r="BV15" s="1">
+        <v>332.1390986566642</v>
+      </c>
+      <c r="EH15" s="1">
         <f t="shared" si="80"/>
-        <v>533.890348338629</v>
-      </c>
-      <c r="BW15" s="1">
+        <v>328.81770767009755</v>
+      </c>
+      <c r="EI15" s="1">
         <f t="shared" si="80"/>
-        <v>528.55144485524272</v>
-      </c>
-      <c r="BX15" s="1">
-        <f t="shared" si="80"/>
-        <v>523.26593040669025</v>
-      </c>
-      <c r="BY15" s="1">
-        <f t="shared" si="80"/>
-        <v>518.0332711026233</v>
-      </c>
-      <c r="BZ15" s="1">
-        <f t="shared" si="80"/>
-        <v>512.85293839159704</v>
-      </c>
-      <c r="CA15" s="1">
-        <f t="shared" si="80"/>
-        <v>507.72440900768106</v>
-      </c>
-      <c r="CB15" s="1">
-        <f t="shared" si="80"/>
-        <v>502.64716491760424</v>
-      </c>
-      <c r="CC15" s="1">
-        <f t="shared" si="80"/>
-        <v>497.62069326842817</v>
-      </c>
-      <c r="CD15" s="1">
-        <f t="shared" si="80"/>
-        <v>492.64448633574386</v>
-      </c>
-      <c r="CE15" s="1">
-        <f t="shared" si="80"/>
-        <v>487.7180414723864</v>
-      </c>
-      <c r="CF15" s="1">
-        <f t="shared" si="80"/>
-        <v>482.84086105766255</v>
-      </c>
-      <c r="CG15" s="1">
-        <f t="shared" si="80"/>
-        <v>478.01245244708593</v>
-      </c>
-      <c r="CH15" s="1">
-        <f t="shared" si="80"/>
-        <v>473.23232792261507</v>
-      </c>
-      <c r="CI15" s="1">
-        <f t="shared" si="80"/>
-        <v>468.50000464338893</v>
-      </c>
-      <c r="CJ15" s="1">
-        <f t="shared" si="80"/>
-        <v>463.81500459695502</v>
-      </c>
-      <c r="CK15" s="1">
-        <f t="shared" si="80"/>
-        <v>459.17685455098547</v>
-      </c>
-      <c r="CL15" s="1">
-        <f t="shared" si="80"/>
-        <v>454.5850860054756</v>
-      </c>
-      <c r="CM15" s="1">
-        <f t="shared" si="80"/>
-        <v>450.03923514542083</v>
-      </c>
-      <c r="CN15" s="1">
-        <f t="shared" si="80"/>
-        <v>445.53884279396664</v>
-      </c>
-      <c r="CO15" s="1">
-        <f t="shared" si="80"/>
-        <v>441.08345436602696</v>
-      </c>
-      <c r="CP15" s="1">
-        <f t="shared" si="80"/>
-        <v>436.6726198223667</v>
-      </c>
-      <c r="CQ15" s="1">
-        <f t="shared" si="80"/>
-        <v>432.30589362414304</v>
-      </c>
-      <c r="CR15" s="1">
-        <f t="shared" si="80"/>
-        <v>427.98283468790163</v>
-      </c>
-      <c r="CS15" s="1">
-        <f t="shared" si="80"/>
-        <v>423.70300634102261</v>
-      </c>
-      <c r="CT15" s="1">
-        <f t="shared" si="80"/>
-        <v>419.46597627761241</v>
-      </c>
-      <c r="CU15" s="1">
-        <f t="shared" si="80"/>
-        <v>415.27131651483626</v>
-      </c>
-      <c r="CV15" s="1">
-        <f t="shared" si="80"/>
-        <v>411.11860334968787</v>
-      </c>
-      <c r="CW15" s="1">
-        <f t="shared" si="80"/>
-        <v>407.00741731619098</v>
-      </c>
-      <c r="CX15" s="1">
-        <f t="shared" si="80"/>
-        <v>402.93734314302907</v>
-      </c>
-      <c r="CY15" s="1">
-        <f t="shared" si="80"/>
-        <v>398.90796971159875</v>
-      </c>
-      <c r="CZ15" s="1">
-        <f t="shared" si="80"/>
-        <v>394.91889001448277</v>
-      </c>
-      <c r="DA15" s="1">
-        <f t="shared" si="80"/>
-        <v>390.96970111433797</v>
-      </c>
-      <c r="DB15" s="1">
-        <f t="shared" ref="DB15:EI15" si="81">DA15*(1+$AR$21)</f>
-        <v>387.06000410319456</v>
-      </c>
-      <c r="DC15" s="1">
-        <f t="shared" si="81"/>
-        <v>383.18940406216262</v>
-      </c>
-      <c r="DD15" s="1">
-        <f t="shared" si="81"/>
-        <v>379.35751002154097</v>
-      </c>
-      <c r="DE15" s="1">
-        <f t="shared" si="81"/>
-        <v>375.56393492132554</v>
-      </c>
-      <c r="DF15" s="1">
-        <f t="shared" si="81"/>
-        <v>371.80829557211229</v>
-      </c>
-      <c r="DG15" s="1">
-        <f t="shared" si="81"/>
-        <v>368.09021261639117</v>
-      </c>
-      <c r="DH15" s="1">
-        <f t="shared" si="81"/>
-        <v>364.40931049022726</v>
-      </c>
-      <c r="DI15" s="1">
-        <f t="shared" si="81"/>
-        <v>360.765217385325</v>
-      </c>
-      <c r="DJ15" s="1">
-        <f t="shared" si="81"/>
-        <v>357.15756521147176</v>
-      </c>
-      <c r="DK15" s="1">
-        <f t="shared" si="81"/>
-        <v>353.58598955935702</v>
-      </c>
-      <c r="DL15" s="1">
-        <f t="shared" si="81"/>
-        <v>350.05012966376347</v>
-      </c>
-      <c r="DM15" s="1">
-        <f t="shared" si="81"/>
-        <v>346.54962836712582</v>
-      </c>
-      <c r="DN15" s="1">
-        <f t="shared" si="81"/>
-        <v>343.08413208345456</v>
-      </c>
-      <c r="DO15" s="1">
-        <f t="shared" si="81"/>
-        <v>339.65329076262003</v>
-      </c>
-      <c r="DP15" s="1">
-        <f t="shared" si="81"/>
-        <v>336.25675785499385</v>
-      </c>
-      <c r="DQ15" s="1">
-        <f t="shared" si="81"/>
-        <v>332.89419027644391</v>
-      </c>
-      <c r="DR15" s="1">
-        <f t="shared" si="81"/>
-        <v>329.56524837367948</v>
-      </c>
-      <c r="DS15" s="1">
-        <f t="shared" si="81"/>
-        <v>326.26959588994271</v>
-      </c>
-      <c r="DT15" s="1">
-        <f t="shared" si="81"/>
-        <v>323.00689993104328</v>
-      </c>
-      <c r="DU15" s="1">
-        <f t="shared" si="81"/>
-        <v>319.77683093173283</v>
-      </c>
-      <c r="DV15" s="1">
-        <f t="shared" si="81"/>
-        <v>316.57906262241551</v>
-      </c>
-      <c r="DW15" s="1">
-        <f t="shared" si="81"/>
-        <v>313.41327199619133</v>
-      </c>
-      <c r="DX15" s="1">
-        <f t="shared" si="81"/>
-        <v>310.27913927622939</v>
-      </c>
-      <c r="DY15" s="1">
-        <f t="shared" si="81"/>
-        <v>307.17634788346709</v>
-      </c>
-      <c r="DZ15" s="1">
-        <f t="shared" si="81"/>
-        <v>304.10458440463242</v>
-      </c>
-      <c r="EA15" s="1">
-        <f t="shared" si="81"/>
-        <v>301.0635385605861</v>
-      </c>
-      <c r="EB15" s="1">
-        <f t="shared" si="81"/>
-        <v>298.05290317498026</v>
-      </c>
-      <c r="EC15" s="1">
-        <f t="shared" si="81"/>
-        <v>295.07237414323043</v>
-      </c>
-      <c r="ED15" s="1">
-        <f t="shared" si="81"/>
-        <v>292.12165040179815</v>
-      </c>
-      <c r="EE15" s="1">
-        <f t="shared" si="81"/>
-        <v>289.20043389778016</v>
-      </c>
-      <c r="EF15" s="1">
-        <f t="shared" si="81"/>
-        <v>286.30842955880235</v>
-      </c>
-      <c r="EG15" s="1">
-        <f t="shared" si="81"/>
-        <v>283.44534526321434</v>
-      </c>
-      <c r="EH15" s="1">
-        <f t="shared" si="81"/>
-        <v>280.61089181058219</v>
-      </c>
-      <c r="EI15" s="1">
-        <f t="shared" si="81"/>
-        <v>277.80478289247634</v>
+        <v>325.52953059339654</v>
       </c>
     </row>
     <row r="16" spans="2:139" x14ac:dyDescent="0.3">
@@ -3319,16 +3311,13 @@
         <v>45.5</v>
       </c>
       <c r="T16" s="5">
-        <f>39.3+6.2</f>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="U16" s="5">
-        <f>39.3+6.2</f>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="V16" s="5">
-        <f>39.3+6.2</f>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="X16" s="5">
         <v>44.9</v>
@@ -3349,48 +3338,37 @@
         <v>44.9</v>
       </c>
       <c r="AD16" s="5">
-        <f t="shared" ref="AD16:AN16" si="82">39.3+6.2</f>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="AE16" s="5">
-        <f t="shared" si="82"/>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="AF16" s="5">
-        <f t="shared" si="82"/>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="AG16" s="5">
-        <f t="shared" si="82"/>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="AH16" s="5">
-        <f t="shared" si="82"/>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="AI16" s="5">
-        <f t="shared" si="82"/>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="AJ16" s="5">
-        <f t="shared" si="82"/>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="AK16" s="5">
-        <f t="shared" si="82"/>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="AL16" s="5">
-        <f t="shared" si="82"/>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="AM16" s="5">
-        <f t="shared" si="82"/>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="AN16" s="5">
-        <f t="shared" si="82"/>
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="17" spans="2:44" x14ac:dyDescent="0.3">
@@ -3398,152 +3376,152 @@
         <v>23</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:R17" si="83">C15/C16</f>
+        <f t="shared" ref="C17:R17" si="81">C15/C16</f>
         <v>-0.29844097995545654</v>
       </c>
       <c r="D17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-2.2271714922050267E-3</v>
       </c>
       <c r="E17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-0.64587973273942101</v>
       </c>
       <c r="F17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-0.38975501113585764</v>
       </c>
       <c r="G17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-0.27171492204899761</v>
       </c>
       <c r="H17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-0.33630289532293978</v>
       </c>
       <c r="I17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-0.40979955456570177</v>
       </c>
       <c r="J17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-0.30957683741648112</v>
       </c>
       <c r="K17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>-5.5679287305122331E-2</v>
       </c>
       <c r="L17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>8.2405345211581355E-2</v>
       </c>
       <c r="M17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>6.236080178173712E-2</v>
       </c>
       <c r="N17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0.27171492204899772</v>
       </c>
       <c r="O17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0.60133630289532269</v>
       </c>
       <c r="P17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0.5412026726057908</v>
       </c>
       <c r="Q17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0.51893095768374098</v>
       </c>
       <c r="R17" s="7">
-        <f t="shared" si="83"/>
+        <f t="shared" si="81"/>
         <v>0.3140311804008909</v>
       </c>
       <c r="S17" s="7">
-        <f t="shared" ref="S17" si="84">S15/S16</f>
+        <f t="shared" ref="S17" si="82">S15/S16</f>
         <v>0.76923076923076861</v>
       </c>
       <c r="T17" s="7">
-        <f t="shared" ref="T17" si="85">T15/T16</f>
-        <v>0.65250109890109864</v>
+        <f t="shared" ref="T17" si="83">T15/T16</f>
+        <v>0.97598253275109204</v>
       </c>
       <c r="U17" s="7">
-        <f t="shared" ref="U17" si="86">U15/U16</f>
-        <v>0.64385912087912134</v>
+        <f t="shared" ref="U17" si="84">U15/U16</f>
+        <v>0.87555567685589464</v>
       </c>
       <c r="V17" s="7">
-        <f t="shared" ref="V17" si="87">V15/V16</f>
-        <v>0.68205120879120873</v>
+        <f t="shared" ref="V17" si="85">V15/V16</f>
+        <v>0.84096179039301311</v>
       </c>
       <c r="X17" s="7">
-        <f t="shared" ref="X17:AE17" si="88">X15/X16</f>
+        <f t="shared" ref="X17:AE17" si="86">X15/X16</f>
         <v>-0.2739420935412028</v>
       </c>
       <c r="Y17" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>-0.35189309576837413</v>
       </c>
       <c r="Z17" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>-1.3363028953229408</v>
       </c>
       <c r="AA17" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>-1.3273942093541193</v>
       </c>
       <c r="AB17" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>0.36080178173719457</v>
       </c>
       <c r="AC17" s="7">
-        <f t="shared" si="88"/>
+        <f t="shared" si="86"/>
         <v>1.9755011135857456</v>
       </c>
       <c r="AD17" s="7">
-        <f t="shared" si="88"/>
-        <v>2.747642197802199</v>
+        <f t="shared" si="86"/>
+        <v>3.4566921397379882</v>
       </c>
       <c r="AE17" s="7">
-        <f t="shared" si="88"/>
-        <v>4.0649874587912098</v>
+        <f t="shared" si="86"/>
+        <v>5.1176946615720542</v>
       </c>
       <c r="AF17" s="7">
-        <f t="shared" ref="AF17" si="89">AF15/AF16</f>
-        <v>5.9394509208791204</v>
+        <f t="shared" ref="AF17" si="87">AF15/AF16</f>
+        <v>7.5120784005458479</v>
       </c>
       <c r="AG17" s="7">
-        <f t="shared" ref="AG17" si="90">AG15/AG16</f>
-        <v>7.7852356306813144</v>
+        <f t="shared" ref="AG17" si="88">AG15/AG16</f>
+        <v>9.5821607513810019</v>
       </c>
       <c r="AH17" s="7">
-        <f t="shared" ref="AH17" si="91">AH15/AH16</f>
-        <v>9.2904352811475786</v>
+        <f t="shared" ref="AH17" si="89">AH15/AH16</f>
+        <v>11.259194995282691</v>
       </c>
       <c r="AI17" s="7">
-        <f t="shared" ref="AI17" si="92">AI15/AI16</f>
-        <v>10.674365370478984</v>
+        <f t="shared" ref="AI17" si="90">AI15/AI16</f>
+        <v>12.794472578848241</v>
       </c>
       <c r="AJ17" s="7">
-        <f t="shared" ref="AJ17" si="93">AJ15/AJ16</f>
-        <v>11.856525301572237</v>
+        <f t="shared" ref="AJ17" si="91">AJ15/AJ16</f>
+        <v>14.099597513825632</v>
       </c>
       <c r="AK17" s="7">
-        <f t="shared" ref="AK17" si="94">AK15/AK16</f>
-        <v>12.926351293205428</v>
+        <f t="shared" ref="AK17" si="92">AK15/AK16</f>
+        <v>15.277849769363467</v>
       </c>
       <c r="AL17" s="7">
-        <f t="shared" ref="AL17" si="95">AL15/AL16</f>
-        <v>14.057015570726829</v>
+        <f t="shared" ref="AL17" si="93">AL15/AL16</f>
+        <v>16.522325111614993</v>
       </c>
       <c r="AM17" s="7">
-        <f t="shared" ref="AM17" si="96">AM15/AM16</f>
-        <v>15.25168505807474</v>
+        <f t="shared" ref="AM17" si="94">AM15/AM16</f>
+        <v>17.836459354658039</v>
       </c>
       <c r="AN17" s="7">
-        <f t="shared" ref="AN17" si="97">AN15/AN16</f>
-        <v>16.51368730627642</v>
+        <f t="shared" ref="AN17" si="95">AN15/AN16</f>
+        <v>19.223862380971788</v>
       </c>
     </row>
     <row r="19" spans="2:44" x14ac:dyDescent="0.3">
@@ -3555,47 +3533,47 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9">
-        <f t="shared" ref="G19:Q19" si="98">G3/C3-1</f>
+        <f t="shared" ref="G19:Q19" si="96">G3/C3-1</f>
         <v>0.46570397111913375</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>0.5034013605442178</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>0.51100628930817593</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>0.42191780821917813</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>0.42487684729064035</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>0.434389140271493</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>0.43184183142559829</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>0.4547206165703277</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>0.44857389801210013</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>0.40615141955835976</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" si="98"/>
+        <f t="shared" si="96"/>
         <v>0.39970930232558133</v>
       </c>
       <c r="R19" s="9">
@@ -3603,36 +3581,36 @@
         <v>0.38807947019867539</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19:V19" si="99">S3/O3-1</f>
+        <f t="shared" ref="S19:V19" si="97">S3/O3-1</f>
         <v>0.37649164677804303</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="99"/>
-        <v>0.35000000000000009</v>
+        <f t="shared" si="97"/>
+        <v>0.41503084688726855</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" si="99"/>
-        <v>0.29000000000000004</v>
+        <f t="shared" si="97"/>
+        <v>0.39999999999999991</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="99"/>
-        <v>0.28000000000000003</v>
+        <f t="shared" si="97"/>
+        <v>0.35000000000000031</v>
       </c>
       <c r="X19" s="9"/>
       <c r="Y19" s="9">
-        <f t="shared" ref="Y19" si="100">Y3/X3-1</f>
+        <f t="shared" ref="Y19" si="98">Y3/X3-1</f>
         <v>1.2838983050847457</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" ref="Z19:AB19" si="101">Z3/Y3-1</f>
+        <f t="shared" ref="Z19:AB19" si="99">Z3/Y3-1</f>
         <v>0.55102040816326525</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.47328548644338153</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.43734776725304458</v>
       </c>
       <c r="AC19" s="9">
@@ -3640,47 +3618,47 @@
         <v>0.40858595368103923</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" ref="AD19:AN19" si="102">AD3/AC3-1</f>
-        <v>0.32087555139687218</v>
+        <f t="shared" ref="AD19:AN19" si="100">AD3/AC3-1</f>
+        <v>0.3843069108407966</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="102"/>
-        <v>0.25</v>
+        <f t="shared" si="100"/>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" si="102"/>
-        <v>0.19999999999999996</v>
+        <f t="shared" si="100"/>
+        <v>0.21999999999999997</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI19" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AJ19" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AK19" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM19" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" si="102"/>
+        <f t="shared" si="100"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -3689,63 +3667,63 @@
         <v>46</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:Q20" si="103">C5/C3</f>
+        <f t="shared" ref="C20:Q20" si="101">C5/C3</f>
         <v>0.72924187725631773</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.72619047619047616</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.71540880503144655</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.72602739726027399</v>
       </c>
       <c r="G20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.73522167487684731</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.72963800904977372</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.72632674297606659</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.73217726396917149</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.72774416594641311</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.7334384858044164</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.73619186046511631</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.73112582781456958</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.73031026252983289</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.73471676948962417</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" si="103"/>
+        <f t="shared" si="101"/>
         <v>0.72897196261682229</v>
       </c>
       <c r="R20" s="9">
@@ -3753,39 +3731,39 @@
         <v>0.71898854961832059</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" ref="S20:V20" si="104">S5/S3</f>
+        <f t="shared" ref="S20:V20" si="102">S5/S3</f>
         <v>0.71131339401820548</v>
       </c>
       <c r="T20" s="9">
+        <f t="shared" si="102"/>
+        <v>0.72374157748711854</v>
+      </c>
+      <c r="U20" s="9">
+        <f t="shared" si="102"/>
+        <v>0.71</v>
+      </c>
+      <c r="V20" s="9">
+        <f t="shared" si="102"/>
+        <v>0.71</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" ref="X20:Y20" si="103">X5/X3</f>
+        <v>0.7076271186440678</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" si="103"/>
+        <v>0.71552257266542973</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" ref="Z20:AB20" si="104">Z5/Z3</f>
+        <v>0.72408293460925033</v>
+      </c>
+      <c r="AA20" s="9">
         <f t="shared" si="104"/>
-        <v>0.71</v>
-      </c>
-      <c r="U20" s="9">
+        <v>0.73071718538565633</v>
+      </c>
+      <c r="AB20" s="9">
         <f t="shared" si="104"/>
-        <v>0.71</v>
-      </c>
-      <c r="V20" s="9">
-        <f t="shared" si="104"/>
-        <v>0.71</v>
-      </c>
-      <c r="X20" s="9">
-        <f t="shared" ref="X20:Y20" si="105">X5/X3</f>
-        <v>0.7076271186440678</v>
-      </c>
-      <c r="Y20" s="9">
-        <f t="shared" si="105"/>
-        <v>0.71552257266542973</v>
-      </c>
-      <c r="Z20" s="9">
-        <f t="shared" ref="Z20:AB20" si="106">Z5/Z3</f>
-        <v>0.72408293460925033</v>
-      </c>
-      <c r="AA20" s="9">
-        <f t="shared" si="106"/>
-        <v>0.73071718538565633</v>
-      </c>
-      <c r="AB20" s="9">
-        <f t="shared" si="106"/>
         <v>0.73225381284127289</v>
       </c>
       <c r="AC20" s="9">
@@ -3793,47 +3771,47 @@
         <v>0.72784387114022187</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20:AN20" si="107">AD5/AD3</f>
-        <v>0.71030663453919307</v>
+        <f t="shared" ref="AD20:AN20" si="105">AD5/AD3</f>
+        <v>0.71364040169949772</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="105"/>
         <v>0.71</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="105"/>
         <v>0.71</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="105"/>
+        <v>0.71000000000000008</v>
+      </c>
+      <c r="AH20" s="9">
+        <f t="shared" si="105"/>
         <v>0.71</v>
       </c>
-      <c r="AH20" s="9">
-        <f t="shared" si="107"/>
+      <c r="AI20" s="9">
+        <f t="shared" si="105"/>
         <v>0.71</v>
       </c>
-      <c r="AI20" s="9">
-        <f t="shared" si="107"/>
+      <c r="AJ20" s="9">
+        <f t="shared" si="105"/>
         <v>0.71</v>
       </c>
-      <c r="AJ20" s="9">
-        <f t="shared" si="107"/>
+      <c r="AK20" s="9">
+        <f t="shared" si="105"/>
         <v>0.71</v>
       </c>
-      <c r="AK20" s="9">
-        <f t="shared" si="107"/>
+      <c r="AL20" s="9">
+        <f t="shared" si="105"/>
         <v>0.71</v>
       </c>
-      <c r="AL20" s="9">
-        <f t="shared" si="107"/>
+      <c r="AM20" s="9">
+        <f t="shared" si="105"/>
         <v>0.71</v>
       </c>
-      <c r="AM20" s="9">
-        <f t="shared" si="107"/>
-        <v>0.71</v>
-      </c>
       <c r="AN20" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="105"/>
         <v>0.71</v>
       </c>
     </row>
@@ -3846,47 +3824,47 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9">
-        <f t="shared" ref="G21:Q21" si="108">G6/C6-1</f>
+        <f t="shared" ref="G21:Q21" si="106">G6/C6-1</f>
         <v>0.32444444444444454</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>0.5616438356164386</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>0.43344709897610922</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>0.48333333333333339</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>0.53691275167785224</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>0.40058479532163727</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>0.19761904761904758</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>0.13033707865168531</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>0.11135371179039311</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>0.1503131524008352</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="108"/>
+        <f t="shared" si="106"/>
         <v>0.25049701789264422</v>
       </c>
       <c r="R21" s="9">
@@ -3894,36 +3872,36 @@
         <v>0.32007952286282326</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21:V21" si="109">S6/O6-1</f>
+        <f t="shared" ref="S21:V21" si="107">S6/O6-1</f>
         <v>0.38310412573673891</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="109"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="107"/>
+        <v>0.33756805807622503</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>0.22999999999999998</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>0.21999999999999997</v>
       </c>
       <c r="X21" s="9"/>
       <c r="Y21" s="9">
-        <f t="shared" ref="Y21" si="110">Y6/X6-1</f>
+        <f t="shared" ref="Y21" si="108">Y6/X6-1</f>
         <v>0.67721518987341756</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" ref="Z21:AB21" si="111">Z6/Y6-1</f>
+        <f t="shared" ref="Z21:AB21" si="109">Z6/Y6-1</f>
         <v>0.95660377358490578</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.45130183220829312</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.29102990033222609</v>
       </c>
       <c r="AC21" s="9">
@@ -3931,47 +3909,47 @@
         <v>0.211013896037056</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" ref="AD21:AN21" si="112">AD6/AC6-1</f>
-        <v>0.27668933276668084</v>
+        <f t="shared" ref="AD21:AN21" si="110">AD6/AC6-1</f>
+        <v>0.28548661283467913</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>0.17999999999999994</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>0.12000000000000011</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN21" s="9">
-        <f t="shared" si="112"/>
+        <f t="shared" si="110"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AQ21" t="s">
@@ -3986,63 +3964,63 @@
         <v>48</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:Q22" si="113">C7/C3</f>
+        <f t="shared" ref="C22:Q22" si="111">C7/C3</f>
         <v>0.35740072202166068</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.16326530612244899</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.24056603773584906</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.19863013698630136</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.18349753694581281</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.17307692307692307</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.18418314255983351</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.18304431599229287</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.14347450302506484</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.13958990536277602</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.1620639534883721</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.12649006622516556</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.11873508353221957</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.11329220415030845</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="113"/>
+        <f t="shared" si="111"/>
         <v>0.13291796469366565</v>
       </c>
       <c r="R22" s="9">
@@ -4050,39 +4028,39 @@
         <v>0.1183206106870229</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22:V22" si="114">S7/S3</f>
+        <f t="shared" ref="S22:V22" si="112">S7/S3</f>
         <v>0.11573472041612484</v>
       </c>
       <c r="T22" s="9">
+        <f t="shared" si="112"/>
+        <v>0.11732065001981767</v>
+      </c>
+      <c r="U22" s="9">
+        <f t="shared" si="112"/>
+        <v>0.11</v>
+      </c>
+      <c r="V22" s="9">
+        <f t="shared" si="112"/>
+        <v>0.11</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" ref="X22:Y22" si="113">X7/X3</f>
+        <v>0.21186440677966104</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" si="113"/>
+        <v>0.21645021645021648</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" ref="Z22:AB22" si="114">Z7/Z3</f>
+        <v>0.2360446570972887</v>
+      </c>
+      <c r="AA22" s="9">
         <f t="shared" si="114"/>
-        <v>0.11</v>
-      </c>
-      <c r="U22" s="9">
+        <v>0.18105548037889038</v>
+      </c>
+      <c r="AB22" s="9">
         <f t="shared" si="114"/>
-        <v>0.11</v>
-      </c>
-      <c r="V22" s="9">
-        <f t="shared" si="114"/>
-        <v>0.11</v>
-      </c>
-      <c r="X22" s="9">
-        <f t="shared" ref="X22:Y22" si="115">X7/X3</f>
-        <v>0.21186440677966104</v>
-      </c>
-      <c r="Y22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.21645021645021648</v>
-      </c>
-      <c r="Z22" s="9">
-        <f t="shared" ref="Z22:AB22" si="116">Z7/Z3</f>
-        <v>0.2360446570972887</v>
-      </c>
-      <c r="AA22" s="9">
-        <f t="shared" si="116"/>
-        <v>0.18105548037889038</v>
-      </c>
-      <c r="AB22" s="9">
-        <f t="shared" si="116"/>
         <v>0.14253436264356992</v>
       </c>
       <c r="AC22" s="9">
@@ -4090,47 +4068,47 @@
         <v>0.12097313193423337</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22:AN22" si="117">AD7/AD3</f>
-        <v>0.11133886962162512</v>
+        <f t="shared" ref="AD22:AN22" si="115">AD7/AD3</f>
+        <v>0.11306102742371572</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>0.1</v>
       </c>
       <c r="AF22" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>0.09</v>
       </c>
       <c r="AG22" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>0.09</v>
       </c>
       <c r="AH22" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>0.09</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>0.09</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>0.09</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>0.09</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>0.09</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>0.09</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>0.09</v>
       </c>
       <c r="AQ22" t="s">
@@ -4149,47 +4127,47 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9">
-        <f t="shared" ref="G23:Q23" si="118">G8/C8-1</f>
+        <f t="shared" ref="G23:Q23" si="116">G8/C8-1</f>
         <v>1.3391304347826085</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>1.5948275862068968</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>2.0270270270270174E-2</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>0.1853281853281854</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>0.12267657992565062</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>6.976744186046524E-2</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>0.10596026490066213</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>0.1791530944625408</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>0.16225165562913912</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>0.1490683229813663</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="118"/>
+        <f t="shared" si="116"/>
         <v>0.14970059880239517</v>
       </c>
       <c r="R23" s="9">
@@ -4197,36 +4175,36 @@
         <v>0.25690607734806625</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23:V23" si="119">S8/O8-1</f>
+        <f t="shared" ref="S23:V23" si="117">S8/O8-1</f>
         <v>0.23931623931623935</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="119"/>
-        <v>0.30000000000000004</v>
+        <f t="shared" si="117"/>
+        <v>0.2432432432432432</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="117"/>
         <v>0.25</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="117"/>
         <v>0.17999999999999994</v>
       </c>
       <c r="X23" s="9"/>
       <c r="Y23" s="9">
-        <f t="shared" ref="Y23" si="120">Y8/X8-1</f>
+        <f t="shared" ref="Y23" si="118">Y8/X8-1</f>
         <v>1.6646341463414638</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" ref="Z23:AB23" si="121">Z8/Y8-1</f>
+        <f t="shared" ref="Z23:AB23" si="119">Z8/Y8-1</f>
         <v>0.79862700228832928</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>0.50000000000000022</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>0.11959287531806617</v>
       </c>
       <c r="AC23" s="9">
@@ -4234,47 +4212,47 @@
         <v>0.18181818181818188</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" ref="AD23:AN23" si="122">AD8/AC8-1</f>
-        <v>0.23903846153846153</v>
+        <f t="shared" ref="AD23:AN23" si="120">AD8/AC8-1</f>
+        <v>0.22557692307692312</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>0.16999999999999993</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>0.1100000000000001</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>7.0000000000000062E-2</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="122"/>
+        <f t="shared" si="120"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ23" t="s">
@@ -4282,7 +4260,7 @@
       </c>
       <c r="AR23" s="5">
         <f>NPV(AR22,AD15:EI15)</f>
-        <v>6483.2739757309128</v>
+        <v>7705.8198992622183</v>
       </c>
     </row>
     <row r="24" spans="2:44" x14ac:dyDescent="0.3">
@@ -4290,63 +4268,63 @@
         <v>50</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:Q24" si="123">C10/C3</f>
+        <f t="shared" ref="C24:Q24" si="121">C10/C3</f>
         <v>-0.2418772563176895</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>-6.802721088435471E-3</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>-0.45125786163522014</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>-0.23835616438356172</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>-0.14655172413793091</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>-0.17081447963800897</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>-0.20915712799167543</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>-0.17533718689788058</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>-7.2601555747623087E-2</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>-3.7854889589905343E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>-3.4156976744186066E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>3.1788079470198655E-2</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>9.8448687350835243E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>0.10487941671340438</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="123"/>
+        <f t="shared" si="121"/>
         <v>7.0093457943925089E-2</v>
       </c>
       <c r="R24" s="9">
@@ -4354,39 +4332,39 @@
         <v>6.6793893129770993E-2</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24:V24" si="124">S10/S3</f>
+        <f t="shared" ref="S24:V24" si="122">S10/S3</f>
         <v>0.10186389250108353</v>
       </c>
       <c r="T24" s="9">
+        <f t="shared" si="122"/>
+        <v>0.13198573127229493</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" si="122"/>
+        <v>0.13505785491766792</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" si="122"/>
+        <v>0.12396805202148713</v>
+      </c>
+      <c r="X24" s="9">
+        <f t="shared" ref="X24:Y24" si="123">X10/X3</f>
+        <v>-0.18220338983050857</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" si="123"/>
+        <v>-9.894867037724181E-2</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" ref="Z24:AB24" si="124">Z10/Z3</f>
+        <v>-0.2388357256778311</v>
+      </c>
+      <c r="AA24" s="9">
         <f t="shared" si="124"/>
-        <v>0.10258615317504821</v>
-      </c>
-      <c r="U24" s="9">
+        <v>-0.17672530446549375</v>
+      </c>
+      <c r="AB24" s="9">
         <f t="shared" si="124"/>
-        <v>9.5411625492042892E-2</v>
-      </c>
-      <c r="V24" s="9">
-        <f t="shared" si="124"/>
-        <v>9.7935054866412199E-2</v>
-      </c>
-      <c r="X24" s="9">
-        <f t="shared" ref="X24:Y24" si="125">X10/X3</f>
-        <v>-0.18220338983050857</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" si="125"/>
-        <v>-9.894867037724181E-2</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" ref="Z24:AB24" si="126">Z10/Z3</f>
-        <v>-0.2388357256778311</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" si="126"/>
-        <v>-0.17672530446549375</v>
-      </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="126"/>
         <v>-2.4665787987196319E-2</v>
       </c>
       <c r="AC24" s="9">
@@ -4394,55 +4372,55 @@
         <v>8.381232455554069E-2</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" ref="AD24:AN24" si="127">AD10/AD3</f>
-        <v>9.9350805092764602E-2</v>
+        <f t="shared" ref="AD24:AN24" si="125">AD10/AD3</f>
+        <v>0.12388470451911922</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="127"/>
-        <v>0.13992645831035264</v>
+        <f t="shared" si="125"/>
+        <v>0.17198942641946702</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="127"/>
-        <v>0.18279044109833861</v>
+        <f t="shared" si="125"/>
+        <v>0.21927514586756541</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="127"/>
-        <v>0.21553416413444196</v>
+        <f t="shared" si="125"/>
+        <v>0.24930111976248018</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="127"/>
-        <v>0.23759593699983605</v>
+        <f t="shared" si="125"/>
+        <v>0.26952105868452664</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="127"/>
-        <v>0.25529982880539914</v>
+        <f t="shared" si="125"/>
+        <v>0.28574693559728009</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="127"/>
-        <v>0.26906209941651621</v>
+        <f t="shared" si="125"/>
+        <v>0.29836025878228839</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="127"/>
-        <v>0.28039101498596242</v>
+        <f t="shared" si="125"/>
+        <v>0.30873044188571208</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="127"/>
-        <v>0.29134664274257049</v>
+        <f t="shared" si="125"/>
+        <v>0.31875936352098116</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="127"/>
-        <v>0.30194153774807297</v>
+        <f t="shared" si="125"/>
+        <v>0.32845848717851317</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="127"/>
-        <v>0.31218782435974735</v>
+        <f t="shared" si="125"/>
+        <v>0.33783888355708486</v>
       </c>
       <c r="AQ24" t="s">
         <v>70</v>
       </c>
       <c r="AR24" s="5">
         <f>Main!D8</f>
-        <v>1082.5999999999999</v>
+        <v>1097.9000000000001</v>
       </c>
     </row>
     <row r="25" spans="2:44" x14ac:dyDescent="0.3">
@@ -4450,63 +4428,63 @@
         <v>21</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:Q25" si="128">C14/C13</f>
+        <f t="shared" ref="C25:Q25" si="126">C14/C13</f>
         <v>0</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>-3.4602076124567475E-3</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>-5.7471264367816074E-3</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>-6.6666666666666697E-3</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>-5.4644808743169382E-3</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>-5.3030303030303018E-2</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>3.8461538461538575E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>-0.54166666666666596</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>3.4482758620689696E-2</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>0.19736842105263161</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>-4.2471042471042497E-2</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>0.15331010452961671</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="128"/>
+        <f t="shared" si="126"/>
         <v>7.9051383399209585E-2</v>
       </c>
       <c r="R25" s="9">
@@ -4514,39 +4492,39 @@
         <v>0.37333333333333335</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:V25" si="129">S14/S13</f>
+        <f t="shared" ref="S25:V25" si="127">S14/S13</f>
         <v>-2.8653295128939853E-3</v>
       </c>
       <c r="T25" s="9">
+        <f t="shared" si="127"/>
+        <v>3.6637931034482749E-2</v>
+      </c>
+      <c r="U25" s="9">
+        <f t="shared" si="127"/>
+        <v>0.15</v>
+      </c>
+      <c r="V25" s="9">
+        <f t="shared" si="127"/>
+        <v>0.15</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" ref="X25:Y25" si="128">X14/X13</f>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="128"/>
+        <v>-6.369426751592357E-3</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" ref="Z25:AB25" si="129">Z14/Z13</f>
+        <v>-3.3444816053511688E-3</v>
+      </c>
+      <c r="AA25" s="9">
         <f t="shared" si="129"/>
-        <v>0.15</v>
-      </c>
-      <c r="U25" s="9">
+        <v>-1.5332197614991491E-2</v>
+      </c>
+      <c r="AB25" s="9">
         <f t="shared" si="129"/>
-        <v>0.15</v>
-      </c>
-      <c r="V25" s="9">
-        <f t="shared" si="129"/>
-        <v>0.15</v>
-      </c>
-      <c r="X25" s="9">
-        <f t="shared" ref="X25:Y25" si="130">X14/X13</f>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="130"/>
-        <v>-6.369426751592357E-3</v>
-      </c>
-      <c r="Z25" s="9">
-        <f t="shared" ref="Z25:AB25" si="131">Z14/Z13</f>
-        <v>-3.3444816053511688E-3</v>
-      </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="131"/>
-        <v>-1.5332197614991491E-2</v>
-      </c>
-      <c r="AB25" s="9">
-        <f t="shared" si="131"/>
         <v>9.4972067039105962E-2</v>
       </c>
       <c r="AC25" s="9">
@@ -4554,47 +4532,47 @@
         <v>0.13378906250000003</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" ref="AD25:AN25" si="132">AD14/AD13</f>
-        <v>0.11211023613099698</v>
+        <f t="shared" ref="AD25:AN25" si="130">AD14/AD13</f>
+        <v>8.9035617699522451E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.15</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.15</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.15</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.15</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.15</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.15</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.15</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.15</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.15</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="132"/>
+        <f t="shared" si="130"/>
         <v>0.15</v>
       </c>
       <c r="AQ25" t="s">
@@ -4602,7 +4580,7 @@
       </c>
       <c r="AR25" s="5">
         <f>AR23+AR24</f>
-        <v>7565.8739757309122</v>
+        <v>8803.719899262218</v>
       </c>
     </row>
     <row r="26" spans="2:44" x14ac:dyDescent="0.3">
@@ -4610,63 +4588,63 @@
         <v>51</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:Q26" si="133">C15/C3</f>
+        <f t="shared" ref="C26:Q26" si="131">C15/C3</f>
         <v>-0.2418772563176895</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>-1.7006802721089404E-3</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>-0.45597484276729566</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>-0.23972602739726037</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>-0.15024630541871911</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>-0.17081447963800897</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>-0.19146722164412081</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>-0.13391136801541428</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>-2.1607605877268732E-2</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>2.9179810725552074E-2</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>2.0348837209302303E-2</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>8.0794701986754952E-2</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>0.16109785202863955</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>0.13628715647784634</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="133"/>
+        <f t="shared" si="131"/>
         <v>0.12097611630321894</v>
       </c>
       <c r="R26" s="9">
@@ -4674,39 +4652,39 @@
         <v>6.7270992366412208E-2</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" ref="S26:V26" si="134">S15/S3</f>
+        <f t="shared" ref="S26:V26" si="132">S15/S3</f>
         <v>0.15171218032076278</v>
       </c>
       <c r="T26" s="9">
+        <f t="shared" si="132"/>
+        <v>0.1771700356718193</v>
+      </c>
+      <c r="U26" s="9">
+        <f t="shared" si="132"/>
+        <v>0.14871847648716799</v>
+      </c>
+      <c r="V26" s="9">
+        <f t="shared" si="132"/>
+        <v>0.1361183559513712</v>
+      </c>
+      <c r="X26" s="9">
+        <f t="shared" ref="X26:Y26" si="133">X15/X3</f>
+        <v>-0.17372881355932213</v>
+      </c>
+      <c r="Y26" s="9">
+        <f t="shared" si="133"/>
+        <v>-9.7711811997526279E-2</v>
+      </c>
+      <c r="Z26" s="9">
+        <f t="shared" ref="Z26:AB26" si="134">Z15/Z3</f>
+        <v>-0.23923444976076572</v>
+      </c>
+      <c r="AA26" s="9">
         <f t="shared" si="134"/>
-        <v>0.1233410190897571</v>
-      </c>
-      <c r="U26" s="9">
+        <v>-0.16129905277401882</v>
+      </c>
+      <c r="AB26" s="9">
         <f t="shared" si="134"/>
-        <v>0.11791152486979488</v>
-      </c>
-      <c r="V26" s="9">
-        <f t="shared" si="134"/>
-        <v>0.11567170354246183</v>
-      </c>
-      <c r="X26" s="9">
-        <f t="shared" ref="X26:Y26" si="135">X15/X3</f>
-        <v>-0.17372881355932213</v>
-      </c>
-      <c r="Y26" s="9">
-        <f t="shared" si="135"/>
-        <v>-9.7711811997526279E-2</v>
-      </c>
-      <c r="Z26" s="9">
-        <f t="shared" ref="Z26:AB26" si="136">Z15/Z3</f>
-        <v>-0.23923444976076572</v>
-      </c>
-      <c r="AA26" s="9">
-        <f t="shared" si="136"/>
-        <v>-0.16129905277401882</v>
-      </c>
-      <c r="AB26" s="9">
-        <f t="shared" si="136"/>
         <v>3.0502730182639867E-2</v>
       </c>
       <c r="AC26" s="9">
@@ -4714,55 +4692,55 @@
         <v>0.1185670364924475</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" ref="AD26:AN26" si="137">AD15/AD3</f>
-        <v>0.12651732991144035</v>
+        <f t="shared" ref="AD26:AN26" si="135">AD15/AD3</f>
+        <v>0.15287417921977584</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="137"/>
-        <v>0.14974041665865506</v>
+        <f t="shared" si="135"/>
+        <v>0.17682262660233203</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="137"/>
-        <v>0.18232443614158619</v>
+        <f t="shared" si="135"/>
+        <v>0.21274714845716361</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="137"/>
-        <v>0.20781289974766551</v>
+        <f t="shared" si="135"/>
+        <v>0.23597676761829922</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="137"/>
-        <v>0.22544682212718731</v>
+        <f t="shared" si="135"/>
+        <v>0.25206958771021182</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="137"/>
-        <v>0.23984262250421243</v>
+        <f t="shared" si="135"/>
+        <v>0.26522334175748657</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="137"/>
-        <v>0.25132510188196738</v>
+        <f t="shared" si="135"/>
+        <v>0.27573392640342476</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="137"/>
-        <v>0.26095468011599671</v>
+        <f t="shared" si="135"/>
+        <v>0.28454858204133493</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="137"/>
-        <v>0.27026696370911357</v>
+        <f t="shared" si="135"/>
+        <v>0.29307316543131362</v>
       </c>
       <c r="AM26" s="9">
-        <f t="shared" si="137"/>
-        <v>0.27927262446379064</v>
+        <f t="shared" si="135"/>
+        <v>0.30131742054021582</v>
       </c>
       <c r="AN26" s="9">
-        <f t="shared" si="137"/>
-        <v>0.28798196808371385</v>
+        <f t="shared" si="135"/>
+        <v>0.3092907574620018</v>
       </c>
       <c r="AQ26" t="s">
         <v>72</v>
       </c>
       <c r="AR26" s="4">
         <f>AR25/AN16</f>
-        <v>166.28294452155851</v>
+        <v>192.22095849917508</v>
       </c>
     </row>
     <row r="27" spans="2:44" x14ac:dyDescent="0.3">
@@ -4771,7 +4749,7 @@
       </c>
       <c r="AR27" s="4">
         <f>Main!D3</f>
-        <v>528.66999999999996</v>
+        <v>278.74</v>
       </c>
     </row>
     <row r="28" spans="2:44" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4791,67 +4769,67 @@
         <v>-60.000000000000036</v>
       </c>
       <c r="AA28" s="8">
-        <f t="shared" ref="AA28:AN28" si="138">AA15</f>
+        <f t="shared" ref="AA28:AN28" si="136">AA15</f>
         <v>-59.599999999999959</v>
       </c>
       <c r="AB28" s="8">
-        <f t="shared" si="138"/>
+        <f t="shared" si="136"/>
         <v>16.200000000000035</v>
       </c>
       <c r="AC28" s="8">
-        <f t="shared" si="138"/>
+        <f t="shared" si="136"/>
         <v>88.699999999999974</v>
       </c>
       <c r="AD28" s="8">
-        <f t="shared" si="138"/>
-        <v>125.01772000000005</v>
+        <f t="shared" si="136"/>
+        <v>158.31649999999985</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" si="138"/>
-        <v>184.95692937500004</v>
+        <f t="shared" si="136"/>
+        <v>234.39041550000007</v>
       </c>
       <c r="AF28" s="8">
-        <f t="shared" si="138"/>
-        <v>270.2450169</v>
+        <f t="shared" si="136"/>
+        <v>344.05319074499982</v>
       </c>
       <c r="AG28" s="8">
-        <f t="shared" si="138"/>
-        <v>354.22822119599982</v>
+        <f t="shared" si="136"/>
+        <v>438.86296241324982</v>
       </c>
       <c r="AH28" s="8">
-        <f t="shared" si="138"/>
-        <v>422.71480529221486</v>
+        <f t="shared" si="136"/>
+        <v>515.67113078394721</v>
       </c>
       <c r="AI28" s="8">
-        <f t="shared" si="138"/>
-        <v>485.68362435679376</v>
+        <f t="shared" si="136"/>
+        <v>585.98684411124941</v>
       </c>
       <c r="AJ28" s="8">
-        <f t="shared" si="138"/>
-        <v>539.47190122153677</v>
+        <f t="shared" si="136"/>
+        <v>645.76156613321393</v>
       </c>
       <c r="AK28" s="8">
-        <f t="shared" si="138"/>
-        <v>588.148983840847</v>
+        <f t="shared" si="136"/>
+        <v>699.72551943684675</v>
       </c>
       <c r="AL28" s="8">
-        <f t="shared" si="138"/>
-        <v>639.59420846807075</v>
+        <f t="shared" si="136"/>
+        <v>756.72249011196664</v>
       </c>
       <c r="AM28" s="8">
-        <f t="shared" si="138"/>
-        <v>693.95167014240064</v>
+        <f t="shared" si="136"/>
+        <v>816.90983844333812</v>
       </c>
       <c r="AN28" s="8">
-        <f t="shared" si="138"/>
-        <v>751.37277243557719</v>
+        <f t="shared" si="136"/>
+        <v>880.45289704850791</v>
       </c>
       <c r="AQ28" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AR28" s="10">
         <f>AR26/AR27-1</f>
-        <v>-0.68546930122466088</v>
+        <v>-0.31039334684948316</v>
       </c>
     </row>
     <row r="29" spans="2:44" x14ac:dyDescent="0.3">
@@ -4879,43 +4857,43 @@
         <v>11.445</v>
       </c>
       <c r="AE29" s="5">
-        <f t="shared" ref="AE29:AN29" si="139">AD29*1.05</f>
+        <f t="shared" ref="AE29:AN29" si="137">AD29*1.05</f>
         <v>12.017250000000001</v>
       </c>
       <c r="AF29" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>12.618112500000001</v>
       </c>
       <c r="AG29" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>13.249018125000001</v>
       </c>
       <c r="AH29" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>13.911469031250002</v>
       </c>
       <c r="AI29" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>14.607042482812503</v>
       </c>
       <c r="AJ29" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>15.337394606953129</v>
       </c>
       <c r="AK29" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>16.104264337300787</v>
       </c>
       <c r="AL29" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>16.909477554165829</v>
       </c>
       <c r="AM29" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>17.754951431874122</v>
       </c>
       <c r="AN29" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>18.642699003467829</v>
       </c>
       <c r="AQ29" t="s">
@@ -4950,19 +4928,19 @@
         <v>121.55000000000001</v>
       </c>
       <c r="AE30" s="5">
-        <f t="shared" ref="AE30:AH30" si="140">AD30*1.1</f>
+        <f t="shared" ref="AE30:AH30" si="138">AD30*1.1</f>
         <v>133.70500000000001</v>
       </c>
       <c r="AF30" s="5">
-        <f t="shared" si="140"/>
+        <f t="shared" si="138"/>
         <v>147.07550000000003</v>
       </c>
       <c r="AG30" s="5">
-        <f t="shared" si="140"/>
+        <f t="shared" si="138"/>
         <v>161.78305000000006</v>
       </c>
       <c r="AH30" s="5">
-        <f t="shared" si="140"/>
+        <f t="shared" si="138"/>
         <v>177.96135500000008</v>
       </c>
       <c r="AI30" s="5">
@@ -4970,23 +4948,23 @@
         <v>181.5205821000001</v>
       </c>
       <c r="AJ30" s="5">
-        <f t="shared" ref="AJ30:AN30" si="141">AI30*1.02</f>
+        <f t="shared" ref="AJ30:AN30" si="139">AI30*1.02</f>
         <v>185.15099374200011</v>
       </c>
       <c r="AK30" s="5">
-        <f t="shared" si="141"/>
+        <f t="shared" si="139"/>
         <v>188.85401361684012</v>
       </c>
       <c r="AL30" s="5">
-        <f t="shared" si="141"/>
+        <f t="shared" si="139"/>
         <v>192.63109388917692</v>
       </c>
       <c r="AM30" s="5">
-        <f t="shared" si="141"/>
+        <f t="shared" si="139"/>
         <v>196.48371576696047</v>
       </c>
       <c r="AN30" s="5">
-        <f t="shared" si="141"/>
+        <f t="shared" si="139"/>
         <v>200.41339008229968</v>
       </c>
     </row>
@@ -5428,68 +5406,68 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="Y39" s="8">
-        <f t="shared" ref="Y39:AD39" si="142">Y28+SUM(Y29:Y38)</f>
+        <f t="shared" ref="Y39:AD39" si="140">Y28+SUM(Y29:Y38)</f>
         <v>17.700000000000003</v>
       </c>
       <c r="Z39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>9.3999999999999702</v>
       </c>
       <c r="AA39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>53.600000000000044</v>
       </c>
       <c r="AB39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>153.60000000000005</v>
       </c>
       <c r="AC39" s="8">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>285.7</v>
       </c>
       <c r="AD39" s="8">
-        <f t="shared" si="142"/>
-        <v>258.01272000000006</v>
+        <f t="shared" si="140"/>
+        <v>291.31149999999985</v>
       </c>
       <c r="AE39" s="8">
-        <f t="shared" ref="AE39:AN39" si="143">AE28+SUM(AE29:AE38)</f>
-        <v>330.67917937500005</v>
+        <f t="shared" ref="AE39:AN39" si="141">AE28+SUM(AE29:AE38)</f>
+        <v>380.11266550000005</v>
       </c>
       <c r="AF39" s="8">
-        <f t="shared" si="143"/>
-        <v>429.93862940000002</v>
+        <f t="shared" si="141"/>
+        <v>503.74680324499985</v>
       </c>
       <c r="AG39" s="8">
-        <f t="shared" si="143"/>
-        <v>529.26028932099985</v>
+        <f t="shared" si="141"/>
+        <v>613.8950305382499</v>
       </c>
       <c r="AH39" s="8">
-        <f t="shared" si="143"/>
-        <v>614.58762932346497</v>
+        <f t="shared" si="141"/>
+        <v>707.54395481519725</v>
       </c>
       <c r="AI39" s="8">
-        <f t="shared" si="143"/>
-        <v>681.81124893960634</v>
+        <f t="shared" si="141"/>
+        <v>782.114468694062</v>
       </c>
       <c r="AJ39" s="8">
-        <f t="shared" si="143"/>
-        <v>739.96028957048998</v>
+        <f t="shared" si="141"/>
+        <v>846.24995448216714</v>
       </c>
       <c r="AK39" s="8">
-        <f t="shared" si="143"/>
-        <v>793.10726179498783</v>
+        <f t="shared" si="141"/>
+        <v>904.68379739098759</v>
       </c>
       <c r="AL39" s="8">
-        <f t="shared" si="143"/>
-        <v>849.13477991141349</v>
+        <f t="shared" si="141"/>
+        <v>966.26306155530938</v>
       </c>
       <c r="AM39" s="8">
-        <f t="shared" si="143"/>
-        <v>908.19033734123525</v>
+        <f t="shared" si="141"/>
+        <v>1031.1485056421727</v>
       </c>
       <c r="AN39" s="8">
-        <f t="shared" si="143"/>
-        <v>970.42886152134474</v>
+        <f t="shared" si="141"/>
+        <v>1099.5089861342753</v>
       </c>
     </row>
     <row r="40" spans="2:136" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5517,43 +5495,43 @@
         <v>9.9</v>
       </c>
       <c r="AE40" s="5">
-        <f t="shared" ref="AE40:AN40" si="144">AD40*1.1</f>
+        <f t="shared" ref="AE40:AN40" si="142">AD40*1.1</f>
         <v>10.89</v>
       </c>
       <c r="AF40" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>11.979000000000001</v>
       </c>
       <c r="AG40" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>13.176900000000002</v>
       </c>
       <c r="AH40" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>14.494590000000002</v>
       </c>
       <c r="AI40" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>15.944049000000003</v>
       </c>
       <c r="AJ40" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>17.538453900000004</v>
       </c>
       <c r="AK40" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>19.292299290000006</v>
       </c>
       <c r="AL40" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>21.221529219000008</v>
       </c>
       <c r="AM40" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>23.343682140900011</v>
       </c>
       <c r="AN40" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>25.678050354990013</v>
       </c>
     </row>
@@ -5582,43 +5560,43 @@
         <v>13.31</v>
       </c>
       <c r="AE41" s="5">
-        <f t="shared" ref="AE41:AN41" si="145">AD41*1.1</f>
+        <f t="shared" ref="AE41:AN41" si="143">AD41*1.1</f>
         <v>14.641000000000002</v>
       </c>
       <c r="AF41" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>16.105100000000004</v>
       </c>
       <c r="AG41" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>17.715610000000005</v>
       </c>
       <c r="AH41" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>19.487171000000007</v>
       </c>
       <c r="AI41" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>21.43588810000001</v>
       </c>
       <c r="AJ41" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>23.579476910000015</v>
       </c>
       <c r="AK41" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>25.937424601000018</v>
       </c>
       <c r="AL41" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>28.531167061100021</v>
       </c>
       <c r="AM41" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>31.384283767210025</v>
       </c>
       <c r="AN41" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>34.522712143931031</v>
       </c>
     </row>
@@ -5631,67 +5609,67 @@
         <v>5.3000000000000007</v>
       </c>
       <c r="Y42" s="5">
-        <f t="shared" ref="Y42:AD42" si="146">SUM(Y40:Y41)</f>
+        <f t="shared" ref="Y42:AD42" si="144">SUM(Y40:Y41)</f>
         <v>4</v>
       </c>
       <c r="Z42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>6.2</v>
       </c>
       <c r="AA42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>10.199999999999999</v>
       </c>
       <c r="AB42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>13.7</v>
       </c>
       <c r="AC42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>21.1</v>
       </c>
       <c r="AD42" s="5">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>23.21</v>
       </c>
       <c r="AE42" s="5">
-        <f t="shared" ref="AE42:AN42" si="147">SUM(AE40:AE41)</f>
+        <f t="shared" ref="AE42:AN42" si="145">SUM(AE40:AE41)</f>
         <v>25.531000000000002</v>
       </c>
       <c r="AF42" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>28.084100000000007</v>
       </c>
       <c r="AG42" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>30.892510000000009</v>
       </c>
       <c r="AH42" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>33.981761000000006</v>
       </c>
       <c r="AI42" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>37.379937100000014</v>
       </c>
       <c r="AJ42" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>41.117930810000018</v>
       </c>
       <c r="AK42" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>45.22972389100002</v>
       </c>
       <c r="AL42" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>49.752696280100025</v>
       </c>
       <c r="AM42" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>54.727965908110036</v>
       </c>
       <c r="AN42" s="5">
-        <f t="shared" si="147"/>
+        <f t="shared" si="145"/>
         <v>60.200762498921044</v>
       </c>
     </row>
@@ -5703,488 +5681,488 @@
         <v>-3.1</v>
       </c>
       <c r="Y43" s="8">
-        <f t="shared" ref="Y43:AD43" si="148">Y39-Y42</f>
+        <f t="shared" ref="Y43:AD43" si="146">Y39-Y42</f>
         <v>13.700000000000003</v>
       </c>
       <c r="Z43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="146"/>
         <v>3.19999999999997</v>
       </c>
       <c r="AA43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="146"/>
         <v>43.400000000000048</v>
       </c>
       <c r="AB43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="146"/>
         <v>139.90000000000006</v>
       </c>
       <c r="AC43" s="8">
-        <f t="shared" si="148"/>
+        <f t="shared" si="146"/>
         <v>264.59999999999997</v>
       </c>
       <c r="AD43" s="8">
-        <f t="shared" si="148"/>
-        <v>234.80272000000005</v>
+        <f t="shared" si="146"/>
+        <v>268.10149999999987</v>
       </c>
       <c r="AE43" s="8">
-        <f t="shared" ref="AE43:AN43" si="149">AE39-AE42</f>
-        <v>305.14817937500004</v>
+        <f t="shared" ref="AE43:AN43" si="147">AE39-AE42</f>
+        <v>354.58166550000004</v>
       </c>
       <c r="AF43" s="8">
-        <f t="shared" si="149"/>
-        <v>401.85452940000005</v>
+        <f t="shared" si="147"/>
+        <v>475.66270324499988</v>
       </c>
       <c r="AG43" s="8">
-        <f t="shared" si="149"/>
-        <v>498.36777932099983</v>
+        <f t="shared" si="147"/>
+        <v>583.00252053824988</v>
       </c>
       <c r="AH43" s="8">
-        <f t="shared" si="149"/>
-        <v>580.60586832346496</v>
+        <f t="shared" si="147"/>
+        <v>673.56219381519725</v>
       </c>
       <c r="AI43" s="8">
-        <f t="shared" si="149"/>
-        <v>644.43131183960634</v>
+        <f t="shared" si="147"/>
+        <v>744.73453159406199</v>
       </c>
       <c r="AJ43" s="8">
-        <f t="shared" si="149"/>
-        <v>698.84235876049001</v>
+        <f t="shared" si="147"/>
+        <v>805.13202367216718</v>
       </c>
       <c r="AK43" s="8">
-        <f t="shared" si="149"/>
-        <v>747.87753790398779</v>
+        <f t="shared" si="147"/>
+        <v>859.45407349998754</v>
       </c>
       <c r="AL43" s="8">
-        <f t="shared" si="149"/>
-        <v>799.38208363131344</v>
+        <f t="shared" si="147"/>
+        <v>916.51036527520932</v>
       </c>
       <c r="AM43" s="8">
-        <f t="shared" si="149"/>
-        <v>853.46237143312521</v>
+        <f t="shared" si="147"/>
+        <v>976.42053973406269</v>
       </c>
       <c r="AN43" s="8">
-        <f t="shared" si="149"/>
-        <v>910.22809902242375</v>
+        <f t="shared" si="147"/>
+        <v>1039.3082236353544</v>
       </c>
       <c r="AO43" s="1">
         <f>AN43*(1+$AR$21)</f>
-        <v>901.1258180321995</v>
+        <v>1028.9151413990007</v>
       </c>
       <c r="AP43" s="1">
-        <f t="shared" ref="AP43:DA43" si="150">AO43*(1+$AR$21)</f>
-        <v>892.11455985187752</v>
+        <f t="shared" ref="AP43:DA43" si="148">AO43*(1+$AR$21)</f>
+        <v>1018.6259899850107</v>
       </c>
       <c r="AQ43" s="1">
-        <f t="shared" si="150"/>
-        <v>883.1934142533587</v>
+        <f t="shared" si="148"/>
+        <v>1008.4397300851606</v>
       </c>
       <c r="AR43" s="1">
-        <f t="shared" si="150"/>
-        <v>874.36148011082514</v>
+        <f t="shared" si="148"/>
+        <v>998.35533278430898</v>
       </c>
       <c r="AS43" s="1">
-        <f t="shared" si="150"/>
-        <v>865.61786530971688</v>
+        <f t="shared" si="148"/>
+        <v>988.3717794564659</v>
       </c>
       <c r="AT43" s="1">
-        <f t="shared" si="150"/>
-        <v>856.96168665661969</v>
+        <f t="shared" si="148"/>
+        <v>978.48806166190127</v>
       </c>
       <c r="AU43" s="1">
-        <f t="shared" si="150"/>
-        <v>848.39206979005348</v>
+        <f t="shared" si="148"/>
+        <v>968.70318104528224</v>
       </c>
       <c r="AV43" s="1">
-        <f t="shared" si="150"/>
-        <v>839.90814909215294</v>
+        <f t="shared" si="148"/>
+        <v>959.01614923482941</v>
       </c>
       <c r="AW43" s="1">
-        <f t="shared" si="150"/>
-        <v>831.50906760123144</v>
+        <f t="shared" si="148"/>
+        <v>949.42598774248108</v>
       </c>
       <c r="AX43" s="1">
-        <f t="shared" si="150"/>
-        <v>823.19397692521909</v>
+        <f t="shared" si="148"/>
+        <v>939.93172786505625</v>
       </c>
       <c r="AY43" s="1">
-        <f t="shared" si="150"/>
-        <v>814.96203715596687</v>
+        <f t="shared" si="148"/>
+        <v>930.53241058640572</v>
       </c>
       <c r="AZ43" s="1">
-        <f t="shared" si="150"/>
-        <v>806.81241678440722</v>
+        <f t="shared" si="148"/>
+        <v>921.22708648054163</v>
       </c>
       <c r="BA43" s="1">
-        <f t="shared" si="150"/>
-        <v>798.74429261656314</v>
+        <f t="shared" si="148"/>
+        <v>912.01481561573621</v>
       </c>
       <c r="BB43" s="1">
-        <f t="shared" si="150"/>
-        <v>790.75684969039753</v>
+        <f t="shared" si="148"/>
+        <v>902.89466745957884</v>
       </c>
       <c r="BC43" s="1">
-        <f t="shared" si="150"/>
-        <v>782.84928119349354</v>
+        <f t="shared" si="148"/>
+        <v>893.86572078498307</v>
       </c>
       <c r="BD43" s="1">
-        <f t="shared" si="150"/>
-        <v>775.02078838155865</v>
+        <f t="shared" si="148"/>
+        <v>884.92706357713325</v>
       </c>
       <c r="BE43" s="1">
-        <f t="shared" si="150"/>
-        <v>767.27058049774303</v>
+        <f t="shared" si="148"/>
+        <v>876.07779294136196</v>
       </c>
       <c r="BF43" s="1">
-        <f t="shared" si="150"/>
-        <v>759.59787469276557</v>
+        <f t="shared" si="148"/>
+        <v>867.31701501194834</v>
       </c>
       <c r="BG43" s="1">
-        <f t="shared" si="150"/>
-        <v>752.00189594583787</v>
+        <f t="shared" si="148"/>
+        <v>858.64384486182882</v>
       </c>
       <c r="BH43" s="1">
-        <f t="shared" si="150"/>
-        <v>744.48187698637946</v>
+        <f t="shared" si="148"/>
+        <v>850.05740641321051</v>
       </c>
       <c r="BI43" s="1">
-        <f t="shared" si="150"/>
-        <v>737.03705821651567</v>
+        <f t="shared" si="148"/>
+        <v>841.55683234907838</v>
       </c>
       <c r="BJ43" s="1">
-        <f t="shared" si="150"/>
-        <v>729.66668763435052</v>
+        <f t="shared" si="148"/>
+        <v>833.14126402558759</v>
       </c>
       <c r="BK43" s="1">
-        <f t="shared" si="150"/>
-        <v>722.37002075800706</v>
+        <f t="shared" si="148"/>
+        <v>824.80985138533174</v>
       </c>
       <c r="BL43" s="1">
-        <f t="shared" si="150"/>
-        <v>715.14632055042694</v>
+        <f t="shared" si="148"/>
+        <v>816.56175287147846</v>
       </c>
       <c r="BM43" s="1">
-        <f t="shared" si="150"/>
-        <v>707.99485734492271</v>
+        <f t="shared" si="148"/>
+        <v>808.39613534276361</v>
       </c>
       <c r="BN43" s="1">
-        <f t="shared" si="150"/>
-        <v>700.91490877147351</v>
+        <f t="shared" si="148"/>
+        <v>800.31217398933597</v>
       </c>
       <c r="BO43" s="1">
-        <f t="shared" si="150"/>
-        <v>693.90575968375879</v>
+        <f t="shared" si="148"/>
+        <v>792.30905224944263</v>
       </c>
       <c r="BP43" s="1">
-        <f t="shared" si="150"/>
-        <v>686.96670208692115</v>
+        <f t="shared" si="148"/>
+        <v>784.38596172694815</v>
       </c>
       <c r="BQ43" s="1">
-        <f t="shared" si="150"/>
-        <v>680.09703506605194</v>
+        <f t="shared" si="148"/>
+        <v>776.54210210967869</v>
       </c>
       <c r="BR43" s="1">
-        <f t="shared" si="150"/>
-        <v>673.29606471539137</v>
+        <f t="shared" si="148"/>
+        <v>768.77668108858188</v>
       </c>
       <c r="BS43" s="1">
-        <f t="shared" si="150"/>
-        <v>666.56310406823741</v>
+        <f t="shared" si="148"/>
+        <v>761.08891427769606</v>
       </c>
       <c r="BT43" s="1">
-        <f t="shared" si="150"/>
-        <v>659.89747302755507</v>
+        <f t="shared" si="148"/>
+        <v>753.47802513491911</v>
       </c>
       <c r="BU43" s="1">
-        <f t="shared" si="150"/>
-        <v>653.29849829727948</v>
+        <f t="shared" si="148"/>
+        <v>745.94324488356995</v>
       </c>
       <c r="BV43" s="1">
-        <f t="shared" si="150"/>
-        <v>646.76551331430665</v>
+        <f t="shared" si="148"/>
+        <v>738.4838124347342</v>
       </c>
       <c r="BW43" s="1">
-        <f t="shared" si="150"/>
-        <v>640.29785818116352</v>
+        <f t="shared" si="148"/>
+        <v>731.09897431038689</v>
       </c>
       <c r="BX43" s="1">
-        <f t="shared" si="150"/>
-        <v>633.89487959935184</v>
+        <f t="shared" si="148"/>
+        <v>723.78798456728305</v>
       </c>
       <c r="BY43" s="1">
-        <f t="shared" si="150"/>
-        <v>627.55593080335836</v>
+        <f t="shared" si="148"/>
+        <v>716.55010472161018</v>
       </c>
       <c r="BZ43" s="1">
-        <f t="shared" si="150"/>
-        <v>621.28037149532474</v>
+        <f t="shared" si="148"/>
+        <v>709.38460367439404</v>
       </c>
       <c r="CA43" s="1">
-        <f t="shared" si="150"/>
-        <v>615.06756778037152</v>
+        <f t="shared" si="148"/>
+        <v>702.29075763765013</v>
       </c>
       <c r="CB43" s="1">
-        <f t="shared" si="150"/>
-        <v>608.91689210256777</v>
+        <f t="shared" si="148"/>
+        <v>695.26785006127363</v>
       </c>
       <c r="CC43" s="1">
-        <f t="shared" si="150"/>
-        <v>602.82772318154207</v>
+        <f t="shared" si="148"/>
+        <v>688.31517156066093</v>
       </c>
       <c r="CD43" s="1">
-        <f t="shared" si="150"/>
-        <v>596.79944594972665</v>
+        <f t="shared" si="148"/>
+        <v>681.43201984505436</v>
       </c>
       <c r="CE43" s="1">
-        <f t="shared" si="150"/>
-        <v>590.83145149022937</v>
+        <f t="shared" si="148"/>
+        <v>674.6176996466038</v>
       </c>
       <c r="CF43" s="1">
-        <f t="shared" si="150"/>
-        <v>584.92313697532711</v>
+        <f t="shared" si="148"/>
+        <v>667.87152265013776</v>
       </c>
       <c r="CG43" s="1">
-        <f t="shared" si="150"/>
-        <v>579.07390560557383</v>
+        <f t="shared" si="148"/>
+        <v>661.1928074236364</v>
       </c>
       <c r="CH43" s="1">
-        <f t="shared" si="150"/>
-        <v>573.28316654951811</v>
+        <f t="shared" si="148"/>
+        <v>654.58087934939999</v>
       </c>
       <c r="CI43" s="1">
-        <f t="shared" si="150"/>
-        <v>567.55033488402296</v>
+        <f t="shared" si="148"/>
+        <v>648.03507055590603</v>
       </c>
       <c r="CJ43" s="1">
-        <f t="shared" si="150"/>
-        <v>561.87483153518269</v>
+        <f t="shared" si="148"/>
+        <v>641.55471985034694</v>
       </c>
       <c r="CK43" s="1">
-        <f t="shared" si="150"/>
-        <v>556.25608321983088</v>
+        <f t="shared" si="148"/>
+        <v>635.13917265184341</v>
       </c>
       <c r="CL43" s="1">
-        <f t="shared" si="150"/>
-        <v>550.69352238763258</v>
+        <f t="shared" si="148"/>
+        <v>628.78778092532502</v>
       </c>
       <c r="CM43" s="1">
-        <f t="shared" si="150"/>
-        <v>545.18658716375626</v>
+        <f t="shared" si="148"/>
+        <v>622.49990311607178</v>
       </c>
       <c r="CN43" s="1">
-        <f t="shared" si="150"/>
-        <v>539.73472129211871</v>
+        <f t="shared" si="148"/>
+        <v>616.2749040849111</v>
       </c>
       <c r="CO43" s="1">
-        <f t="shared" si="150"/>
-        <v>534.3373740791975</v>
+        <f t="shared" si="148"/>
+        <v>610.11215504406198</v>
       </c>
       <c r="CP43" s="1">
-        <f t="shared" si="150"/>
-        <v>528.9940003384055</v>
+        <f t="shared" si="148"/>
+        <v>604.01103349362131</v>
       </c>
       <c r="CQ43" s="1">
-        <f t="shared" si="150"/>
-        <v>523.7040603350215</v>
+        <f t="shared" si="148"/>
+        <v>597.97092315868508</v>
       </c>
       <c r="CR43" s="1">
-        <f t="shared" si="150"/>
-        <v>518.46701973167126</v>
+        <f t="shared" si="148"/>
+        <v>591.99121392709822</v>
       </c>
       <c r="CS43" s="1">
-        <f t="shared" si="150"/>
-        <v>513.28234953435458</v>
+        <f t="shared" si="148"/>
+        <v>586.07130178782722</v>
       </c>
       <c r="CT43" s="1">
-        <f t="shared" si="150"/>
-        <v>508.14952603901105</v>
+        <f t="shared" si="148"/>
+        <v>580.21058876994891</v>
       </c>
       <c r="CU43" s="1">
-        <f t="shared" si="150"/>
-        <v>503.06803077862094</v>
+        <f t="shared" si="148"/>
+        <v>574.40848288224947</v>
       </c>
       <c r="CV43" s="1">
-        <f t="shared" si="150"/>
-        <v>498.03735047083472</v>
+        <f t="shared" si="148"/>
+        <v>568.66439805342702</v>
       </c>
       <c r="CW43" s="1">
-        <f t="shared" si="150"/>
-        <v>493.0569769661264</v>
+        <f t="shared" si="148"/>
+        <v>562.97775407289271</v>
       </c>
       <c r="CX43" s="1">
-        <f t="shared" si="150"/>
-        <v>488.12640719646515</v>
+        <f t="shared" si="148"/>
+        <v>557.34797653216378</v>
       </c>
       <c r="CY43" s="1">
-        <f t="shared" si="150"/>
-        <v>483.24514312450049</v>
+        <f t="shared" si="148"/>
+        <v>551.77449676684216</v>
       </c>
       <c r="CZ43" s="1">
-        <f t="shared" si="150"/>
-        <v>478.41269169325545</v>
+        <f t="shared" si="148"/>
+        <v>546.25675179917368</v>
       </c>
       <c r="DA43" s="1">
-        <f t="shared" si="150"/>
-        <v>473.62856477632289</v>
+        <f t="shared" si="148"/>
+        <v>540.79418428118197</v>
       </c>
       <c r="DB43" s="1">
-        <f t="shared" ref="DB43:EF43" si="151">DA43*(1+$AR$21)</f>
-        <v>468.89227912855966</v>
+        <f t="shared" ref="DB43:EF43" si="149">DA43*(1+$AR$21)</f>
+        <v>535.38624243837012</v>
       </c>
       <c r="DC43" s="1">
-        <f t="shared" si="151"/>
-        <v>464.20335633727404</v>
+        <f t="shared" si="149"/>
+        <v>530.03238001398643</v>
       </c>
       <c r="DD43" s="1">
-        <f t="shared" si="151"/>
-        <v>459.56132277390128</v>
+        <f t="shared" si="149"/>
+        <v>524.73205621384659</v>
       </c>
       <c r="DE43" s="1">
-        <f t="shared" si="151"/>
-        <v>454.96570954616226</v>
+        <f t="shared" si="149"/>
+        <v>519.48473565170809</v>
       </c>
       <c r="DF43" s="1">
-        <f t="shared" si="151"/>
-        <v>450.41605245070065</v>
+        <f t="shared" si="149"/>
+        <v>514.28988829519096</v>
       </c>
       <c r="DG43" s="1">
-        <f t="shared" si="151"/>
-        <v>445.91189192619362</v>
+        <f t="shared" si="149"/>
+        <v>509.14698941223907</v>
       </c>
       <c r="DH43" s="1">
-        <f t="shared" si="151"/>
-        <v>441.45277300693169</v>
+        <f t="shared" si="149"/>
+        <v>504.05551951811668</v>
       </c>
       <c r="DI43" s="1">
-        <f t="shared" si="151"/>
-        <v>437.03824527686237</v>
+        <f t="shared" si="149"/>
+        <v>499.0149643229355</v>
       </c>
       <c r="DJ43" s="1">
-        <f t="shared" si="151"/>
-        <v>432.66786282409373</v>
+        <f t="shared" si="149"/>
+        <v>494.02481467970614</v>
       </c>
       <c r="DK43" s="1">
-        <f t="shared" si="151"/>
-        <v>428.3411841958528</v>
+        <f t="shared" si="149"/>
+        <v>489.08456653290909</v>
       </c>
       <c r="DL43" s="1">
-        <f t="shared" si="151"/>
-        <v>424.05777235389428</v>
+        <f t="shared" si="149"/>
+        <v>484.19372086758</v>
       </c>
       <c r="DM43" s="1">
-        <f t="shared" si="151"/>
-        <v>419.81719463035535</v>
+        <f t="shared" si="149"/>
+        <v>479.3517836589042</v>
       </c>
       <c r="DN43" s="1">
-        <f t="shared" si="151"/>
-        <v>415.6190226840518</v>
+        <f t="shared" si="149"/>
+        <v>474.55826582231515</v>
       </c>
       <c r="DO43" s="1">
-        <f t="shared" si="151"/>
-        <v>411.46283245721128</v>
+        <f t="shared" si="149"/>
+        <v>469.81268316409199</v>
       </c>
       <c r="DP43" s="1">
-        <f t="shared" si="151"/>
-        <v>407.34820413263918</v>
+        <f t="shared" si="149"/>
+        <v>465.11455633245106</v>
       </c>
       <c r="DQ43" s="1">
-        <f t="shared" si="151"/>
-        <v>403.27472209131281</v>
+        <f t="shared" si="149"/>
+        <v>460.46341076912654</v>
       </c>
       <c r="DR43" s="1">
-        <f t="shared" si="151"/>
-        <v>399.2419748703997</v>
+        <f t="shared" si="149"/>
+        <v>455.85877666143529</v>
       </c>
       <c r="DS43" s="1">
-        <f t="shared" si="151"/>
-        <v>395.24955512169572</v>
+        <f t="shared" si="149"/>
+        <v>451.30018889482091</v>
       </c>
       <c r="DT43" s="1">
-        <f t="shared" si="151"/>
-        <v>391.29705957047878</v>
+        <f t="shared" si="149"/>
+        <v>446.78718700587268</v>
       </c>
       <c r="DU43" s="1">
-        <f t="shared" si="151"/>
-        <v>387.38408897477399</v>
+        <f t="shared" si="149"/>
+        <v>442.31931513581395</v>
       </c>
       <c r="DV43" s="1">
-        <f t="shared" si="151"/>
-        <v>383.51024808502626</v>
+        <f t="shared" si="149"/>
+        <v>437.89612198445582</v>
       </c>
       <c r="DW43" s="1">
-        <f t="shared" si="151"/>
-        <v>379.67514560417601</v>
+        <f t="shared" si="149"/>
+        <v>433.51716076461128</v>
       </c>
       <c r="DX43" s="1">
-        <f t="shared" si="151"/>
-        <v>375.87839414813425</v>
+        <f t="shared" si="149"/>
+        <v>429.18198915696519</v>
       </c>
       <c r="DY43" s="1">
-        <f t="shared" si="151"/>
-        <v>372.11961020665291</v>
+        <f t="shared" si="149"/>
+        <v>424.89016926539551</v>
       </c>
       <c r="DZ43" s="1">
-        <f t="shared" si="151"/>
-        <v>368.39841410458638</v>
+        <f t="shared" si="149"/>
+        <v>420.64126757274158</v>
       </c>
       <c r="EA43" s="1">
-        <f t="shared" si="151"/>
-        <v>364.71442996354051</v>
+        <f t="shared" si="149"/>
+        <v>416.43485489701419</v>
       </c>
       <c r="EB43" s="1">
-        <f t="shared" si="151"/>
-        <v>361.06728566390512</v>
+        <f t="shared" si="149"/>
+        <v>412.27050634804402</v>
       </c>
       <c r="EC43" s="1">
-        <f t="shared" si="151"/>
-        <v>357.45661280726608</v>
+        <f t="shared" si="149"/>
+        <v>408.14780128456357</v>
       </c>
       <c r="ED43" s="1">
-        <f t="shared" si="151"/>
-        <v>353.88204667919342</v>
+        <f t="shared" si="149"/>
+        <v>404.06632327171792</v>
       </c>
       <c r="EE43" s="1">
-        <f t="shared" si="151"/>
-        <v>350.34322621240148</v>
+        <f t="shared" si="149"/>
+        <v>400.02566003900074</v>
       </c>
       <c r="EF43" s="1">
-        <f t="shared" si="151"/>
-        <v>346.83979395027745</v>
+        <f t="shared" si="149"/>
+        <v>396.02540343861074</v>
       </c>
     </row>
     <row r="46" spans="2:136" x14ac:dyDescent="0.3">
       <c r="AR46" s="5">
         <f>NPV(AR22,AD43:EF43)</f>
-        <v>8256.1910211471059</v>
+        <v>9478.703973408552</v>
       </c>
     </row>
     <row r="47" spans="2:136" x14ac:dyDescent="0.3">
       <c r="AR47" s="5">
         <f>Main!D8</f>
-        <v>1082.5999999999999</v>
+        <v>1097.9000000000001</v>
       </c>
     </row>
     <row r="48" spans="2:136" x14ac:dyDescent="0.3">
       <c r="AR48" s="5">
         <f>AR46+AR47</f>
-        <v>9338.7910211471062</v>
+        <v>10576.603973408552</v>
       </c>
     </row>
     <row r="49" spans="44:44" x14ac:dyDescent="0.3">
       <c r="AR49" s="4">
         <f>AR48/AN16</f>
-        <v>205.2481543109254</v>
+        <v>230.93021776001206</v>
       </c>
     </row>
     <row r="50" spans="44:44" x14ac:dyDescent="0.3">
       <c r="AR50" s="4">
         <f>Main!D3</f>
-        <v>528.66999999999996</v>
+        <v>278.74</v>
       </c>
     </row>
     <row r="51" spans="44:44" x14ac:dyDescent="0.3">
       <c r="AR51" s="10">
         <f>AR49/AR50-1</f>
-        <v>-0.61176508159924825</v>
+        <v>-0.17152106708756532</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/DUOL.xlsx
+++ b/Financial Analysis/DUOL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D951848-C802-4B5F-BD0D-5BF8FE77F8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FEDEF4-BBCB-4739-B675-9C858EB3253C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9EA5A098-45C5-472E-8765-EE9A7145AF0E}"/>
   </bookViews>
@@ -31,6 +31,30 @@
     <author>Anton Mniszek</author>
   </authors>
   <commentList>
+    <comment ref="V3" authorId="0" shapeId="0" xr:uid="{5504AB99-F7AB-4999-B5CC-4F46DD99FC02}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anton Mniszek:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+(Q325) guidance 273-277m</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="AD3" authorId="0" shapeId="0" xr:uid="{58708693-72ED-4B1C-ACAC-E527BE89624F}">
       <text>
         <r>
@@ -290,7 +314,7 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Overvalued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -403,13 +427,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>21</xdr:col>
       <xdr:colOff>22860</xdr:colOff>
       <xdr:row>44</xdr:row>
       <xdr:rowOff>106680</xdr:rowOff>
@@ -427,7 +451,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13091160" y="7620"/>
+          <a:off x="13700760" y="7620"/>
           <a:ext cx="0" cy="8145780"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -827,17 +851,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>278.74</v>
+        <v>195.41</v>
       </c>
       <c r="E3" s="3">
-        <v>45909</v>
+        <v>45967</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45909</v>
+        <v>45967</v>
       </c>
       <c r="G3" s="3">
-        <v>45966</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -845,10 +869,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="5">
-        <v>45.8</v>
+        <f>46.1</f>
+        <v>46.1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -857,7 +882,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>12766.291999999999</v>
+        <v>9008.4009999999998</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -865,11 +890,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="5">
-        <f>976.2+121.7</f>
-        <v>1097.9000000000001</v>
+        <f>1011.5+109.9</f>
+        <v>1121.4000000000001</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -880,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -889,7 +914,7 @@
       </c>
       <c r="D8" s="5">
         <f>D6-D7</f>
-        <v>1097.9000000000001</v>
+        <v>1121.4000000000001</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -898,7 +923,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>11668.392</v>
+        <v>7887.0010000000002</v>
       </c>
     </row>
   </sheetData>
@@ -1090,12 +1115,10 @@
         <v>252.3</v>
       </c>
       <c r="U3" s="8">
-        <f>Q3*1.4</f>
-        <v>269.64</v>
+        <v>271.7</v>
       </c>
       <c r="V3" s="8">
-        <f>R3*1.35</f>
-        <v>282.96000000000004</v>
+        <v>275</v>
       </c>
       <c r="X3" s="8">
         <v>70.8</v>
@@ -1121,47 +1144,47 @@
       </c>
       <c r="AD3" s="8">
         <f>SUM(S3:V3)</f>
-        <v>1035.5999999999999</v>
+        <v>1029.7</v>
       </c>
       <c r="AE3" s="8">
-        <f>AD3*1.28</f>
-        <v>1325.568</v>
+        <f>AD3*1.25</f>
+        <v>1287.125</v>
       </c>
       <c r="AF3" s="8">
-        <f>AE3*1.22</f>
-        <v>1617.1929599999999</v>
+        <f>AE3*1.2</f>
+        <v>1544.55</v>
       </c>
       <c r="AG3" s="8">
         <f>AF3*1.15</f>
-        <v>1859.7719039999997</v>
+        <v>1776.2324999999998</v>
       </c>
       <c r="AH3" s="8">
         <f>AG3*1.1</f>
-        <v>2045.7490943999999</v>
+        <v>1953.8557499999999</v>
       </c>
       <c r="AI3" s="8">
         <f>AH3*1.08</f>
-        <v>2209.4090219519999</v>
+        <v>2110.1642099999999</v>
       </c>
       <c r="AJ3" s="8">
         <f>AI3*1.06</f>
-        <v>2341.9735632691199</v>
+        <v>2236.7740626</v>
       </c>
       <c r="AK3" s="8">
         <f>AJ3*1.05</f>
-        <v>2459.072241432576</v>
+        <v>2348.6127657299999</v>
       </c>
       <c r="AL3" s="8">
         <f t="shared" ref="AL3:AN3" si="0">AK3*1.05</f>
-        <v>2582.0258535042049</v>
+        <v>2466.0434040165001</v>
       </c>
       <c r="AM3" s="8">
         <f t="shared" si="0"/>
-        <v>2711.1271461794154</v>
+        <v>2589.3455742173251</v>
       </c>
       <c r="AN3" s="8">
         <f t="shared" si="0"/>
-        <v>2846.6835034883861</v>
+        <v>2718.8128529281917</v>
       </c>
     </row>
     <row r="4" spans="2:139" x14ac:dyDescent="0.3">
@@ -1223,12 +1246,11 @@
         <v>69.7</v>
       </c>
       <c r="U4" s="5">
-        <f t="shared" ref="U4:V4" si="1">U3-U5</f>
-        <v>78.195600000000013</v>
+        <v>74.8</v>
       </c>
       <c r="V4" s="5">
-        <f t="shared" si="1"/>
-        <v>82.058400000000034</v>
+        <f t="shared" ref="V4" si="1">V3-V5</f>
+        <v>79.75</v>
       </c>
       <c r="X4" s="5">
         <v>20.7</v>
@@ -1254,47 +1276,47 @@
       </c>
       <c r="AD4" s="5">
         <f>SUM(S4:V4)</f>
-        <v>296.55400000000009</v>
+        <v>290.85000000000002</v>
       </c>
       <c r="AE4" s="5">
         <f>AE3-AE5</f>
-        <v>384.41471999999999</v>
+        <v>373.26625000000001</v>
       </c>
       <c r="AF4" s="5">
         <f t="shared" ref="AF4:AN4" si="2">AF3-AF5</f>
-        <v>468.98595840000007</v>
+        <v>447.91949999999997</v>
       </c>
       <c r="AG4" s="5">
         <f t="shared" si="2"/>
-        <v>539.33385215999988</v>
+        <v>515.10742499999992</v>
       </c>
       <c r="AH4" s="5">
         <f t="shared" si="2"/>
-        <v>593.26723737600014</v>
+        <v>566.61816750000003</v>
       </c>
       <c r="AI4" s="5">
         <f t="shared" si="2"/>
-        <v>640.72861636608013</v>
+        <v>611.94762089999995</v>
       </c>
       <c r="AJ4" s="5">
         <f t="shared" si="2"/>
-        <v>679.17233334804496</v>
+        <v>648.66447815400011</v>
       </c>
       <c r="AK4" s="5">
         <f t="shared" si="2"/>
-        <v>713.13095001544707</v>
+        <v>681.09770206170015</v>
       </c>
       <c r="AL4" s="5">
         <f t="shared" si="2"/>
-        <v>748.78749751621945</v>
+        <v>715.15258716478502</v>
       </c>
       <c r="AM4" s="5">
         <f t="shared" si="2"/>
-        <v>786.2268723920306</v>
+        <v>750.91021652302447</v>
       </c>
       <c r="AN4" s="5">
         <f t="shared" si="2"/>
-        <v>825.53821601163213</v>
+        <v>788.45572734917573</v>
       </c>
     </row>
     <row r="5" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1302,7 +1324,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="8">
-        <f t="shared" ref="C5:T5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:U5" si="3">C3-C4</f>
         <v>40.4</v>
       </c>
       <c r="D5" s="8">
@@ -1374,12 +1396,12 @@
         <v>182.60000000000002</v>
       </c>
       <c r="U5" s="8">
-        <f t="shared" ref="U5:V5" si="4">U3*0.71</f>
-        <v>191.44439999999997</v>
+        <f t="shared" si="3"/>
+        <v>196.89999999999998</v>
       </c>
       <c r="V5" s="8">
-        <f t="shared" si="4"/>
-        <v>200.9016</v>
+        <f t="shared" ref="V5" si="4">V3*0.71</f>
+        <v>195.25</v>
       </c>
       <c r="X5" s="8">
         <f t="shared" ref="X5:AD5" si="5">X3-X4</f>
@@ -1407,47 +1429,47 @@
       </c>
       <c r="AD5" s="8">
         <f t="shared" si="5"/>
-        <v>739.04599999999982</v>
+        <v>738.85</v>
       </c>
       <c r="AE5" s="8">
         <f>AE3*0.71</f>
-        <v>941.15328</v>
+        <v>913.85874999999999</v>
       </c>
       <c r="AF5" s="8">
         <f t="shared" ref="AF5:AN5" si="6">AF3*0.71</f>
-        <v>1148.2070015999998</v>
+        <v>1096.6305</v>
       </c>
       <c r="AG5" s="8">
         <f t="shared" si="6"/>
-        <v>1320.4380518399998</v>
+        <v>1261.1250749999999</v>
       </c>
       <c r="AH5" s="8">
         <f t="shared" si="6"/>
-        <v>1452.4818570239997</v>
+        <v>1387.2375824999999</v>
       </c>
       <c r="AI5" s="8">
         <f t="shared" si="6"/>
-        <v>1568.6804055859197</v>
+        <v>1498.2165891</v>
       </c>
       <c r="AJ5" s="8">
         <f t="shared" si="6"/>
-        <v>1662.801229921075</v>
+        <v>1588.1095844459999</v>
       </c>
       <c r="AK5" s="8">
         <f t="shared" si="6"/>
-        <v>1745.9412914171289</v>
+        <v>1667.5150636682997</v>
       </c>
       <c r="AL5" s="8">
         <f t="shared" si="6"/>
-        <v>1833.2383559879854</v>
+        <v>1750.890816851715</v>
       </c>
       <c r="AM5" s="8">
         <f t="shared" si="6"/>
-        <v>1924.9002737873848</v>
+        <v>1838.4353576943006</v>
       </c>
       <c r="AN5" s="8">
         <f t="shared" si="6"/>
-        <v>2021.145287476754</v>
+        <v>1930.3571255790159</v>
       </c>
     </row>
     <row r="6" spans="2:139" x14ac:dyDescent="0.3">
@@ -1509,12 +1531,11 @@
         <v>73.7</v>
       </c>
       <c r="U6" s="5">
-        <f>Q6*1.23</f>
-        <v>77.36699999999999</v>
+        <v>82.7</v>
       </c>
       <c r="V6" s="5">
-        <f>R6*1.22</f>
-        <v>81.00800000000001</v>
+        <f>R6*1.3</f>
+        <v>86.320000000000007</v>
       </c>
       <c r="X6" s="5">
         <v>31.6</v>
@@ -1540,47 +1561,47 @@
       </c>
       <c r="AD6" s="5">
         <f>SUM(S6:V6)</f>
-        <v>302.47500000000002</v>
+        <v>313.12</v>
       </c>
       <c r="AE6" s="5">
-        <f>AD6*1.18</f>
-        <v>356.9205</v>
+        <f>AD6*1.2</f>
+        <v>375.74399999999997</v>
       </c>
       <c r="AF6" s="5">
-        <f>AE6*1.12</f>
-        <v>399.75096000000002</v>
+        <f>AE6*1.14</f>
+        <v>428.34815999999995</v>
       </c>
       <c r="AG6" s="5">
         <f>AF6*1.06</f>
-        <v>423.73601760000003</v>
+        <v>454.04904959999999</v>
       </c>
       <c r="AH6" s="5">
         <f>AG6*1.04</f>
-        <v>440.68545830400006</v>
+        <v>472.211011584</v>
       </c>
       <c r="AI6" s="5">
         <f>AH6*1.03</f>
-        <v>453.90602205312007</v>
+        <v>486.37734193151999</v>
       </c>
       <c r="AJ6" s="5">
         <f>AI6*1.02</f>
-        <v>462.98414249418249</v>
+        <v>496.10488877015041</v>
       </c>
       <c r="AK6" s="5">
         <f t="shared" ref="AK6:AN6" si="7">AJ6*1.02</f>
-        <v>472.24382534406612</v>
+        <v>506.02698654555343</v>
       </c>
       <c r="AL6" s="5">
         <f t="shared" si="7"/>
-        <v>481.68870185094744</v>
+        <v>516.14752627646453</v>
       </c>
       <c r="AM6" s="5">
         <f t="shared" si="7"/>
-        <v>491.32247588796639</v>
+        <v>526.47047680199387</v>
       </c>
       <c r="AN6" s="5">
         <f t="shared" si="7"/>
-        <v>501.14892540572572</v>
+        <v>536.99988633803378</v>
       </c>
     </row>
     <row r="7" spans="2:139" x14ac:dyDescent="0.3">
@@ -1642,12 +1663,11 @@
         <v>29.6</v>
       </c>
       <c r="U7" s="5">
-        <f t="shared" ref="U7:V7" si="8">U3*0.11</f>
-        <v>29.660399999999999</v>
+        <v>35.1</v>
       </c>
       <c r="V7" s="5">
-        <f t="shared" si="8"/>
-        <v>31.125600000000006</v>
+        <f>V3*0.14</f>
+        <v>38.500000000000007</v>
       </c>
       <c r="X7" s="5">
         <v>15</v>
@@ -1673,47 +1693,47 @@
       </c>
       <c r="AD7" s="5">
         <f>SUM(S7:V7)</f>
-        <v>117.086</v>
+        <v>129.9</v>
       </c>
       <c r="AE7" s="5">
-        <f>AE3*0.1</f>
-        <v>132.55680000000001</v>
+        <f>AE3*0.12</f>
+        <v>154.45499999999998</v>
       </c>
       <c r="AF7" s="5">
-        <f>AF3*0.09</f>
-        <v>145.54736639999999</v>
+        <f>AF3*0.11</f>
+        <v>169.90049999999999</v>
       </c>
       <c r="AG7" s="5">
-        <f>AG3*0.09</f>
-        <v>167.37947135999997</v>
+        <f>AG3*0.1</f>
+        <v>177.62324999999998</v>
       </c>
       <c r="AH7" s="5">
-        <f t="shared" ref="AH7:AN7" si="9">AH3*0.09</f>
-        <v>184.11741849599997</v>
+        <f>AH3*0.095</f>
+        <v>185.61629625</v>
       </c>
       <c r="AI7" s="5">
-        <f t="shared" si="9"/>
-        <v>198.84681197567997</v>
+        <f t="shared" ref="AI7:AN7" si="8">AI3*0.095</f>
+        <v>200.46559994999998</v>
       </c>
       <c r="AJ7" s="5">
-        <f t="shared" si="9"/>
-        <v>210.77762069422079</v>
+        <f t="shared" si="8"/>
+        <v>212.493535947</v>
       </c>
       <c r="AK7" s="5">
-        <f t="shared" si="9"/>
-        <v>221.31650172893183</v>
+        <f t="shared" si="8"/>
+        <v>223.11821274434999</v>
       </c>
       <c r="AL7" s="5">
-        <f t="shared" si="9"/>
-        <v>232.38232681537843</v>
+        <f t="shared" si="8"/>
+        <v>234.27412338156751</v>
       </c>
       <c r="AM7" s="5">
-        <f t="shared" si="9"/>
-        <v>244.00144315614739</v>
+        <f t="shared" si="8"/>
+        <v>245.9878295506459</v>
       </c>
       <c r="AN7" s="5">
-        <f t="shared" si="9"/>
-        <v>256.20151531395476</v>
+        <f t="shared" si="8"/>
+        <v>258.28722102817824</v>
       </c>
     </row>
     <row r="8" spans="2:139" x14ac:dyDescent="0.3">
@@ -1775,12 +1795,11 @@
         <v>46</v>
       </c>
       <c r="U8" s="5">
-        <f t="shared" ref="U8" si="10">Q8*1.25</f>
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="V8" s="5">
-        <f>R8*1.18</f>
-        <v>53.69</v>
+        <f>R8*1.1</f>
+        <v>50.050000000000004</v>
       </c>
       <c r="X8" s="5">
         <v>16.399999999999999</v>
@@ -1806,47 +1825,47 @@
       </c>
       <c r="AD8" s="5">
         <f>SUM(S8:V8)</f>
-        <v>191.19</v>
+        <v>183.55</v>
       </c>
       <c r="AE8" s="5">
-        <f>AD8*1.17</f>
-        <v>223.69229999999999</v>
+        <f>AD8*1.12</f>
+        <v>205.57600000000002</v>
       </c>
       <c r="AF8" s="5">
-        <f>AE8*1.11</f>
-        <v>248.29845300000002</v>
+        <f>AE8*1.09</f>
+        <v>224.07784000000004</v>
       </c>
       <c r="AG8" s="5">
-        <f>AF8*1.07</f>
-        <v>265.67934471000007</v>
+        <f>AF8*1.06</f>
+        <v>237.52251040000004</v>
       </c>
       <c r="AH8" s="5">
         <f>AG8*1.04</f>
-        <v>276.30651849840007</v>
+        <v>247.02341081600005</v>
       </c>
       <c r="AI8" s="5">
         <f>AH8*1.03</f>
-        <v>284.59571405335208</v>
+        <v>254.43411314048006</v>
       </c>
       <c r="AJ8" s="5">
         <f>AI8*1.02</f>
-        <v>290.28762833441914</v>
+        <v>259.52279540328965</v>
       </c>
       <c r="AK8" s="5">
         <f>AJ8*1.01</f>
-        <v>293.19050461776334</v>
+        <v>262.11802335732256</v>
       </c>
       <c r="AL8" s="5">
-        <f t="shared" ref="AL8:AN8" si="11">AK8*1.01</f>
-        <v>296.12240966394097</v>
+        <f t="shared" ref="AL8:AN8" si="9">AK8*1.01</f>
+        <v>264.73920359089578</v>
       </c>
       <c r="AM8" s="5">
-        <f t="shared" si="11"/>
-        <v>299.08363376058037</v>
+        <f t="shared" si="9"/>
+        <v>267.38659562680476</v>
       </c>
       <c r="AN8" s="5">
-        <f t="shared" si="11"/>
-        <v>302.07447009818617</v>
+        <f t="shared" si="9"/>
+        <v>270.06046158307282</v>
       </c>
     </row>
     <row r="9" spans="2:139" x14ac:dyDescent="0.3">
@@ -1854,152 +1873,152 @@
         <v>17</v>
       </c>
       <c r="C9" s="5">
-        <f t="shared" ref="C9:R9" si="12">SUM(C6:C8)</f>
+        <f t="shared" ref="C9:R9" si="10">SUM(C6:C8)</f>
         <v>53.8</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>43.1</v>
       </c>
       <c r="E9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>74.2</v>
       </c>
       <c r="F9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>70.400000000000006</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>71.599999999999994</v>
       </c>
       <c r="H9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>79.599999999999994</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>89.9</v>
       </c>
       <c r="J9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>94.2</v>
       </c>
       <c r="K9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>92.6</v>
       </c>
       <c r="L9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>97.8</v>
       </c>
       <c r="M9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>106</v>
       </c>
       <c r="N9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>105.60000000000001</v>
       </c>
       <c r="O9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>105.9</v>
       </c>
       <c r="P9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>112.3</v>
       </c>
       <c r="Q9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>126.9</v>
       </c>
       <c r="R9" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v>136.69999999999999</v>
       </c>
       <c r="S9" s="5">
-        <f t="shared" ref="S9" si="13">SUM(S6:S8)</f>
+        <f t="shared" ref="S9" si="11">SUM(S6:S8)</f>
         <v>140.60000000000002</v>
       </c>
       <c r="T9" s="5">
-        <f t="shared" ref="T9" si="14">SUM(T6:T8)</f>
+        <f t="shared" ref="T9" si="12">SUM(T6:T8)</f>
         <v>149.30000000000001</v>
       </c>
       <c r="U9" s="5">
-        <f t="shared" ref="U9" si="15">SUM(U6:U8)</f>
-        <v>155.0274</v>
+        <f t="shared" ref="U9" si="13">SUM(U6:U8)</f>
+        <v>161.80000000000001</v>
       </c>
       <c r="V9" s="5">
-        <f t="shared" ref="V9" si="16">SUM(V6:V8)</f>
-        <v>165.8236</v>
+        <f t="shared" ref="V9" si="14">SUM(V6:V8)</f>
+        <v>174.87000000000003</v>
       </c>
       <c r="X9" s="5">
-        <f t="shared" ref="X9:AD9" si="17">SUM(X6:X8)</f>
+        <f t="shared" ref="X9:AD9" si="15">SUM(X6:X8)</f>
         <v>63</v>
       </c>
       <c r="Y9" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>131.69999999999999</v>
       </c>
       <c r="Z9" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>241.5</v>
       </c>
       <c r="AA9" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>335.3</v>
       </c>
       <c r="AB9" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>402</v>
       </c>
       <c r="AC9" s="5">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>481.8</v>
       </c>
       <c r="AD9" s="5">
-        <f t="shared" si="17"/>
-        <v>610.75099999999998</v>
+        <f t="shared" si="15"/>
+        <v>626.56999999999994</v>
       </c>
       <c r="AE9" s="5">
-        <f t="shared" ref="AE9" si="18">SUM(AE6:AE8)</f>
-        <v>713.16959999999995</v>
+        <f t="shared" ref="AE9" si="16">SUM(AE6:AE8)</f>
+        <v>735.77499999999998</v>
       </c>
       <c r="AF9" s="5">
-        <f t="shared" ref="AF9" si="19">SUM(AF6:AF8)</f>
-        <v>793.59677939999995</v>
+        <f t="shared" ref="AF9" si="17">SUM(AF6:AF8)</f>
+        <v>822.32650000000001</v>
       </c>
       <c r="AG9" s="5">
-        <f t="shared" ref="AG9" si="20">SUM(AG6:AG8)</f>
-        <v>856.79483367000012</v>
+        <f t="shared" ref="AG9" si="18">SUM(AG6:AG8)</f>
+        <v>869.19480999999996</v>
       </c>
       <c r="AH9" s="5">
-        <f t="shared" ref="AH9" si="21">SUM(AH6:AH8)</f>
-        <v>901.10939529840016</v>
+        <f t="shared" ref="AH9" si="19">SUM(AH6:AH8)</f>
+        <v>904.85071865000009</v>
       </c>
       <c r="AI9" s="5">
-        <f t="shared" ref="AI9" si="22">SUM(AI6:AI8)</f>
-        <v>937.34854808215209</v>
+        <f t="shared" ref="AI9" si="20">SUM(AI6:AI8)</f>
+        <v>941.27705502200001</v>
       </c>
       <c r="AJ9" s="5">
-        <f t="shared" ref="AJ9" si="23">SUM(AJ6:AJ8)</f>
-        <v>964.04939152282236</v>
+        <f t="shared" ref="AJ9" si="21">SUM(AJ6:AJ8)</f>
+        <v>968.12122012044006</v>
       </c>
       <c r="AK9" s="5">
-        <f t="shared" ref="AK9" si="24">SUM(AK6:AK8)</f>
-        <v>986.75083169076129</v>
+        <f t="shared" ref="AK9" si="22">SUM(AK6:AK8)</f>
+        <v>991.26322264722603</v>
       </c>
       <c r="AL9" s="5">
-        <f t="shared" ref="AL9" si="25">SUM(AL6:AL8)</f>
-        <v>1010.1934383302669</v>
+        <f t="shared" ref="AL9" si="23">SUM(AL6:AL8)</f>
+        <v>1015.1608532489279</v>
       </c>
       <c r="AM9" s="5">
-        <f t="shared" ref="AM9" si="26">SUM(AM6:AM8)</f>
-        <v>1034.4075528046942</v>
+        <f t="shared" ref="AM9" si="24">SUM(AM6:AM8)</f>
+        <v>1039.8449019794446</v>
       </c>
       <c r="AN9" s="5">
-        <f t="shared" ref="AN9" si="27">SUM(AN6:AN8)</f>
-        <v>1059.4249108178667</v>
+        <f t="shared" ref="AN9" si="25">SUM(AN6:AN8)</f>
+        <v>1065.3475689492848</v>
       </c>
     </row>
     <row r="10" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2007,152 +2026,152 @@
         <v>18</v>
       </c>
       <c r="C10" s="8">
-        <f t="shared" ref="C10:R10" si="28">C5-C9</f>
+        <f t="shared" ref="C10:R10" si="26">C5-C9</f>
         <v>-13.399999999999999</v>
       </c>
       <c r="D10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>-0.40000000000000568</v>
       </c>
       <c r="E10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>-28.700000000000003</v>
       </c>
       <c r="F10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>-17.400000000000006</v>
       </c>
       <c r="G10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>-11.899999999999991</v>
       </c>
       <c r="H10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>-15.099999999999994</v>
       </c>
       <c r="I10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>-20.100000000000009</v>
       </c>
       <c r="J10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>-18.200000000000003</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>-8.3999999999999915</v>
       </c>
       <c r="L10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>-4.7999999999999972</v>
       </c>
       <c r="M10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>-4.7000000000000028</v>
       </c>
       <c r="N10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>4.7999999999999972</v>
       </c>
       <c r="O10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>16.499999999999986</v>
       </c>
       <c r="P10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>18.700000000000003</v>
       </c>
       <c r="Q10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>13.499999999999972</v>
       </c>
       <c r="R10" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="26"/>
         <v>14</v>
       </c>
       <c r="S10" s="8">
-        <f t="shared" ref="S10" si="29">S5-S9</f>
+        <f t="shared" ref="S10" si="27">S5-S9</f>
         <v>23.499999999999972</v>
       </c>
       <c r="T10" s="8">
-        <f t="shared" ref="T10" si="30">T5-T9</f>
+        <f t="shared" ref="T10" si="28">T5-T9</f>
         <v>33.300000000000011</v>
       </c>
       <c r="U10" s="8">
-        <f t="shared" ref="U10" si="31">U5-U9</f>
-        <v>36.416999999999973</v>
+        <f t="shared" ref="U10" si="29">U5-U9</f>
+        <v>35.099999999999966</v>
       </c>
       <c r="V10" s="8">
-        <f t="shared" ref="V10" si="32">V5-V9</f>
-        <v>35.078000000000003</v>
+        <f t="shared" ref="V10" si="30">V5-V9</f>
+        <v>20.379999999999967</v>
       </c>
       <c r="X10" s="8">
-        <f t="shared" ref="X10:AD10" si="33">X5-X9</f>
+        <f t="shared" ref="X10:AD10" si="31">X5-X9</f>
         <v>-12.900000000000006</v>
       </c>
       <c r="Y10" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>-16</v>
       </c>
       <c r="Z10" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>-59.900000000000034</v>
       </c>
       <c r="AA10" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>-65.299999999999955</v>
       </c>
       <c r="AB10" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>-13.099999999999966</v>
       </c>
       <c r="AC10" s="8">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
         <v>62.699999999999989</v>
       </c>
       <c r="AD10" s="8">
-        <f t="shared" si="33"/>
-        <v>128.29499999999985</v>
+        <f t="shared" si="31"/>
+        <v>112.28000000000009</v>
       </c>
       <c r="AE10" s="8">
-        <f t="shared" ref="AE10" si="34">AE5-AE9</f>
-        <v>227.98368000000005</v>
+        <f t="shared" ref="AE10" si="32">AE5-AE9</f>
+        <v>178.08375000000001</v>
       </c>
       <c r="AF10" s="8">
-        <f t="shared" ref="AF10" si="35">AF5-AF9</f>
-        <v>354.61022219999984</v>
+        <f t="shared" ref="AF10" si="33">AF5-AF9</f>
+        <v>274.30399999999997</v>
       </c>
       <c r="AG10" s="8">
-        <f t="shared" ref="AG10" si="36">AG5-AG9</f>
-        <v>463.64321816999973</v>
+        <f t="shared" ref="AG10" si="34">AG5-AG9</f>
+        <v>391.93026499999996</v>
       </c>
       <c r="AH10" s="8">
-        <f t="shared" ref="AH10" si="37">AH5-AH9</f>
-        <v>551.37246172559958</v>
+        <f t="shared" ref="AH10" si="35">AH5-AH9</f>
+        <v>482.38686384999983</v>
       </c>
       <c r="AI10" s="8">
-        <f t="shared" ref="AI10" si="38">AI5-AI9</f>
-        <v>631.33185750376765</v>
+        <f t="shared" ref="AI10" si="36">AI5-AI9</f>
+        <v>556.93953407799995</v>
       </c>
       <c r="AJ10" s="8">
-        <f t="shared" ref="AJ10" si="39">AJ5-AJ9</f>
-        <v>698.75183839825263</v>
+        <f t="shared" ref="AJ10" si="37">AJ5-AJ9</f>
+        <v>619.98836432555981</v>
       </c>
       <c r="AK10" s="8">
-        <f t="shared" ref="AK10" si="40">AK5-AK9</f>
-        <v>759.19045972636764</v>
+        <f t="shared" ref="AK10" si="38">AK5-AK9</f>
+        <v>676.25184102107369</v>
       </c>
       <c r="AL10" s="8">
-        <f t="shared" ref="AL10" si="41">AL5-AL9</f>
-        <v>823.04491765771854</v>
+        <f t="shared" ref="AL10" si="39">AL5-AL9</f>
+        <v>735.72996360278717</v>
       </c>
       <c r="AM10" s="8">
-        <f t="shared" ref="AM10" si="42">AM5-AM9</f>
-        <v>890.49272098269057</v>
+        <f t="shared" ref="AM10" si="40">AM5-AM9</f>
+        <v>798.59045571485603</v>
       </c>
       <c r="AN10" s="8">
-        <f t="shared" ref="AN10" si="43">AN5-AN9</f>
-        <v>961.72037665888729</v>
+        <f t="shared" ref="AN10" si="41">AN5-AN9</f>
+        <v>865.00955662973115</v>
       </c>
     </row>
     <row r="11" spans="2:139" x14ac:dyDescent="0.3">
@@ -2214,7 +2233,7 @@
         <v>-1.7</v>
       </c>
       <c r="U11" s="5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="V11" s="5">
         <v>1</v>
@@ -2243,47 +2262,47 @@
       </c>
       <c r="AD11" s="5">
         <f>SUM(S11:V11)</f>
-        <v>-0.70000000000000018</v>
+        <v>-1.2000000000000002</v>
       </c>
       <c r="AE11" s="5">
         <f>AD11*1.05</f>
-        <v>-0.73500000000000021</v>
+        <v>-1.2600000000000002</v>
       </c>
       <c r="AF11" s="5">
-        <f t="shared" ref="AF11:AN11" si="44">AE11*1.05</f>
-        <v>-0.77175000000000027</v>
+        <f t="shared" ref="AF11:AN11" si="42">AE11*1.05</f>
+        <v>-1.3230000000000004</v>
       </c>
       <c r="AG11" s="5">
-        <f t="shared" si="44"/>
-        <v>-0.81033750000000027</v>
+        <f t="shared" si="42"/>
+        <v>-1.3891500000000006</v>
       </c>
       <c r="AH11" s="5">
-        <f t="shared" si="44"/>
-        <v>-0.85085437500000027</v>
+        <f t="shared" si="42"/>
+        <v>-1.4586075000000007</v>
       </c>
       <c r="AI11" s="5">
-        <f t="shared" si="44"/>
-        <v>-0.89339709375000032</v>
+        <f t="shared" si="42"/>
+        <v>-1.5315378750000008</v>
       </c>
       <c r="AJ11" s="5">
-        <f t="shared" si="44"/>
-        <v>-0.93806694843750038</v>
+        <f t="shared" si="42"/>
+        <v>-1.608114768750001</v>
       </c>
       <c r="AK11" s="5">
-        <f t="shared" si="44"/>
-        <v>-0.98497029585937546</v>
+        <f t="shared" si="42"/>
+        <v>-1.6885205071875011</v>
       </c>
       <c r="AL11" s="5">
-        <f t="shared" si="44"/>
-        <v>-1.0342188106523442</v>
+        <f t="shared" si="42"/>
+        <v>-1.7729465325468763</v>
       </c>
       <c r="AM11" s="5">
-        <f t="shared" si="44"/>
-        <v>-1.0859297511849615</v>
+        <f t="shared" si="42"/>
+        <v>-1.8615938591742203</v>
       </c>
       <c r="AN11" s="5">
-        <f t="shared" si="44"/>
-        <v>-1.1402262387442097</v>
+        <f t="shared" si="42"/>
+        <v>-1.9546735521329313</v>
       </c>
     </row>
     <row r="12" spans="2:139" x14ac:dyDescent="0.3">
@@ -2345,12 +2364,11 @@
         <v>-11.4</v>
       </c>
       <c r="U12" s="5">
-        <f t="shared" ref="U12:V12" si="45">Q12*1.05</f>
-        <v>-11.76</v>
+        <v>-11.8</v>
       </c>
       <c r="V12" s="5">
-        <f t="shared" si="45"/>
-        <v>-11.234999999999999</v>
+        <f>R12*1.1</f>
+        <v>-11.77</v>
       </c>
       <c r="X12" s="5">
         <v>0</v>
@@ -2376,47 +2394,47 @@
       </c>
       <c r="AD12" s="5">
         <f>SUM(S12:V12)</f>
-        <v>-44.795000000000002</v>
+        <v>-45.370000000000005</v>
       </c>
       <c r="AE12" s="5">
         <f>AD12*1.05</f>
-        <v>-47.034750000000003</v>
+        <v>-47.638500000000008</v>
       </c>
       <c r="AF12" s="5">
-        <f t="shared" ref="AF12:AN12" si="46">AE12*1.05</f>
-        <v>-49.386487500000001</v>
+        <f t="shared" ref="AF12:AN12" si="43">AE12*1.05</f>
+        <v>-50.02042500000001</v>
       </c>
       <c r="AG12" s="5">
-        <f t="shared" si="46"/>
-        <v>-51.855811875000001</v>
+        <f t="shared" si="43"/>
+        <v>-52.521446250000011</v>
       </c>
       <c r="AH12" s="5">
-        <f t="shared" si="46"/>
-        <v>-54.448602468750003</v>
+        <f t="shared" si="43"/>
+        <v>-55.147518562500011</v>
       </c>
       <c r="AI12" s="5">
-        <f t="shared" si="46"/>
-        <v>-57.171032592187508</v>
+        <f t="shared" si="43"/>
+        <v>-57.904894490625011</v>
       </c>
       <c r="AJ12" s="5">
-        <f t="shared" si="46"/>
-        <v>-60.029584221796888</v>
+        <f t="shared" si="43"/>
+        <v>-60.800139215156264</v>
       </c>
       <c r="AK12" s="5">
-        <f t="shared" si="46"/>
-        <v>-63.031063432886732</v>
+        <f t="shared" si="43"/>
+        <v>-63.840146175914079</v>
       </c>
       <c r="AL12" s="5">
-        <f t="shared" si="46"/>
-        <v>-66.182616604531077</v>
+        <f t="shared" si="43"/>
+        <v>-67.032153484709781</v>
       </c>
       <c r="AM12" s="5">
-        <f t="shared" si="46"/>
-        <v>-69.491747434757627</v>
+        <f t="shared" si="43"/>
+        <v>-70.383761158945276</v>
       </c>
       <c r="AN12" s="5">
-        <f t="shared" si="46"/>
-        <v>-72.96633480649551</v>
+        <f t="shared" si="43"/>
+        <v>-73.902949216892537</v>
       </c>
     </row>
     <row r="13" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2424,152 +2442,152 @@
         <v>20</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:R13" si="47">C10-C11-C12</f>
+        <f t="shared" ref="C13:R13" si="44">C10-C11-C12</f>
         <v>-13.399999999999999</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>-0.1000000000000057</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>-28.900000000000002</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>-17.400000000000006</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>-12.199999999999992</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>-14.999999999999995</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>-18.300000000000008</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>-13.200000000000003</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>-2.5999999999999925</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>2.400000000000003</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>2.8999999999999968</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>15.199999999999998</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>25.899999999999984</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>28.700000000000003</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>25.299999999999969</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" si="47"/>
+        <f t="shared" si="44"/>
         <v>22.5</v>
       </c>
       <c r="S13" s="8">
-        <f t="shared" ref="S13" si="48">S10-S11-S12</f>
+        <f t="shared" ref="S13" si="45">S10-S11-S12</f>
         <v>34.89999999999997</v>
       </c>
       <c r="T13" s="8">
-        <f t="shared" ref="T13" si="49">T10-T11-T12</f>
+        <f t="shared" ref="T13" si="46">T10-T11-T12</f>
         <v>46.400000000000013</v>
       </c>
       <c r="U13" s="8">
-        <f t="shared" ref="U13" si="50">U10-U11-U12</f>
-        <v>47.176999999999971</v>
+        <f t="shared" ref="U13" si="47">U10-U11-U12</f>
+        <v>46.399999999999963</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" ref="V13" si="51">V10-V11-V12</f>
-        <v>45.313000000000002</v>
+        <f t="shared" ref="V13" si="48">V10-V11-V12</f>
+        <v>31.149999999999967</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" ref="X13:AE13" si="52">X10-X11-X12</f>
+        <f t="shared" ref="X13:AE13" si="49">X10-X11-X12</f>
         <v>-12.300000000000006</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>-15.7</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>-59.800000000000033</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>-58.69999999999996</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>17.900000000000034</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" si="52"/>
+        <f t="shared" si="49"/>
         <v>102.39999999999998</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="52"/>
-        <v>173.78999999999985</v>
+        <f t="shared" si="49"/>
+        <v>158.85000000000008</v>
       </c>
       <c r="AE13" s="8">
-        <f t="shared" si="52"/>
-        <v>275.75343000000009</v>
+        <f t="shared" si="49"/>
+        <v>226.98225000000002</v>
       </c>
       <c r="AF13" s="8">
-        <f t="shared" ref="AF13" si="53">AF10-AF11-AF12</f>
-        <v>404.76845969999982</v>
+        <f t="shared" ref="AF13" si="50">AF10-AF11-AF12</f>
+        <v>325.64742499999994</v>
       </c>
       <c r="AG13" s="8">
-        <f t="shared" ref="AG13" si="54">AG10-AG11-AG12</f>
-        <v>516.30936754499976</v>
+        <f t="shared" ref="AG13" si="51">AG10-AG11-AG12</f>
+        <v>445.84086124999993</v>
       </c>
       <c r="AH13" s="8">
-        <f t="shared" ref="AH13" si="55">AH10-AH11-AH12</f>
-        <v>606.6719185693496</v>
+        <f t="shared" ref="AH13" si="52">AH10-AH11-AH12</f>
+        <v>538.99298991249987</v>
       </c>
       <c r="AI13" s="8">
-        <f t="shared" ref="AI13" si="56">AI10-AI11-AI12</f>
-        <v>689.39628718970516</v>
+        <f t="shared" ref="AI13" si="53">AI10-AI11-AI12</f>
+        <v>616.37596644362497</v>
       </c>
       <c r="AJ13" s="8">
-        <f t="shared" ref="AJ13" si="57">AJ10-AJ11-AJ12</f>
-        <v>759.71948956848701</v>
+        <f t="shared" ref="AJ13" si="54">AJ10-AJ11-AJ12</f>
+        <v>682.39661830946613</v>
       </c>
       <c r="AK13" s="8">
-        <f t="shared" ref="AK13" si="58">AK10-AK11-AK12</f>
-        <v>823.20649345511379</v>
+        <f t="shared" ref="AK13" si="55">AK10-AK11-AK12</f>
+        <v>741.78050770417531</v>
       </c>
       <c r="AL13" s="8">
-        <f t="shared" ref="AL13" si="59">AL10-AL11-AL12</f>
-        <v>890.26175307290191</v>
+        <f t="shared" ref="AL13" si="56">AL10-AL11-AL12</f>
+        <v>804.53506362004373</v>
       </c>
       <c r="AM13" s="8">
-        <f t="shared" ref="AM13" si="60">AM10-AM11-AM12</f>
-        <v>961.07039816863312</v>
+        <f t="shared" ref="AM13" si="57">AM10-AM11-AM12</f>
+        <v>870.83581073297557</v>
       </c>
       <c r="AN13" s="8">
-        <f t="shared" ref="AN13" si="61">AN10-AN11-AN12</f>
-        <v>1035.826937704127</v>
+        <f t="shared" ref="AN13" si="58">AN10-AN11-AN12</f>
+        <v>940.86717939875666</v>
       </c>
     </row>
     <row r="14" spans="2:139" x14ac:dyDescent="0.3">
@@ -2631,12 +2649,11 @@
         <v>1.7</v>
       </c>
       <c r="U14" s="5">
-        <f t="shared" ref="U14:V14" si="62">U13*0.15</f>
-        <v>7.0765499999999957</v>
+        <v>2</v>
       </c>
       <c r="V14" s="5">
-        <f t="shared" si="62"/>
-        <v>6.7969499999999998</v>
+        <f t="shared" ref="V14" si="59">V13*0.15</f>
+        <v>4.672499999999995</v>
       </c>
       <c r="X14" s="5">
         <v>0</v>
@@ -2662,47 +2679,47 @@
       </c>
       <c r="AD14" s="5">
         <f>SUM(S14:V14)</f>
-        <v>15.473499999999994</v>
+        <v>8.2724999999999937</v>
       </c>
       <c r="AE14" s="5">
         <f>AE13*0.15</f>
-        <v>41.363014500000013</v>
+        <v>34.047337500000005</v>
       </c>
       <c r="AF14" s="5">
-        <f t="shared" ref="AF14:AN14" si="63">AF13*0.15</f>
-        <v>60.715268954999971</v>
+        <f t="shared" ref="AF14:AN14" si="60">AF13*0.15</f>
+        <v>48.847113749999991</v>
       </c>
       <c r="AG14" s="5">
-        <f t="shared" si="63"/>
-        <v>77.446405131749955</v>
+        <f t="shared" si="60"/>
+        <v>66.876129187499984</v>
       </c>
       <c r="AH14" s="5">
-        <f t="shared" si="63"/>
-        <v>91.000787785402437</v>
+        <f t="shared" si="60"/>
+        <v>80.848948486874974</v>
       </c>
       <c r="AI14" s="5">
-        <f t="shared" si="63"/>
-        <v>103.40944307845577</v>
+        <f t="shared" si="60"/>
+        <v>92.456394966543741</v>
       </c>
       <c r="AJ14" s="5">
-        <f t="shared" si="63"/>
-        <v>113.95792343527305</v>
+        <f t="shared" si="60"/>
+        <v>102.35949274641992</v>
       </c>
       <c r="AK14" s="5">
-        <f t="shared" si="63"/>
-        <v>123.48097401826706</v>
+        <f t="shared" si="60"/>
+        <v>111.2670761556263</v>
       </c>
       <c r="AL14" s="5">
-        <f t="shared" si="63"/>
-        <v>133.53926296093528</v>
+        <f t="shared" si="60"/>
+        <v>120.68025954300656</v>
       </c>
       <c r="AM14" s="5">
-        <f t="shared" si="63"/>
-        <v>144.16055972529497</v>
+        <f t="shared" si="60"/>
+        <v>130.62537160994634</v>
       </c>
       <c r="AN14" s="5">
-        <f t="shared" si="63"/>
-        <v>155.37404065561904</v>
+        <f t="shared" si="60"/>
+        <v>141.13007690981348</v>
       </c>
     </row>
     <row r="15" spans="2:139" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2710,548 +2727,548 @@
         <v>22</v>
       </c>
       <c r="C15" s="8">
-        <f t="shared" ref="C15:R15" si="64">C13-C14</f>
+        <f t="shared" ref="C15:R15" si="61">C13-C14</f>
         <v>-13.399999999999999</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-0.1000000000000057</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-29.000000000000004</v>
       </c>
       <c r="F15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-17.500000000000007</v>
       </c>
       <c r="G15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-12.199999999999992</v>
       </c>
       <c r="H15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-15.099999999999994</v>
       </c>
       <c r="I15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-18.400000000000009</v>
       </c>
       <c r="J15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-13.900000000000002</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>-2.4999999999999925</v>
       </c>
       <c r="L15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>3.7000000000000028</v>
       </c>
       <c r="M15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>2.7999999999999967</v>
       </c>
       <c r="N15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>12.199999999999998</v>
       </c>
       <c r="O15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>26.999999999999986</v>
       </c>
       <c r="P15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>24.300000000000004</v>
       </c>
       <c r="Q15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>23.299999999999969</v>
       </c>
       <c r="R15" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="61"/>
         <v>14.1</v>
       </c>
       <c r="S15" s="8">
-        <f t="shared" ref="S15" si="65">S13-S14</f>
+        <f t="shared" ref="S15" si="62">S13-S14</f>
         <v>34.999999999999972</v>
       </c>
       <c r="T15" s="8">
-        <f t="shared" ref="T15" si="66">T13-T14</f>
+        <f t="shared" ref="T15" si="63">T13-T14</f>
         <v>44.70000000000001</v>
       </c>
       <c r="U15" s="8">
-        <f t="shared" ref="U15" si="67">U13-U14</f>
-        <v>40.100449999999974</v>
+        <f t="shared" ref="U15" si="64">U13-U14</f>
+        <v>44.399999999999963</v>
       </c>
       <c r="V15" s="8">
-        <f t="shared" ref="V15" si="68">V13-V14</f>
-        <v>38.51605</v>
+        <f t="shared" ref="V15" si="65">V13-V14</f>
+        <v>26.477499999999971</v>
       </c>
       <c r="X15" s="8">
-        <f t="shared" ref="X15:AE15" si="69">X13-X14</f>
+        <f t="shared" ref="X15:AE15" si="66">X13-X14</f>
         <v>-12.300000000000006</v>
       </c>
       <c r="Y15" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>-15.799999999999999</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>-60.000000000000036</v>
       </c>
       <c r="AA15" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>-59.599999999999959</v>
       </c>
       <c r="AB15" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>16.200000000000035</v>
       </c>
       <c r="AC15" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="66"/>
         <v>88.699999999999974</v>
       </c>
       <c r="AD15" s="8">
-        <f t="shared" si="69"/>
-        <v>158.31649999999985</v>
+        <f t="shared" si="66"/>
+        <v>150.5775000000001</v>
       </c>
       <c r="AE15" s="8">
-        <f t="shared" si="69"/>
-        <v>234.39041550000007</v>
+        <f t="shared" si="66"/>
+        <v>192.93491250000002</v>
       </c>
       <c r="AF15" s="8">
-        <f t="shared" ref="AF15" si="70">AF13-AF14</f>
-        <v>344.05319074499982</v>
+        <f t="shared" ref="AF15" si="67">AF13-AF14</f>
+        <v>276.80031124999994</v>
       </c>
       <c r="AG15" s="8">
-        <f t="shared" ref="AG15" si="71">AG13-AG14</f>
-        <v>438.86296241324982</v>
+        <f t="shared" ref="AG15" si="68">AG13-AG14</f>
+        <v>378.96473206249993</v>
       </c>
       <c r="AH15" s="8">
-        <f t="shared" ref="AH15" si="72">AH13-AH14</f>
-        <v>515.67113078394721</v>
+        <f t="shared" ref="AH15" si="69">AH13-AH14</f>
+        <v>458.14404142562489</v>
       </c>
       <c r="AI15" s="8">
-        <f t="shared" ref="AI15" si="73">AI13-AI14</f>
-        <v>585.98684411124941</v>
+        <f t="shared" ref="AI15" si="70">AI13-AI14</f>
+        <v>523.91957147708126</v>
       </c>
       <c r="AJ15" s="8">
-        <f t="shared" ref="AJ15" si="74">AJ13-AJ14</f>
-        <v>645.76156613321393</v>
+        <f t="shared" ref="AJ15" si="71">AJ13-AJ14</f>
+        <v>580.03712556304617</v>
       </c>
       <c r="AK15" s="8">
-        <f t="shared" ref="AK15" si="75">AK13-AK14</f>
-        <v>699.72551943684675</v>
+        <f t="shared" ref="AK15" si="72">AK13-AK14</f>
+        <v>630.51343154854897</v>
       </c>
       <c r="AL15" s="8">
-        <f t="shared" ref="AL15" si="76">AL13-AL14</f>
-        <v>756.72249011196664</v>
+        <f t="shared" ref="AL15" si="73">AL13-AL14</f>
+        <v>683.85480407703722</v>
       </c>
       <c r="AM15" s="8">
-        <f t="shared" ref="AM15" si="77">AM13-AM14</f>
-        <v>816.90983844333812</v>
+        <f t="shared" ref="AM15" si="74">AM13-AM14</f>
+        <v>740.21043912302923</v>
       </c>
       <c r="AN15" s="8">
-        <f t="shared" ref="AN15" si="78">AN13-AN14</f>
-        <v>880.45289704850791</v>
+        <f t="shared" ref="AN15" si="75">AN13-AN14</f>
+        <v>799.73710248894315</v>
       </c>
       <c r="AO15" s="1">
         <f>AN15*(1+$AR$21)</f>
-        <v>871.64836807802283</v>
+        <v>791.73973146405376</v>
       </c>
       <c r="AP15" s="1">
-        <f t="shared" ref="AP15:DA15" si="79">AO15*(1+$AR$21)</f>
-        <v>862.93188439724258</v>
+        <f t="shared" ref="AP15:DA15" si="76">AO15*(1+$AR$21)</f>
+        <v>783.82233414941322</v>
       </c>
       <c r="AQ15" s="1">
-        <f t="shared" si="79"/>
-        <v>854.30256555327014</v>
+        <f t="shared" si="76"/>
+        <v>775.98411080791914</v>
       </c>
       <c r="AR15" s="1">
-        <f t="shared" si="79"/>
-        <v>845.75953989773745</v>
+        <f t="shared" si="76"/>
+        <v>768.22426969983997</v>
       </c>
       <c r="AS15" s="1">
-        <f t="shared" si="79"/>
-        <v>837.30194449876012</v>
+        <f t="shared" si="76"/>
+        <v>760.54202700284156</v>
       </c>
       <c r="AT15" s="1">
-        <f t="shared" si="79"/>
-        <v>828.92892505377256</v>
+        <f t="shared" si="76"/>
+        <v>752.93660673281317</v>
       </c>
       <c r="AU15" s="1">
-        <f t="shared" si="79"/>
-        <v>820.6396358032348</v>
+        <f t="shared" si="76"/>
+        <v>745.40724066548501</v>
       </c>
       <c r="AV15" s="1">
-        <f t="shared" si="79"/>
-        <v>812.43323944520239</v>
+        <f t="shared" si="76"/>
+        <v>737.95316825883015</v>
       </c>
       <c r="AW15" s="1">
-        <f t="shared" si="79"/>
-        <v>804.30890705075035</v>
+        <f t="shared" si="76"/>
+        <v>730.57363657624182</v>
       </c>
       <c r="AX15" s="1">
-        <f t="shared" si="79"/>
-        <v>796.26581798024279</v>
+        <f t="shared" si="76"/>
+        <v>723.26790021047941</v>
       </c>
       <c r="AY15" s="1">
-        <f t="shared" si="79"/>
-        <v>788.30315980044031</v>
+        <f t="shared" si="76"/>
+        <v>716.03522120837465</v>
       </c>
       <c r="AZ15" s="1">
-        <f t="shared" si="79"/>
-        <v>780.42012820243588</v>
+        <f t="shared" si="76"/>
+        <v>708.87486899629084</v>
       </c>
       <c r="BA15" s="1">
-        <f t="shared" si="79"/>
-        <v>772.61592692041154</v>
+        <f t="shared" si="76"/>
+        <v>701.78612030632792</v>
       </c>
       <c r="BB15" s="1">
-        <f t="shared" si="79"/>
-        <v>764.88976765120742</v>
+        <f t="shared" si="76"/>
+        <v>694.76825910326465</v>
       </c>
       <c r="BC15" s="1">
-        <f t="shared" si="79"/>
-        <v>757.24086997469533</v>
+        <f t="shared" si="76"/>
+        <v>687.82057651223204</v>
       </c>
       <c r="BD15" s="1">
-        <f t="shared" si="79"/>
-        <v>749.66846127494841</v>
+        <f t="shared" si="76"/>
+        <v>680.94237074710975</v>
       </c>
       <c r="BE15" s="1">
-        <f t="shared" si="79"/>
-        <v>742.17177666219891</v>
+        <f t="shared" si="76"/>
+        <v>674.13294703963868</v>
       </c>
       <c r="BF15" s="1">
-        <f t="shared" si="79"/>
-        <v>734.7500588955769</v>
+        <f t="shared" si="76"/>
+        <v>667.39161756924227</v>
       </c>
       <c r="BG15" s="1">
-        <f t="shared" si="79"/>
-        <v>727.40255830662113</v>
+        <f t="shared" si="76"/>
+        <v>660.71770139354987</v>
       </c>
       <c r="BH15" s="1">
-        <f t="shared" si="79"/>
-        <v>720.12853272355494</v>
+        <f t="shared" si="76"/>
+        <v>654.11052437961439</v>
       </c>
       <c r="BI15" s="1">
-        <f t="shared" si="79"/>
-        <v>712.92724739631933</v>
+        <f t="shared" si="76"/>
+        <v>647.56941913581829</v>
       </c>
       <c r="BJ15" s="1">
-        <f t="shared" si="79"/>
-        <v>705.79797492235616</v>
+        <f t="shared" si="76"/>
+        <v>641.09372494446006</v>
       </c>
       <c r="BK15" s="1">
-        <f t="shared" si="79"/>
-        <v>698.73999517313257</v>
+        <f t="shared" si="76"/>
+        <v>634.68278769501546</v>
       </c>
       <c r="BL15" s="1">
-        <f t="shared" si="79"/>
-        <v>691.75259522140129</v>
+        <f t="shared" si="76"/>
+        <v>628.33595981806525</v>
       </c>
       <c r="BM15" s="1">
-        <f t="shared" si="79"/>
-        <v>684.83506926918733</v>
+        <f t="shared" si="76"/>
+        <v>622.05260021988454</v>
       </c>
       <c r="BN15" s="1">
-        <f t="shared" si="79"/>
-        <v>677.98671857649549</v>
+        <f t="shared" si="76"/>
+        <v>615.83207421768566</v>
       </c>
       <c r="BO15" s="1">
-        <f t="shared" si="79"/>
-        <v>671.20685139073055</v>
+        <f t="shared" si="76"/>
+        <v>609.67375347550876</v>
       </c>
       <c r="BP15" s="1">
-        <f t="shared" si="79"/>
-        <v>664.49478287682325</v>
+        <f t="shared" si="76"/>
+        <v>603.57701594075365</v>
       </c>
       <c r="BQ15" s="1">
-        <f t="shared" si="79"/>
-        <v>657.84983504805496</v>
+        <f t="shared" si="76"/>
+        <v>597.54124578134611</v>
       </c>
       <c r="BR15" s="1">
-        <f t="shared" si="79"/>
-        <v>651.27133669757438</v>
+        <f t="shared" si="76"/>
+        <v>591.56583332353262</v>
       </c>
       <c r="BS15" s="1">
-        <f t="shared" si="79"/>
-        <v>644.75862333059865</v>
+        <f t="shared" si="76"/>
+        <v>585.65017499029727</v>
       </c>
       <c r="BT15" s="1">
-        <f t="shared" si="79"/>
-        <v>638.31103709729268</v>
+        <f t="shared" si="76"/>
+        <v>579.79367324039424</v>
       </c>
       <c r="BU15" s="1">
-        <f t="shared" si="79"/>
-        <v>631.9279267263197</v>
+        <f t="shared" si="76"/>
+        <v>573.99573650799027</v>
       </c>
       <c r="BV15" s="1">
-        <f t="shared" si="79"/>
-        <v>625.60864745905644</v>
+        <f t="shared" si="76"/>
+        <v>568.25577914291034</v>
       </c>
       <c r="BW15" s="1">
-        <f t="shared" si="79"/>
-        <v>619.35256098446587</v>
+        <f t="shared" si="76"/>
+        <v>562.57322135148127</v>
       </c>
       <c r="BX15" s="1">
-        <f t="shared" si="79"/>
-        <v>613.15903537462123</v>
+        <f t="shared" si="76"/>
+        <v>556.9474891379665</v>
       </c>
       <c r="BY15" s="1">
-        <f t="shared" si="79"/>
-        <v>607.02744502087501</v>
+        <f t="shared" si="76"/>
+        <v>551.37801424658687</v>
       </c>
       <c r="BZ15" s="1">
-        <f t="shared" si="79"/>
-        <v>600.95717057066622</v>
+        <f t="shared" si="76"/>
+        <v>545.86423410412101</v>
       </c>
       <c r="CA15" s="1">
-        <f t="shared" si="79"/>
-        <v>594.94759886495956</v>
+        <f t="shared" si="76"/>
+        <v>540.40559176307977</v>
       </c>
       <c r="CB15" s="1">
-        <f t="shared" si="79"/>
-        <v>588.99812287630994</v>
+        <f t="shared" si="76"/>
+        <v>535.00153584544898</v>
       </c>
       <c r="CC15" s="1">
-        <f t="shared" si="79"/>
-        <v>583.10814164754686</v>
+        <f t="shared" si="76"/>
+        <v>529.65152048699451</v>
       </c>
       <c r="CD15" s="1">
-        <f t="shared" si="79"/>
-        <v>577.27706023107135</v>
+        <f t="shared" si="76"/>
+        <v>524.35500528212458</v>
       </c>
       <c r="CE15" s="1">
-        <f t="shared" si="79"/>
-        <v>571.5042896287606</v>
+        <f t="shared" si="76"/>
+        <v>519.11145522930337</v>
       </c>
       <c r="CF15" s="1">
-        <f t="shared" si="79"/>
-        <v>565.78924673247298</v>
+        <f t="shared" si="76"/>
+        <v>513.92034067701036</v>
       </c>
       <c r="CG15" s="1">
-        <f t="shared" si="79"/>
-        <v>560.13135426514827</v>
+        <f t="shared" si="76"/>
+        <v>508.78113727024027</v>
       </c>
       <c r="CH15" s="1">
-        <f t="shared" si="79"/>
-        <v>554.53004072249678</v>
+        <f t="shared" si="76"/>
+        <v>503.69332589753787</v>
       </c>
       <c r="CI15" s="1">
-        <f t="shared" si="79"/>
-        <v>548.98474031527178</v>
+        <f t="shared" si="76"/>
+        <v>498.65639263856247</v>
       </c>
       <c r="CJ15" s="1">
-        <f t="shared" si="79"/>
-        <v>543.4948929121191</v>
+        <f t="shared" si="76"/>
+        <v>493.66982871217681</v>
       </c>
       <c r="CK15" s="1">
-        <f t="shared" si="79"/>
-        <v>538.05994398299788</v>
+        <f t="shared" si="76"/>
+        <v>488.73313042505504</v>
       </c>
       <c r="CL15" s="1">
-        <f t="shared" si="79"/>
-        <v>532.67934454316787</v>
+        <f t="shared" si="76"/>
+        <v>483.84579912080449</v>
       </c>
       <c r="CM15" s="1">
-        <f t="shared" si="79"/>
-        <v>527.35255109773618</v>
+        <f t="shared" si="76"/>
+        <v>479.00734112959645</v>
       </c>
       <c r="CN15" s="1">
-        <f t="shared" si="79"/>
-        <v>522.0790255867588</v>
+        <f t="shared" si="76"/>
+        <v>474.21726771830049</v>
       </c>
       <c r="CO15" s="1">
-        <f t="shared" si="79"/>
-        <v>516.85823533089126</v>
+        <f t="shared" si="76"/>
+        <v>469.47509504111747</v>
       </c>
       <c r="CP15" s="1">
-        <f t="shared" si="79"/>
-        <v>511.68965297758234</v>
+        <f t="shared" si="76"/>
+        <v>464.78034409070631</v>
       </c>
       <c r="CQ15" s="1">
-        <f t="shared" si="79"/>
-        <v>506.57275644780651</v>
+        <f t="shared" si="76"/>
+        <v>460.13254064979924</v>
       </c>
       <c r="CR15" s="1">
-        <f t="shared" si="79"/>
-        <v>501.50702888332842</v>
+        <f t="shared" si="76"/>
+        <v>455.53121524330123</v>
       </c>
       <c r="CS15" s="1">
-        <f t="shared" si="79"/>
-        <v>496.49195859449515</v>
+        <f t="shared" si="76"/>
+        <v>450.9759030908682</v>
       </c>
       <c r="CT15" s="1">
-        <f t="shared" si="79"/>
-        <v>491.52703900855016</v>
+        <f t="shared" si="76"/>
+        <v>446.4661440599595</v>
       </c>
       <c r="CU15" s="1">
-        <f t="shared" si="79"/>
-        <v>486.61176861846468</v>
+        <f t="shared" si="76"/>
+        <v>442.00148261935988</v>
       </c>
       <c r="CV15" s="1">
-        <f t="shared" si="79"/>
-        <v>481.74565093228006</v>
+        <f t="shared" si="76"/>
+        <v>437.58146779316627</v>
       </c>
       <c r="CW15" s="1">
-        <f t="shared" si="79"/>
-        <v>476.92819442295723</v>
+        <f t="shared" si="76"/>
+        <v>433.20565311523461</v>
       </c>
       <c r="CX15" s="1">
-        <f t="shared" si="79"/>
-        <v>472.15891247872764</v>
+        <f t="shared" si="76"/>
+        <v>428.87359658408224</v>
       </c>
       <c r="CY15" s="1">
-        <f t="shared" si="79"/>
-        <v>467.43732335394037</v>
+        <f t="shared" si="76"/>
+        <v>424.58486061824141</v>
       </c>
       <c r="CZ15" s="1">
-        <f t="shared" si="79"/>
-        <v>462.76295012040094</v>
+        <f t="shared" si="76"/>
+        <v>420.33901201205902</v>
       </c>
       <c r="DA15" s="1">
-        <f t="shared" si="79"/>
-        <v>458.13532061919693</v>
+        <f t="shared" si="76"/>
+        <v>416.1356218919384</v>
       </c>
       <c r="DB15" s="1">
-        <f t="shared" ref="DB15:EI15" si="80">DA15*(1+$AR$21)</f>
-        <v>453.55396741300495</v>
+        <f t="shared" ref="DB15:EI15" si="77">DA15*(1+$AR$21)</f>
+        <v>411.97426567301903</v>
       </c>
       <c r="DC15" s="1">
-        <f t="shared" si="80"/>
-        <v>449.01842773887489</v>
+        <f t="shared" si="77"/>
+        <v>407.85452301628885</v>
       </c>
       <c r="DD15" s="1">
-        <f t="shared" si="80"/>
-        <v>444.52824346148611</v>
+        <f t="shared" si="77"/>
+        <v>403.77597778612596</v>
       </c>
       <c r="DE15" s="1">
-        <f t="shared" si="80"/>
-        <v>440.08296102687126</v>
+        <f t="shared" si="77"/>
+        <v>399.73821800826471</v>
       </c>
       <c r="DF15" s="1">
-        <f t="shared" si="80"/>
-        <v>435.68213141660254</v>
+        <f t="shared" si="77"/>
+        <v>395.74083582818207</v>
       </c>
       <c r="DG15" s="1">
-        <f t="shared" si="80"/>
-        <v>431.3253101024365</v>
+        <f t="shared" si="77"/>
+        <v>391.78342746990023</v>
       </c>
       <c r="DH15" s="1">
-        <f t="shared" si="80"/>
-        <v>427.01205700141213</v>
+        <f t="shared" si="77"/>
+        <v>387.8655931952012</v>
       </c>
       <c r="DI15" s="1">
-        <f t="shared" si="80"/>
-        <v>422.74193643139802</v>
+        <f t="shared" si="77"/>
+        <v>383.98693726324916</v>
       </c>
       <c r="DJ15" s="1">
-        <f t="shared" si="80"/>
-        <v>418.51451706708406</v>
+        <f t="shared" si="77"/>
+        <v>380.14706789061665</v>
       </c>
       <c r="DK15" s="1">
-        <f t="shared" si="80"/>
-        <v>414.32937189641319</v>
+        <f t="shared" si="77"/>
+        <v>376.34559721171047</v>
       </c>
       <c r="DL15" s="1">
-        <f t="shared" si="80"/>
-        <v>410.18607817744908</v>
+        <f t="shared" si="77"/>
+        <v>372.58214123959334</v>
       </c>
       <c r="DM15" s="1">
-        <f t="shared" si="80"/>
-        <v>406.08421739567456</v>
+        <f t="shared" si="77"/>
+        <v>368.85631982719741</v>
       </c>
       <c r="DN15" s="1">
-        <f t="shared" si="80"/>
-        <v>402.0233752217178</v>
+        <f t="shared" si="77"/>
+        <v>365.16775662892542</v>
       </c>
       <c r="DO15" s="1">
-        <f t="shared" si="80"/>
-        <v>398.00314146950063</v>
+        <f t="shared" si="77"/>
+        <v>361.51607906263615</v>
       </c>
       <c r="DP15" s="1">
-        <f t="shared" si="80"/>
-        <v>394.02311005480561</v>
+        <f t="shared" si="77"/>
+        <v>357.90091827200979</v>
       </c>
       <c r="DQ15" s="1">
-        <f t="shared" si="80"/>
-        <v>390.08287895425758</v>
+        <f t="shared" si="77"/>
+        <v>354.3219090892897</v>
       </c>
       <c r="DR15" s="1">
-        <f t="shared" si="80"/>
-        <v>386.18205016471501</v>
+        <f t="shared" si="77"/>
+        <v>350.77868999839683</v>
       </c>
       <c r="DS15" s="1">
-        <f t="shared" si="80"/>
-        <v>382.32022966306783</v>
+        <f t="shared" si="77"/>
+        <v>347.27090309841287</v>
       </c>
       <c r="DT15" s="1">
-        <f t="shared" si="80"/>
-        <v>378.49702736643718</v>
+        <f t="shared" si="77"/>
+        <v>343.79819406742877</v>
       </c>
       <c r="DU15" s="1">
-        <f t="shared" si="80"/>
-        <v>374.7120570927728</v>
+        <f t="shared" si="77"/>
+        <v>340.3602121267545</v>
       </c>
       <c r="DV15" s="1">
-        <f t="shared" si="80"/>
-        <v>370.96493652184506</v>
+        <f t="shared" si="77"/>
+        <v>336.95661000548694</v>
       </c>
       <c r="DW15" s="1">
-        <f t="shared" si="80"/>
-        <v>367.25528715662659</v>
+        <f t="shared" si="77"/>
+        <v>333.58704390543204</v>
       </c>
       <c r="DX15" s="1">
-        <f t="shared" si="80"/>
-        <v>363.58273428506033</v>
+        <f t="shared" si="77"/>
+        <v>330.25117346637774</v>
       </c>
       <c r="DY15" s="1">
-        <f t="shared" si="80"/>
-        <v>359.94690694220969</v>
+        <f t="shared" si="77"/>
+        <v>326.94866173171397</v>
       </c>
       <c r="DZ15" s="1">
-        <f t="shared" si="80"/>
-        <v>356.34743787278757</v>
+        <f t="shared" si="77"/>
+        <v>323.6791751143968</v>
       </c>
       <c r="EA15" s="1">
-        <f t="shared" si="80"/>
-        <v>352.78396349405966</v>
+        <f t="shared" si="77"/>
+        <v>320.44238336325282</v>
       </c>
       <c r="EB15" s="1">
-        <f t="shared" si="80"/>
-        <v>349.25612385911904</v>
+        <f t="shared" si="77"/>
+        <v>317.2379595296203</v>
       </c>
       <c r="EC15" s="1">
-        <f t="shared" si="80"/>
-        <v>345.76356262052786</v>
+        <f t="shared" si="77"/>
+        <v>314.06557993432409</v>
       </c>
       <c r="ED15" s="1">
-        <f t="shared" si="80"/>
-        <v>342.30592699432259</v>
+        <f t="shared" si="77"/>
+        <v>310.92492413498087</v>
       </c>
       <c r="EE15" s="1">
-        <f t="shared" si="80"/>
-        <v>338.88286772437937</v>
+        <f t="shared" si="77"/>
+        <v>307.81567489363107</v>
       </c>
       <c r="EF15" s="1">
-        <f t="shared" si="80"/>
-        <v>335.49403904713557</v>
+        <f t="shared" si="77"/>
+        <v>304.73751814469477</v>
       </c>
       <c r="EG15" s="1">
-        <f t="shared" si="80"/>
-        <v>332.1390986566642</v>
+        <f t="shared" si="77"/>
+        <v>301.69014296324781</v>
       </c>
       <c r="EH15" s="1">
-        <f t="shared" si="80"/>
-        <v>328.81770767009755</v>
+        <f t="shared" si="77"/>
+        <v>298.67324153361534</v>
       </c>
       <c r="EI15" s="1">
-        <f t="shared" si="80"/>
-        <v>325.52953059339654</v>
+        <f t="shared" si="77"/>
+        <v>295.68650911827916</v>
       </c>
     </row>
     <row r="16" spans="2:139" x14ac:dyDescent="0.3">
@@ -3314,10 +3331,12 @@
         <v>45.8</v>
       </c>
       <c r="U16" s="5">
-        <v>45.8</v>
+        <f>46.1</f>
+        <v>46.1</v>
       </c>
       <c r="V16" s="5">
-        <v>45.8</v>
+        <f>46.1</f>
+        <v>46.1</v>
       </c>
       <c r="X16" s="5">
         <v>44.9</v>
@@ -3338,37 +3357,48 @@
         <v>44.9</v>
       </c>
       <c r="AD16" s="5">
-        <v>45.8</v>
+        <f t="shared" ref="AD16:AN16" si="78">46.1</f>
+        <v>46.1</v>
       </c>
       <c r="AE16" s="5">
-        <v>45.8</v>
+        <f t="shared" si="78"/>
+        <v>46.1</v>
       </c>
       <c r="AF16" s="5">
-        <v>45.8</v>
+        <f t="shared" si="78"/>
+        <v>46.1</v>
       </c>
       <c r="AG16" s="5">
-        <v>45.8</v>
+        <f t="shared" si="78"/>
+        <v>46.1</v>
       </c>
       <c r="AH16" s="5">
-        <v>45.8</v>
+        <f t="shared" si="78"/>
+        <v>46.1</v>
       </c>
       <c r="AI16" s="5">
-        <v>45.8</v>
+        <f t="shared" si="78"/>
+        <v>46.1</v>
       </c>
       <c r="AJ16" s="5">
-        <v>45.8</v>
+        <f t="shared" si="78"/>
+        <v>46.1</v>
       </c>
       <c r="AK16" s="5">
-        <v>45.8</v>
+        <f t="shared" si="78"/>
+        <v>46.1</v>
       </c>
       <c r="AL16" s="5">
-        <v>45.8</v>
+        <f t="shared" si="78"/>
+        <v>46.1</v>
       </c>
       <c r="AM16" s="5">
-        <v>45.8</v>
+        <f t="shared" si="78"/>
+        <v>46.1</v>
       </c>
       <c r="AN16" s="5">
-        <v>45.8</v>
+        <f t="shared" si="78"/>
+        <v>46.1</v>
       </c>
     </row>
     <row r="17" spans="2:44" x14ac:dyDescent="0.3">
@@ -3376,152 +3406,152 @@
         <v>23</v>
       </c>
       <c r="C17" s="7">
-        <f t="shared" ref="C17:R17" si="81">C15/C16</f>
+        <f t="shared" ref="C17:R17" si="79">C15/C16</f>
         <v>-0.29844097995545654</v>
       </c>
       <c r="D17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>-2.2271714922050267E-3</v>
       </c>
       <c r="E17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>-0.64587973273942101</v>
       </c>
       <c r="F17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>-0.38975501113585764</v>
       </c>
       <c r="G17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>-0.27171492204899761</v>
       </c>
       <c r="H17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>-0.33630289532293978</v>
       </c>
       <c r="I17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>-0.40979955456570177</v>
       </c>
       <c r="J17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>-0.30957683741648112</v>
       </c>
       <c r="K17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>-5.5679287305122331E-2</v>
       </c>
       <c r="L17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>8.2405345211581355E-2</v>
       </c>
       <c r="M17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>6.236080178173712E-2</v>
       </c>
       <c r="N17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>0.27171492204899772</v>
       </c>
       <c r="O17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>0.60133630289532269</v>
       </c>
       <c r="P17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>0.5412026726057908</v>
       </c>
       <c r="Q17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>0.51893095768374098</v>
       </c>
       <c r="R17" s="7">
-        <f t="shared" si="81"/>
+        <f t="shared" si="79"/>
         <v>0.3140311804008909</v>
       </c>
       <c r="S17" s="7">
-        <f t="shared" ref="S17" si="82">S15/S16</f>
+        <f t="shared" ref="S17" si="80">S15/S16</f>
         <v>0.76923076923076861</v>
       </c>
       <c r="T17" s="7">
-        <f t="shared" ref="T17" si="83">T15/T16</f>
+        <f t="shared" ref="T17" si="81">T15/T16</f>
         <v>0.97598253275109204</v>
       </c>
       <c r="U17" s="7">
-        <f t="shared" ref="U17" si="84">U15/U16</f>
-        <v>0.87555567685589464</v>
+        <f t="shared" ref="U17" si="82">U15/U16</f>
+        <v>0.96312364425162611</v>
       </c>
       <c r="V17" s="7">
-        <f t="shared" ref="V17" si="85">V15/V16</f>
-        <v>0.84096179039301311</v>
+        <f t="shared" ref="V17" si="83">V15/V16</f>
+        <v>0.57434924078091043</v>
       </c>
       <c r="X17" s="7">
-        <f t="shared" ref="X17:AE17" si="86">X15/X16</f>
+        <f t="shared" ref="X17:AE17" si="84">X15/X16</f>
         <v>-0.2739420935412028</v>
       </c>
       <c r="Y17" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>-0.35189309576837413</v>
       </c>
       <c r="Z17" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>-1.3363028953229408</v>
       </c>
       <c r="AA17" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>-1.3273942093541193</v>
       </c>
       <c r="AB17" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>0.36080178173719457</v>
       </c>
       <c r="AC17" s="7">
-        <f t="shared" si="86"/>
+        <f t="shared" si="84"/>
         <v>1.9755011135857456</v>
       </c>
       <c r="AD17" s="7">
-        <f t="shared" si="86"/>
-        <v>3.4566921397379882</v>
+        <f t="shared" si="84"/>
+        <v>3.2663232104121498</v>
       </c>
       <c r="AE17" s="7">
-        <f t="shared" si="86"/>
-        <v>5.1176946615720542</v>
+        <f t="shared" si="84"/>
+        <v>4.1851390997830809</v>
       </c>
       <c r="AF17" s="7">
-        <f t="shared" ref="AF17" si="87">AF15/AF16</f>
-        <v>7.5120784005458479</v>
+        <f t="shared" ref="AF17" si="85">AF15/AF16</f>
+        <v>6.0043451464208228</v>
       </c>
       <c r="AG17" s="7">
-        <f t="shared" ref="AG17" si="88">AG15/AG16</f>
-        <v>9.5821607513810019</v>
+        <f t="shared" ref="AG17" si="86">AG15/AG16</f>
+        <v>8.2204931033080246</v>
       </c>
       <c r="AH17" s="7">
-        <f t="shared" ref="AH17" si="89">AH15/AH16</f>
-        <v>11.259194995282691</v>
+        <f t="shared" ref="AH17" si="87">AH15/AH16</f>
+        <v>9.9380486209463097</v>
       </c>
       <c r="AI17" s="7">
-        <f t="shared" ref="AI17" si="90">AI15/AI16</f>
-        <v>12.794472578848241</v>
+        <f t="shared" ref="AI17" si="88">AI15/AI16</f>
+        <v>11.364849706661198</v>
       </c>
       <c r="AJ17" s="7">
-        <f t="shared" ref="AJ17" si="91">AJ15/AJ16</f>
-        <v>14.099597513825632</v>
+        <f t="shared" ref="AJ17" si="89">AJ15/AJ16</f>
+        <v>12.582150229133322</v>
       </c>
       <c r="AK17" s="7">
-        <f t="shared" ref="AK17" si="92">AK15/AK16</f>
-        <v>15.277849769363467</v>
+        <f t="shared" ref="AK17" si="90">AK15/AK16</f>
+        <v>13.677080944653991</v>
       </c>
       <c r="AL17" s="7">
-        <f t="shared" ref="AL17" si="93">AL15/AL16</f>
-        <v>16.522325111614993</v>
+        <f t="shared" ref="AL17" si="91">AL15/AL16</f>
+        <v>14.834160609046361</v>
       </c>
       <c r="AM17" s="7">
-        <f t="shared" ref="AM17" si="94">AM15/AM16</f>
-        <v>17.836459354658039</v>
+        <f t="shared" ref="AM17" si="92">AM15/AM16</f>
+        <v>16.056625577506058</v>
       </c>
       <c r="AN17" s="7">
-        <f t="shared" ref="AN17" si="95">AN15/AN16</f>
-        <v>19.223862380971788</v>
+        <f t="shared" ref="AN17" si="93">AN15/AN16</f>
+        <v>17.347876409738461</v>
       </c>
     </row>
     <row r="19" spans="2:44" x14ac:dyDescent="0.3">
@@ -3533,47 +3563,47 @@
       <c r="E19" s="9"/>
       <c r="F19" s="9"/>
       <c r="G19" s="9">
-        <f t="shared" ref="G19:Q19" si="96">G3/C3-1</f>
+        <f t="shared" ref="G19:Q19" si="94">G3/C3-1</f>
         <v>0.46570397111913375</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.5034013605442178</v>
       </c>
       <c r="I19" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.51100628930817593</v>
       </c>
       <c r="J19" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.42191780821917813</v>
       </c>
       <c r="K19" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.42487684729064035</v>
       </c>
       <c r="L19" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.434389140271493</v>
       </c>
       <c r="M19" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.43184183142559829</v>
       </c>
       <c r="N19" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.4547206165703277</v>
       </c>
       <c r="O19" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.44857389801210013</v>
       </c>
       <c r="P19" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.40615141955835976</v>
       </c>
       <c r="Q19" s="9">
-        <f t="shared" si="96"/>
+        <f t="shared" si="94"/>
         <v>0.39970930232558133</v>
       </c>
       <c r="R19" s="9">
@@ -3581,36 +3611,36 @@
         <v>0.38807947019867539</v>
       </c>
       <c r="S19" s="9">
-        <f t="shared" ref="S19:V19" si="97">S3/O3-1</f>
+        <f t="shared" ref="S19:V19" si="95">S3/O3-1</f>
         <v>0.37649164677804303</v>
       </c>
       <c r="T19" s="9">
-        <f t="shared" si="97"/>
+        <f t="shared" si="95"/>
         <v>0.41503084688726855</v>
       </c>
       <c r="U19" s="9">
-        <f t="shared" si="97"/>
-        <v>0.39999999999999991</v>
+        <f t="shared" si="95"/>
+        <v>0.41069574247144347</v>
       </c>
       <c r="V19" s="9">
-        <f t="shared" si="97"/>
-        <v>0.35000000000000031</v>
+        <f t="shared" si="95"/>
+        <v>0.31202290076335881</v>
       </c>
       <c r="X19" s="9"/>
       <c r="Y19" s="9">
-        <f t="shared" ref="Y19" si="98">Y3/X3-1</f>
+        <f t="shared" ref="Y19" si="96">Y3/X3-1</f>
         <v>1.2838983050847457</v>
       </c>
       <c r="Z19" s="9">
-        <f t="shared" ref="Z19:AB19" si="99">Z3/Y3-1</f>
+        <f t="shared" ref="Z19:AB19" si="97">Z3/Y3-1</f>
         <v>0.55102040816326525</v>
       </c>
       <c r="AA19" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.47328548644338153</v>
       </c>
       <c r="AB19" s="9">
-        <f t="shared" si="99"/>
+        <f t="shared" si="97"/>
         <v>0.43734776725304458</v>
       </c>
       <c r="AC19" s="9">
@@ -3618,47 +3648,47 @@
         <v>0.40858595368103923</v>
       </c>
       <c r="AD19" s="9">
-        <f t="shared" ref="AD19:AN19" si="100">AD3/AC3-1</f>
-        <v>0.3843069108407966</v>
+        <f t="shared" ref="AD19:AN19" si="98">AD3/AC3-1</f>
+        <v>0.37642026467049861</v>
       </c>
       <c r="AE19" s="9">
-        <f t="shared" si="100"/>
-        <v>0.28000000000000003</v>
+        <f t="shared" si="98"/>
+        <v>0.25</v>
       </c>
       <c r="AF19" s="9">
-        <f t="shared" si="100"/>
-        <v>0.21999999999999997</v>
+        <f t="shared" si="98"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AG19" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>0.14999999999999991</v>
       </c>
       <c r="AH19" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="AI19" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AJ19" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AK19" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AL19" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AM19" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN19" s="9">
-        <f t="shared" si="100"/>
+        <f t="shared" si="98"/>
         <v>5.0000000000000044E-2</v>
       </c>
     </row>
@@ -3667,63 +3697,63 @@
         <v>46</v>
       </c>
       <c r="C20" s="9">
-        <f t="shared" ref="C20:Q20" si="101">C5/C3</f>
+        <f t="shared" ref="C20:Q20" si="99">C5/C3</f>
         <v>0.72924187725631773</v>
       </c>
       <c r="D20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.72619047619047616</v>
       </c>
       <c r="E20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.71540880503144655</v>
       </c>
       <c r="F20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.72602739726027399</v>
       </c>
       <c r="G20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.73522167487684731</v>
       </c>
       <c r="H20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.72963800904977372</v>
       </c>
       <c r="I20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.72632674297606659</v>
       </c>
       <c r="J20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.73217726396917149</v>
       </c>
       <c r="K20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.72774416594641311</v>
       </c>
       <c r="L20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.7334384858044164</v>
       </c>
       <c r="M20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.73619186046511631</v>
       </c>
       <c r="N20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.73112582781456958</v>
       </c>
       <c r="O20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.73031026252983289</v>
       </c>
       <c r="P20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.73471676948962417</v>
       </c>
       <c r="Q20" s="9">
-        <f t="shared" si="101"/>
+        <f t="shared" si="99"/>
         <v>0.72897196261682229</v>
       </c>
       <c r="R20" s="9">
@@ -3731,39 +3761,39 @@
         <v>0.71898854961832059</v>
       </c>
       <c r="S20" s="9">
-        <f t="shared" ref="S20:V20" si="102">S5/S3</f>
+        <f t="shared" ref="S20:V20" si="100">S5/S3</f>
         <v>0.71131339401820548</v>
       </c>
       <c r="T20" s="9">
+        <f t="shared" si="100"/>
+        <v>0.72374157748711854</v>
+      </c>
+      <c r="U20" s="9">
+        <f t="shared" si="100"/>
+        <v>0.7246963562753036</v>
+      </c>
+      <c r="V20" s="9">
+        <f t="shared" si="100"/>
+        <v>0.71</v>
+      </c>
+      <c r="X20" s="9">
+        <f t="shared" ref="X20:Y20" si="101">X5/X3</f>
+        <v>0.7076271186440678</v>
+      </c>
+      <c r="Y20" s="9">
+        <f t="shared" si="101"/>
+        <v>0.71552257266542973</v>
+      </c>
+      <c r="Z20" s="9">
+        <f t="shared" ref="Z20:AB20" si="102">Z5/Z3</f>
+        <v>0.72408293460925033</v>
+      </c>
+      <c r="AA20" s="9">
         <f t="shared" si="102"/>
-        <v>0.72374157748711854</v>
-      </c>
-      <c r="U20" s="9">
+        <v>0.73071718538565633</v>
+      </c>
+      <c r="AB20" s="9">
         <f t="shared" si="102"/>
-        <v>0.71</v>
-      </c>
-      <c r="V20" s="9">
-        <f t="shared" si="102"/>
-        <v>0.71</v>
-      </c>
-      <c r="X20" s="9">
-        <f t="shared" ref="X20:Y20" si="103">X5/X3</f>
-        <v>0.7076271186440678</v>
-      </c>
-      <c r="Y20" s="9">
-        <f t="shared" si="103"/>
-        <v>0.71552257266542973</v>
-      </c>
-      <c r="Z20" s="9">
-        <f t="shared" ref="Z20:AB20" si="104">Z5/Z3</f>
-        <v>0.72408293460925033</v>
-      </c>
-      <c r="AA20" s="9">
-        <f t="shared" si="104"/>
-        <v>0.73071718538565633</v>
-      </c>
-      <c r="AB20" s="9">
-        <f t="shared" si="104"/>
         <v>0.73225381284127289</v>
       </c>
       <c r="AC20" s="9">
@@ -3771,47 +3801,47 @@
         <v>0.72784387114022187</v>
       </c>
       <c r="AD20" s="9">
-        <f t="shared" ref="AD20:AN20" si="105">AD5/AD3</f>
-        <v>0.71364040169949772</v>
+        <f t="shared" ref="AD20:AN20" si="103">AD5/AD3</f>
+        <v>0.71753908905506458</v>
       </c>
       <c r="AE20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>0.71</v>
       </c>
       <c r="AF20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>0.71</v>
       </c>
       <c r="AG20" s="9">
-        <f t="shared" si="105"/>
-        <v>0.71000000000000008</v>
+        <f t="shared" si="103"/>
+        <v>0.71</v>
       </c>
       <c r="AH20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>0.71</v>
       </c>
       <c r="AI20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>0.71</v>
       </c>
       <c r="AJ20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>0.71</v>
       </c>
       <c r="AK20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>0.71</v>
       </c>
       <c r="AL20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>0.71</v>
       </c>
       <c r="AM20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>0.71</v>
       </c>
       <c r="AN20" s="9">
-        <f t="shared" si="105"/>
+        <f t="shared" si="103"/>
         <v>0.71</v>
       </c>
     </row>
@@ -3824,47 +3854,47 @@
       <c r="E21" s="9"/>
       <c r="F21" s="9"/>
       <c r="G21" s="9">
-        <f t="shared" ref="G21:Q21" si="106">G6/C6-1</f>
+        <f t="shared" ref="G21:Q21" si="104">G6/C6-1</f>
         <v>0.32444444444444454</v>
       </c>
       <c r="H21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>0.5616438356164386</v>
       </c>
       <c r="I21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>0.43344709897610922</v>
       </c>
       <c r="J21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>0.48333333333333339</v>
       </c>
       <c r="K21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>0.53691275167785224</v>
       </c>
       <c r="L21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>0.40058479532163727</v>
       </c>
       <c r="M21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>0.19761904761904758</v>
       </c>
       <c r="N21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>0.13033707865168531</v>
       </c>
       <c r="O21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>0.11135371179039311</v>
       </c>
       <c r="P21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>0.1503131524008352</v>
       </c>
       <c r="Q21" s="9">
-        <f t="shared" si="106"/>
+        <f t="shared" si="104"/>
         <v>0.25049701789264422</v>
       </c>
       <c r="R21" s="9">
@@ -3872,36 +3902,36 @@
         <v>0.32007952286282326</v>
       </c>
       <c r="S21" s="9">
-        <f t="shared" ref="S21:V21" si="107">S6/O6-1</f>
+        <f t="shared" ref="S21:V21" si="105">S6/O6-1</f>
         <v>0.38310412573673891</v>
       </c>
       <c r="T21" s="9">
-        <f t="shared" si="107"/>
+        <f t="shared" si="105"/>
         <v>0.33756805807622503</v>
       </c>
       <c r="U21" s="9">
-        <f t="shared" si="107"/>
-        <v>0.22999999999999998</v>
+        <f t="shared" si="105"/>
+        <v>0.31478537360890302</v>
       </c>
       <c r="V21" s="9">
-        <f t="shared" si="107"/>
-        <v>0.21999999999999997</v>
+        <f t="shared" si="105"/>
+        <v>0.30000000000000004</v>
       </c>
       <c r="X21" s="9"/>
       <c r="Y21" s="9">
-        <f t="shared" ref="Y21" si="108">Y6/X6-1</f>
+        <f t="shared" ref="Y21" si="106">Y6/X6-1</f>
         <v>0.67721518987341756</v>
       </c>
       <c r="Z21" s="9">
-        <f t="shared" ref="Z21:AB21" si="109">Z6/Y6-1</f>
+        <f t="shared" ref="Z21:AB21" si="107">Z6/Y6-1</f>
         <v>0.95660377358490578</v>
       </c>
       <c r="AA21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>0.45130183220829312</v>
       </c>
       <c r="AB21" s="9">
-        <f t="shared" si="109"/>
+        <f t="shared" si="107"/>
         <v>0.29102990033222609</v>
       </c>
       <c r="AC21" s="9">
@@ -3909,47 +3939,47 @@
         <v>0.211013896037056</v>
       </c>
       <c r="AD21" s="9">
-        <f t="shared" ref="AD21:AN21" si="110">AD6/AC6-1</f>
-        <v>0.28548661283467913</v>
+        <f t="shared" ref="AD21:AN21" si="108">AD6/AC6-1</f>
+        <v>0.3307267318317042</v>
       </c>
       <c r="AE21" s="9">
-        <f t="shared" si="110"/>
-        <v>0.17999999999999994</v>
+        <f t="shared" si="108"/>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AF21" s="9">
-        <f t="shared" si="110"/>
-        <v>0.12000000000000011</v>
+        <f t="shared" si="108"/>
+        <v>0.1399999999999999</v>
       </c>
       <c r="AG21" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="AH21" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AI21" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ21" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK21" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AL21" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AM21" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AN21" s="9">
-        <f t="shared" si="110"/>
+        <f t="shared" si="108"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AQ21" t="s">
@@ -3964,63 +3994,63 @@
         <v>48</v>
       </c>
       <c r="C22" s="9">
-        <f t="shared" ref="C22:Q22" si="111">C7/C3</f>
+        <f t="shared" ref="C22:Q22" si="109">C7/C3</f>
         <v>0.35740072202166068</v>
       </c>
       <c r="D22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.16326530612244899</v>
       </c>
       <c r="E22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.24056603773584906</v>
       </c>
       <c r="F22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.19863013698630136</v>
       </c>
       <c r="G22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.18349753694581281</v>
       </c>
       <c r="H22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.17307692307692307</v>
       </c>
       <c r="I22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.18418314255983351</v>
       </c>
       <c r="J22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.18304431599229287</v>
       </c>
       <c r="K22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.14347450302506484</v>
       </c>
       <c r="L22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.13958990536277602</v>
       </c>
       <c r="M22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.1620639534883721</v>
       </c>
       <c r="N22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.12649006622516556</v>
       </c>
       <c r="O22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.11873508353221957</v>
       </c>
       <c r="P22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.11329220415030845</v>
       </c>
       <c r="Q22" s="9">
-        <f t="shared" si="111"/>
+        <f t="shared" si="109"/>
         <v>0.13291796469366565</v>
       </c>
       <c r="R22" s="9">
@@ -4028,39 +4058,39 @@
         <v>0.1183206106870229</v>
       </c>
       <c r="S22" s="9">
-        <f t="shared" ref="S22:V22" si="112">S7/S3</f>
+        <f t="shared" ref="S22:V22" si="110">S7/S3</f>
         <v>0.11573472041612484</v>
       </c>
       <c r="T22" s="9">
+        <f t="shared" si="110"/>
+        <v>0.11732065001981767</v>
+      </c>
+      <c r="U22" s="9">
+        <f t="shared" si="110"/>
+        <v>0.12918660287081341</v>
+      </c>
+      <c r="V22" s="9">
+        <f t="shared" si="110"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="X22" s="9">
+        <f t="shared" ref="X22:Y22" si="111">X7/X3</f>
+        <v>0.21186440677966104</v>
+      </c>
+      <c r="Y22" s="9">
+        <f t="shared" si="111"/>
+        <v>0.21645021645021648</v>
+      </c>
+      <c r="Z22" s="9">
+        <f t="shared" ref="Z22:AB22" si="112">Z7/Z3</f>
+        <v>0.2360446570972887</v>
+      </c>
+      <c r="AA22" s="9">
         <f t="shared" si="112"/>
-        <v>0.11732065001981767</v>
-      </c>
-      <c r="U22" s="9">
+        <v>0.18105548037889038</v>
+      </c>
+      <c r="AB22" s="9">
         <f t="shared" si="112"/>
-        <v>0.11</v>
-      </c>
-      <c r="V22" s="9">
-        <f t="shared" si="112"/>
-        <v>0.11</v>
-      </c>
-      <c r="X22" s="9">
-        <f t="shared" ref="X22:Y22" si="113">X7/X3</f>
-        <v>0.21186440677966104</v>
-      </c>
-      <c r="Y22" s="9">
-        <f t="shared" si="113"/>
-        <v>0.21645021645021648</v>
-      </c>
-      <c r="Z22" s="9">
-        <f t="shared" ref="Z22:AB22" si="114">Z7/Z3</f>
-        <v>0.2360446570972887</v>
-      </c>
-      <c r="AA22" s="9">
-        <f t="shared" si="114"/>
-        <v>0.18105548037889038</v>
-      </c>
-      <c r="AB22" s="9">
-        <f t="shared" si="114"/>
         <v>0.14253436264356992</v>
       </c>
       <c r="AC22" s="9">
@@ -4068,48 +4098,48 @@
         <v>0.12097313193423337</v>
       </c>
       <c r="AD22" s="9">
-        <f t="shared" ref="AD22:AN22" si="115">AD7/AD3</f>
-        <v>0.11306102742371572</v>
+        <f t="shared" ref="AD22:AN22" si="113">AD7/AD3</f>
+        <v>0.1261532485189861</v>
       </c>
       <c r="AE22" s="9">
-        <f t="shared" si="115"/>
+        <f t="shared" si="113"/>
+        <v>0.11999999999999998</v>
+      </c>
+      <c r="AF22" s="9">
+        <f t="shared" si="113"/>
+        <v>0.11</v>
+      </c>
+      <c r="AG22" s="9">
+        <f t="shared" si="113"/>
         <v>0.1</v>
       </c>
-      <c r="AF22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.09</v>
-      </c>
-      <c r="AG22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.09</v>
-      </c>
       <c r="AH22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.09</v>
+        <f t="shared" si="113"/>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="AI22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.09</v>
+        <f t="shared" si="113"/>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="AJ22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.09</v>
+        <f t="shared" si="113"/>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="AK22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.09</v>
+        <f t="shared" si="113"/>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="AL22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.09</v>
+        <f t="shared" si="113"/>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="AM22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.09</v>
+        <f t="shared" si="113"/>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="AN22" s="9">
-        <f t="shared" si="115"/>
-        <v>0.09</v>
+        <f t="shared" si="113"/>
+        <v>9.5000000000000015E-2</v>
       </c>
       <c r="AQ22" t="s">
         <v>68</v>
@@ -4127,47 +4157,47 @@
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9">
-        <f t="shared" ref="G23:Q23" si="116">G8/C8-1</f>
+        <f t="shared" ref="G23:Q23" si="114">G8/C8-1</f>
         <v>1.3391304347826085</v>
       </c>
       <c r="H23" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>1.5948275862068968</v>
       </c>
       <c r="I23" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>2.0270270270270174E-2</v>
       </c>
       <c r="J23" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>0.1853281853281854</v>
       </c>
       <c r="K23" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>0.12267657992565062</v>
       </c>
       <c r="L23" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>6.976744186046524E-2</v>
       </c>
       <c r="M23" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>0.10596026490066213</v>
       </c>
       <c r="N23" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>0.1791530944625408</v>
       </c>
       <c r="O23" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>0.16225165562913912</v>
       </c>
       <c r="P23" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>0.1490683229813663</v>
       </c>
       <c r="Q23" s="9">
-        <f t="shared" si="116"/>
+        <f t="shared" si="114"/>
         <v>0.14970059880239517</v>
       </c>
       <c r="R23" s="9">
@@ -4175,36 +4205,36 @@
         <v>0.25690607734806625</v>
       </c>
       <c r="S23" s="9">
-        <f t="shared" ref="S23:V23" si="117">S8/O8-1</f>
+        <f t="shared" ref="S23:V23" si="115">S8/O8-1</f>
         <v>0.23931623931623935</v>
       </c>
       <c r="T23" s="9">
-        <f t="shared" si="117"/>
+        <f t="shared" si="115"/>
         <v>0.2432432432432432</v>
       </c>
       <c r="U23" s="9">
-        <f t="shared" si="117"/>
-        <v>0.25</v>
+        <f t="shared" si="115"/>
+        <v>0.14583333333333348</v>
       </c>
       <c r="V23" s="9">
-        <f t="shared" si="117"/>
-        <v>0.17999999999999994</v>
+        <f t="shared" si="115"/>
+        <v>0.10000000000000009</v>
       </c>
       <c r="X23" s="9"/>
       <c r="Y23" s="9">
-        <f t="shared" ref="Y23" si="118">Y8/X8-1</f>
+        <f t="shared" ref="Y23" si="116">Y8/X8-1</f>
         <v>1.6646341463414638</v>
       </c>
       <c r="Z23" s="9">
-        <f t="shared" ref="Z23:AB23" si="119">Z8/Y8-1</f>
+        <f t="shared" ref="Z23:AB23" si="117">Z8/Y8-1</f>
         <v>0.79862700228832928</v>
       </c>
       <c r="AA23" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="117"/>
         <v>0.50000000000000022</v>
       </c>
       <c r="AB23" s="9">
-        <f t="shared" si="119"/>
+        <f t="shared" si="117"/>
         <v>0.11959287531806617</v>
       </c>
       <c r="AC23" s="9">
@@ -4212,47 +4242,47 @@
         <v>0.18181818181818188</v>
       </c>
       <c r="AD23" s="9">
-        <f t="shared" ref="AD23:AN23" si="120">AD8/AC8-1</f>
-        <v>0.22557692307692312</v>
+        <f t="shared" ref="AD23:AN23" si="118">AD8/AC8-1</f>
+        <v>0.17660256410256414</v>
       </c>
       <c r="AE23" s="9">
-        <f t="shared" si="120"/>
-        <v>0.16999999999999993</v>
+        <f t="shared" si="118"/>
+        <v>0.12000000000000011</v>
       </c>
       <c r="AF23" s="9">
-        <f t="shared" si="120"/>
-        <v>0.1100000000000001</v>
+        <f t="shared" si="118"/>
+        <v>9.000000000000008E-2</v>
       </c>
       <c r="AG23" s="9">
-        <f t="shared" si="120"/>
-        <v>7.0000000000000062E-2</v>
+        <f t="shared" si="118"/>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AH23" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AI23" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AJ23" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK23" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AL23" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AM23" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AN23" s="9">
-        <f t="shared" si="120"/>
+        <f t="shared" si="118"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AQ23" t="s">
@@ -4260,7 +4290,7 @@
       </c>
       <c r="AR23" s="5">
         <f>NPV(AR22,AD15:EI15)</f>
-        <v>7705.8198992622183</v>
+        <v>6924.3696840620387</v>
       </c>
     </row>
     <row r="24" spans="2:44" x14ac:dyDescent="0.3">
@@ -4268,63 +4298,63 @@
         <v>50</v>
       </c>
       <c r="C24" s="9">
-        <f t="shared" ref="C24:Q24" si="121">C10/C3</f>
+        <f t="shared" ref="C24:Q24" si="119">C10/C3</f>
         <v>-0.2418772563176895</v>
       </c>
       <c r="D24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>-6.802721088435471E-3</v>
       </c>
       <c r="E24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>-0.45125786163522014</v>
       </c>
       <c r="F24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>-0.23835616438356172</v>
       </c>
       <c r="G24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>-0.14655172413793091</v>
       </c>
       <c r="H24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>-0.17081447963800897</v>
       </c>
       <c r="I24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>-0.20915712799167543</v>
       </c>
       <c r="J24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>-0.17533718689788058</v>
       </c>
       <c r="K24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>-7.2601555747623087E-2</v>
       </c>
       <c r="L24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>-3.7854889589905343E-2</v>
       </c>
       <c r="M24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>-3.4156976744186066E-2</v>
       </c>
       <c r="N24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>3.1788079470198655E-2</v>
       </c>
       <c r="O24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>9.8448687350835243E-2</v>
       </c>
       <c r="P24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>0.10487941671340438</v>
       </c>
       <c r="Q24" s="9">
-        <f t="shared" si="121"/>
+        <f t="shared" si="119"/>
         <v>7.0093457943925089E-2</v>
       </c>
       <c r="R24" s="9">
@@ -4332,39 +4362,39 @@
         <v>6.6793893129770993E-2</v>
       </c>
       <c r="S24" s="9">
-        <f t="shared" ref="S24:V24" si="122">S10/S3</f>
+        <f t="shared" ref="S24:V24" si="120">S10/S3</f>
         <v>0.10186389250108353</v>
       </c>
       <c r="T24" s="9">
+        <f t="shared" si="120"/>
+        <v>0.13198573127229493</v>
+      </c>
+      <c r="U24" s="9">
+        <f t="shared" si="120"/>
+        <v>0.12918660287081327</v>
+      </c>
+      <c r="V24" s="9">
+        <f t="shared" si="120"/>
+        <v>7.4109090909090791E-2</v>
+      </c>
+      <c r="X24" s="9">
+        <f t="shared" ref="X24:Y24" si="121">X10/X3</f>
+        <v>-0.18220338983050857</v>
+      </c>
+      <c r="Y24" s="9">
+        <f t="shared" si="121"/>
+        <v>-9.894867037724181E-2</v>
+      </c>
+      <c r="Z24" s="9">
+        <f t="shared" ref="Z24:AB24" si="122">Z10/Z3</f>
+        <v>-0.2388357256778311</v>
+      </c>
+      <c r="AA24" s="9">
         <f t="shared" si="122"/>
-        <v>0.13198573127229493</v>
-      </c>
-      <c r="U24" s="9">
+        <v>-0.17672530446549375</v>
+      </c>
+      <c r="AB24" s="9">
         <f t="shared" si="122"/>
-        <v>0.13505785491766792</v>
-      </c>
-      <c r="V24" s="9">
-        <f t="shared" si="122"/>
-        <v>0.12396805202148713</v>
-      </c>
-      <c r="X24" s="9">
-        <f t="shared" ref="X24:Y24" si="123">X10/X3</f>
-        <v>-0.18220338983050857</v>
-      </c>
-      <c r="Y24" s="9">
-        <f t="shared" si="123"/>
-        <v>-9.894867037724181E-2</v>
-      </c>
-      <c r="Z24" s="9">
-        <f t="shared" ref="Z24:AB24" si="124">Z10/Z3</f>
-        <v>-0.2388357256778311</v>
-      </c>
-      <c r="AA24" s="9">
-        <f t="shared" si="124"/>
-        <v>-0.17672530446549375</v>
-      </c>
-      <c r="AB24" s="9">
-        <f t="shared" si="124"/>
         <v>-2.4665787987196319E-2</v>
       </c>
       <c r="AC24" s="9">
@@ -4372,55 +4402,55 @@
         <v>8.381232455554069E-2</v>
       </c>
       <c r="AD24" s="9">
-        <f t="shared" ref="AD24:AN24" si="125">AD10/AD3</f>
-        <v>0.12388470451911922</v>
+        <f t="shared" ref="AD24:AN24" si="123">AD10/AD3</f>
+        <v>0.1090414683888512</v>
       </c>
       <c r="AE24" s="9">
-        <f t="shared" si="125"/>
-        <v>0.17198942641946702</v>
+        <f t="shared" si="123"/>
+        <v>0.13835777410896377</v>
       </c>
       <c r="AF24" s="9">
-        <f t="shared" si="125"/>
-        <v>0.21927514586756541</v>
+        <f t="shared" si="123"/>
+        <v>0.17759476870285842</v>
       </c>
       <c r="AG24" s="9">
-        <f t="shared" si="125"/>
-        <v>0.24930111976248018</v>
+        <f t="shared" si="123"/>
+        <v>0.22065256941306952</v>
       </c>
       <c r="AH24" s="9">
-        <f t="shared" si="125"/>
-        <v>0.26952105868452664</v>
+        <f t="shared" si="123"/>
+        <v>0.24688970199053836</v>
       </c>
       <c r="AI24" s="9">
-        <f t="shared" si="125"/>
-        <v>0.28574693559728009</v>
+        <f t="shared" si="123"/>
+        <v>0.2639318454169024</v>
       </c>
       <c r="AJ24" s="9">
-        <f t="shared" si="125"/>
-        <v>0.29836025878228839</v>
+        <f t="shared" si="123"/>
+        <v>0.27717970030683053</v>
       </c>
       <c r="AK24" s="9">
-        <f t="shared" si="125"/>
-        <v>0.30873044188571208</v>
+        <f t="shared" si="123"/>
+        <v>0.28793671348834721</v>
       </c>
       <c r="AL24" s="9">
-        <f t="shared" si="125"/>
-        <v>0.31875936352098116</v>
+        <f t="shared" si="123"/>
+        <v>0.29834428802205482</v>
       </c>
       <c r="AM24" s="9">
-        <f t="shared" si="125"/>
-        <v>0.32845848717851317</v>
+        <f t="shared" si="123"/>
+        <v>0.30841401150414</v>
       </c>
       <c r="AN24" s="9">
-        <f t="shared" si="125"/>
-        <v>0.33783888355708486</v>
+        <f t="shared" si="123"/>
+        <v>0.31815707936576298</v>
       </c>
       <c r="AQ24" t="s">
         <v>70</v>
       </c>
       <c r="AR24" s="5">
         <f>Main!D8</f>
-        <v>1097.9000000000001</v>
+        <v>1121.4000000000001</v>
       </c>
     </row>
     <row r="25" spans="2:44" x14ac:dyDescent="0.3">
@@ -4428,63 +4458,63 @@
         <v>21</v>
       </c>
       <c r="C25" s="9">
-        <f t="shared" ref="C25:Q25" si="126">C14/C13</f>
+        <f t="shared" ref="C25:Q25" si="124">C14/C13</f>
         <v>0</v>
       </c>
       <c r="D25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="E25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>-3.4602076124567475E-3</v>
       </c>
       <c r="F25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>-5.7471264367816074E-3</v>
       </c>
       <c r="G25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0</v>
       </c>
       <c r="H25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>-6.6666666666666697E-3</v>
       </c>
       <c r="I25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>-5.4644808743169382E-3</v>
       </c>
       <c r="J25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>-5.3030303030303018E-2</v>
       </c>
       <c r="K25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>3.8461538461538575E-2</v>
       </c>
       <c r="L25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>-0.54166666666666596</v>
       </c>
       <c r="M25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>3.4482758620689696E-2</v>
       </c>
       <c r="N25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.19736842105263161</v>
       </c>
       <c r="O25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>-4.2471042471042497E-2</v>
       </c>
       <c r="P25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>0.15331010452961671</v>
       </c>
       <c r="Q25" s="9">
-        <f t="shared" si="126"/>
+        <f t="shared" si="124"/>
         <v>7.9051383399209585E-2</v>
       </c>
       <c r="R25" s="9">
@@ -4492,39 +4522,39 @@
         <v>0.37333333333333335</v>
       </c>
       <c r="S25" s="9">
-        <f t="shared" ref="S25:V25" si="127">S14/S13</f>
+        <f t="shared" ref="S25:V25" si="125">S14/S13</f>
         <v>-2.8653295128939853E-3</v>
       </c>
       <c r="T25" s="9">
+        <f t="shared" si="125"/>
+        <v>3.6637931034482749E-2</v>
+      </c>
+      <c r="U25" s="9">
+        <f t="shared" si="125"/>
+        <v>4.3103448275862107E-2</v>
+      </c>
+      <c r="V25" s="9">
+        <f t="shared" si="125"/>
+        <v>0.15</v>
+      </c>
+      <c r="X25" s="9">
+        <f t="shared" ref="X25:Y25" si="126">X14/X13</f>
+        <v>0</v>
+      </c>
+      <c r="Y25" s="9">
+        <f t="shared" si="126"/>
+        <v>-6.369426751592357E-3</v>
+      </c>
+      <c r="Z25" s="9">
+        <f t="shared" ref="Z25:AB25" si="127">Z14/Z13</f>
+        <v>-3.3444816053511688E-3</v>
+      </c>
+      <c r="AA25" s="9">
         <f t="shared" si="127"/>
-        <v>3.6637931034482749E-2</v>
-      </c>
-      <c r="U25" s="9">
+        <v>-1.5332197614991491E-2</v>
+      </c>
+      <c r="AB25" s="9">
         <f t="shared" si="127"/>
-        <v>0.15</v>
-      </c>
-      <c r="V25" s="9">
-        <f t="shared" si="127"/>
-        <v>0.15</v>
-      </c>
-      <c r="X25" s="9">
-        <f t="shared" ref="X25:Y25" si="128">X14/X13</f>
-        <v>0</v>
-      </c>
-      <c r="Y25" s="9">
-        <f t="shared" si="128"/>
-        <v>-6.369426751592357E-3</v>
-      </c>
-      <c r="Z25" s="9">
-        <f t="shared" ref="Z25:AB25" si="129">Z14/Z13</f>
-        <v>-3.3444816053511688E-3</v>
-      </c>
-      <c r="AA25" s="9">
-        <f t="shared" si="129"/>
-        <v>-1.5332197614991491E-2</v>
-      </c>
-      <c r="AB25" s="9">
-        <f t="shared" si="129"/>
         <v>9.4972067039105962E-2</v>
       </c>
       <c r="AC25" s="9">
@@ -4532,47 +4562,47 @@
         <v>0.13378906250000003</v>
       </c>
       <c r="AD25" s="9">
-        <f t="shared" ref="AD25:AN25" si="130">AD14/AD13</f>
-        <v>8.9035617699522451E-2</v>
+        <f t="shared" ref="AD25:AN25" si="128">AD14/AD13</f>
+        <v>5.2077431539187848E-2</v>
       </c>
       <c r="AE25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>0.15</v>
       </c>
       <c r="AF25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>0.15</v>
       </c>
       <c r="AG25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>0.15</v>
       </c>
       <c r="AH25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>0.15</v>
       </c>
       <c r="AI25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>0.15</v>
       </c>
       <c r="AJ25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>0.15</v>
       </c>
       <c r="AK25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>0.15</v>
       </c>
       <c r="AL25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>0.15</v>
       </c>
       <c r="AM25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>0.15</v>
       </c>
       <c r="AN25" s="9">
-        <f t="shared" si="130"/>
+        <f t="shared" si="128"/>
         <v>0.15</v>
       </c>
       <c r="AQ25" t="s">
@@ -4580,7 +4610,7 @@
       </c>
       <c r="AR25" s="5">
         <f>AR23+AR24</f>
-        <v>8803.719899262218</v>
+        <v>8045.7696840620392</v>
       </c>
     </row>
     <row r="26" spans="2:44" x14ac:dyDescent="0.3">
@@ -4588,63 +4618,63 @@
         <v>51</v>
       </c>
       <c r="C26" s="9">
-        <f t="shared" ref="C26:Q26" si="131">C15/C3</f>
+        <f t="shared" ref="C26:Q26" si="129">C15/C3</f>
         <v>-0.2418772563176895</v>
       </c>
       <c r="D26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>-1.7006802721089404E-3</v>
       </c>
       <c r="E26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>-0.45597484276729566</v>
       </c>
       <c r="F26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>-0.23972602739726037</v>
       </c>
       <c r="G26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>-0.15024630541871911</v>
       </c>
       <c r="H26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>-0.17081447963800897</v>
       </c>
       <c r="I26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>-0.19146722164412081</v>
       </c>
       <c r="J26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>-0.13391136801541428</v>
       </c>
       <c r="K26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>-2.1607605877268732E-2</v>
       </c>
       <c r="L26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>2.9179810725552074E-2</v>
       </c>
       <c r="M26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>2.0348837209302303E-2</v>
       </c>
       <c r="N26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>8.0794701986754952E-2</v>
       </c>
       <c r="O26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>0.16109785202863955</v>
       </c>
       <c r="P26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>0.13628715647784634</v>
       </c>
       <c r="Q26" s="9">
-        <f t="shared" si="131"/>
+        <f t="shared" si="129"/>
         <v>0.12097611630321894</v>
       </c>
       <c r="R26" s="9">
@@ -4652,39 +4682,39 @@
         <v>6.7270992366412208E-2</v>
       </c>
       <c r="S26" s="9">
-        <f t="shared" ref="S26:V26" si="132">S15/S3</f>
+        <f t="shared" ref="S26:V26" si="130">S15/S3</f>
         <v>0.15171218032076278</v>
       </c>
       <c r="T26" s="9">
+        <f t="shared" si="130"/>
+        <v>0.1771700356718193</v>
+      </c>
+      <c r="U26" s="9">
+        <f t="shared" si="130"/>
+        <v>0.16341553183658433</v>
+      </c>
+      <c r="V26" s="9">
+        <f t="shared" si="130"/>
+        <v>9.628181818181808E-2</v>
+      </c>
+      <c r="X26" s="9">
+        <f t="shared" ref="X26:Y26" si="131">X15/X3</f>
+        <v>-0.17372881355932213</v>
+      </c>
+      <c r="Y26" s="9">
+        <f t="shared" si="131"/>
+        <v>-9.7711811997526279E-2</v>
+      </c>
+      <c r="Z26" s="9">
+        <f t="shared" ref="Z26:AB26" si="132">Z15/Z3</f>
+        <v>-0.23923444976076572</v>
+      </c>
+      <c r="AA26" s="9">
         <f t="shared" si="132"/>
-        <v>0.1771700356718193</v>
-      </c>
-      <c r="U26" s="9">
+        <v>-0.16129905277401882</v>
+      </c>
+      <c r="AB26" s="9">
         <f t="shared" si="132"/>
-        <v>0.14871847648716799</v>
-      </c>
-      <c r="V26" s="9">
-        <f t="shared" si="132"/>
-        <v>0.1361183559513712</v>
-      </c>
-      <c r="X26" s="9">
-        <f t="shared" ref="X26:Y26" si="133">X15/X3</f>
-        <v>-0.17372881355932213</v>
-      </c>
-      <c r="Y26" s="9">
-        <f t="shared" si="133"/>
-        <v>-9.7711811997526279E-2</v>
-      </c>
-      <c r="Z26" s="9">
-        <f t="shared" ref="Z26:AB26" si="134">Z15/Z3</f>
-        <v>-0.23923444976076572</v>
-      </c>
-      <c r="AA26" s="9">
-        <f t="shared" si="134"/>
-        <v>-0.16129905277401882</v>
-      </c>
-      <c r="AB26" s="9">
-        <f t="shared" si="134"/>
         <v>3.0502730182639867E-2</v>
       </c>
       <c r="AC26" s="9">
@@ -4692,55 +4722,55 @@
         <v>0.1185670364924475</v>
       </c>
       <c r="AD26" s="9">
-        <f t="shared" ref="AD26:AN26" si="135">AD15/AD3</f>
-        <v>0.15287417921977584</v>
+        <f t="shared" ref="AD26:AN26" si="133">AD15/AD3</f>
+        <v>0.14623434009905806</v>
       </c>
       <c r="AE26" s="9">
-        <f t="shared" si="135"/>
-        <v>0.17682262660233203</v>
+        <f t="shared" si="133"/>
+        <v>0.14989601825774498</v>
       </c>
       <c r="AF26" s="9">
-        <f t="shared" si="135"/>
-        <v>0.21274714845716361</v>
+        <f t="shared" si="133"/>
+        <v>0.17921097487941468</v>
       </c>
       <c r="AG26" s="9">
-        <f t="shared" si="135"/>
-        <v>0.23597676761829922</v>
+        <f t="shared" si="133"/>
+        <v>0.21335311231074758</v>
       </c>
       <c r="AH26" s="9">
-        <f t="shared" si="135"/>
-        <v>0.25206958771021182</v>
+        <f t="shared" si="133"/>
+        <v>0.23448201916933986</v>
       </c>
       <c r="AI26" s="9">
-        <f t="shared" si="135"/>
-        <v>0.26522334175748657</v>
+        <f t="shared" si="133"/>
+        <v>0.24828379184626645</v>
       </c>
       <c r="AJ26" s="9">
-        <f t="shared" si="135"/>
-        <v>0.27573392640342476</v>
+        <f t="shared" si="133"/>
+        <v>0.25931860318910255</v>
       </c>
       <c r="AK26" s="9">
-        <f t="shared" si="135"/>
-        <v>0.28454858204133493</v>
+        <f t="shared" si="133"/>
+        <v>0.26846206439339171</v>
       </c>
       <c r="AL26" s="9">
-        <f t="shared" si="135"/>
-        <v>0.29307316543131362</v>
+        <f t="shared" si="133"/>
+        <v>0.27730850274704316</v>
       </c>
       <c r="AM26" s="9">
-        <f t="shared" si="135"/>
-        <v>0.30131742054021582</v>
+        <f t="shared" si="133"/>
+        <v>0.28586776770681555</v>
       </c>
       <c r="AN26" s="9">
-        <f t="shared" si="135"/>
-        <v>0.3092907574620018</v>
+        <f t="shared" si="133"/>
+        <v>0.29414937538919511</v>
       </c>
       <c r="AQ26" t="s">
         <v>72</v>
       </c>
       <c r="AR26" s="4">
         <f>AR25/AN16</f>
-        <v>192.22095849917508</v>
+        <v>174.5286265523219</v>
       </c>
     </row>
     <row r="27" spans="2:44" x14ac:dyDescent="0.3">
@@ -4749,7 +4779,7 @@
       </c>
       <c r="AR27" s="4">
         <f>Main!D3</f>
-        <v>278.74</v>
+        <v>195.41</v>
       </c>
     </row>
     <row r="28" spans="2:44" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4769,67 +4799,67 @@
         <v>-60.000000000000036</v>
       </c>
       <c r="AA28" s="8">
-        <f t="shared" ref="AA28:AN28" si="136">AA15</f>
+        <f t="shared" ref="AA28:AN28" si="134">AA15</f>
         <v>-59.599999999999959</v>
       </c>
       <c r="AB28" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>16.200000000000035</v>
       </c>
       <c r="AC28" s="8">
-        <f t="shared" si="136"/>
+        <f t="shared" si="134"/>
         <v>88.699999999999974</v>
       </c>
       <c r="AD28" s="8">
-        <f t="shared" si="136"/>
-        <v>158.31649999999985</v>
+        <f t="shared" si="134"/>
+        <v>150.5775000000001</v>
       </c>
       <c r="AE28" s="8">
-        <f t="shared" si="136"/>
-        <v>234.39041550000007</v>
+        <f t="shared" si="134"/>
+        <v>192.93491250000002</v>
       </c>
       <c r="AF28" s="8">
-        <f t="shared" si="136"/>
-        <v>344.05319074499982</v>
+        <f t="shared" si="134"/>
+        <v>276.80031124999994</v>
       </c>
       <c r="AG28" s="8">
-        <f t="shared" si="136"/>
-        <v>438.86296241324982</v>
+        <f t="shared" si="134"/>
+        <v>378.96473206249993</v>
       </c>
       <c r="AH28" s="8">
-        <f t="shared" si="136"/>
-        <v>515.67113078394721</v>
+        <f t="shared" si="134"/>
+        <v>458.14404142562489</v>
       </c>
       <c r="AI28" s="8">
-        <f t="shared" si="136"/>
-        <v>585.98684411124941</v>
+        <f t="shared" si="134"/>
+        <v>523.91957147708126</v>
       </c>
       <c r="AJ28" s="8">
-        <f t="shared" si="136"/>
-        <v>645.76156613321393</v>
+        <f t="shared" si="134"/>
+        <v>580.03712556304617</v>
       </c>
       <c r="AK28" s="8">
-        <f t="shared" si="136"/>
-        <v>699.72551943684675</v>
+        <f t="shared" si="134"/>
+        <v>630.51343154854897</v>
       </c>
       <c r="AL28" s="8">
-        <f t="shared" si="136"/>
-        <v>756.72249011196664</v>
+        <f t="shared" si="134"/>
+        <v>683.85480407703722</v>
       </c>
       <c r="AM28" s="8">
-        <f t="shared" si="136"/>
-        <v>816.90983844333812</v>
+        <f t="shared" si="134"/>
+        <v>740.21043912302923</v>
       </c>
       <c r="AN28" s="8">
-        <f t="shared" si="136"/>
-        <v>880.45289704850791</v>
+        <f t="shared" si="134"/>
+        <v>799.73710248894315</v>
       </c>
       <c r="AQ28" s="1" t="s">
         <v>74</v>
       </c>
       <c r="AR28" s="10">
         <f>AR26/AR27-1</f>
-        <v>-0.31039334684948316</v>
+        <v>-0.1068592878955944</v>
       </c>
     </row>
     <row r="29" spans="2:44" x14ac:dyDescent="0.3">
@@ -4857,43 +4887,43 @@
         <v>11.445</v>
       </c>
       <c r="AE29" s="5">
-        <f t="shared" ref="AE29:AN29" si="137">AD29*1.05</f>
+        <f t="shared" ref="AE29:AN29" si="135">AD29*1.05</f>
         <v>12.017250000000001</v>
       </c>
       <c r="AF29" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>12.618112500000001</v>
       </c>
       <c r="AG29" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>13.249018125000001</v>
       </c>
       <c r="AH29" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>13.911469031250002</v>
       </c>
       <c r="AI29" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>14.607042482812503</v>
       </c>
       <c r="AJ29" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>15.337394606953129</v>
       </c>
       <c r="AK29" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>16.104264337300787</v>
       </c>
       <c r="AL29" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>16.909477554165829</v>
       </c>
       <c r="AM29" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>17.754951431874122</v>
       </c>
       <c r="AN29" s="5">
-        <f t="shared" si="137"/>
+        <f t="shared" si="135"/>
         <v>18.642699003467829</v>
       </c>
       <c r="AQ29" t="s">
@@ -4928,19 +4958,19 @@
         <v>121.55000000000001</v>
       </c>
       <c r="AE30" s="5">
-        <f t="shared" ref="AE30:AH30" si="138">AD30*1.1</f>
+        <f t="shared" ref="AE30:AH30" si="136">AD30*1.1</f>
         <v>133.70500000000001</v>
       </c>
       <c r="AF30" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="136"/>
         <v>147.07550000000003</v>
       </c>
       <c r="AG30" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="136"/>
         <v>161.78305000000006</v>
       </c>
       <c r="AH30" s="5">
-        <f t="shared" si="138"/>
+        <f t="shared" si="136"/>
         <v>177.96135500000008</v>
       </c>
       <c r="AI30" s="5">
@@ -4948,23 +4978,23 @@
         <v>181.5205821000001</v>
       </c>
       <c r="AJ30" s="5">
-        <f t="shared" ref="AJ30:AN30" si="139">AI30*1.02</f>
+        <f t="shared" ref="AJ30:AN30" si="137">AI30*1.02</f>
         <v>185.15099374200011</v>
       </c>
       <c r="AK30" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>188.85401361684012</v>
       </c>
       <c r="AL30" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>192.63109388917692</v>
       </c>
       <c r="AM30" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>196.48371576696047</v>
       </c>
       <c r="AN30" s="5">
-        <f t="shared" si="139"/>
+        <f t="shared" si="137"/>
         <v>200.41339008229968</v>
       </c>
     </row>
@@ -5406,68 +5436,68 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="Y39" s="8">
-        <f t="shared" ref="Y39:AD39" si="140">Y28+SUM(Y29:Y38)</f>
+        <f t="shared" ref="Y39:AD39" si="138">Y28+SUM(Y29:Y38)</f>
         <v>17.700000000000003</v>
       </c>
       <c r="Z39" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="138"/>
         <v>9.3999999999999702</v>
       </c>
       <c r="AA39" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="138"/>
         <v>53.600000000000044</v>
       </c>
       <c r="AB39" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="138"/>
         <v>153.60000000000005</v>
       </c>
       <c r="AC39" s="8">
-        <f t="shared" si="140"/>
+        <f t="shared" si="138"/>
         <v>285.7</v>
       </c>
       <c r="AD39" s="8">
-        <f t="shared" si="140"/>
-        <v>291.31149999999985</v>
+        <f t="shared" si="138"/>
+        <v>283.5725000000001</v>
       </c>
       <c r="AE39" s="8">
-        <f t="shared" ref="AE39:AN39" si="141">AE28+SUM(AE29:AE38)</f>
-        <v>380.11266550000005</v>
+        <f t="shared" ref="AE39:AN39" si="139">AE28+SUM(AE29:AE38)</f>
+        <v>338.65716250000003</v>
       </c>
       <c r="AF39" s="8">
-        <f t="shared" si="141"/>
-        <v>503.74680324499985</v>
+        <f t="shared" si="139"/>
+        <v>436.49392374999996</v>
       </c>
       <c r="AG39" s="8">
-        <f t="shared" si="141"/>
-        <v>613.8950305382499</v>
+        <f t="shared" si="139"/>
+        <v>553.99680018749996</v>
       </c>
       <c r="AH39" s="8">
-        <f t="shared" si="141"/>
-        <v>707.54395481519725</v>
+        <f t="shared" si="139"/>
+        <v>650.01686545687494</v>
       </c>
       <c r="AI39" s="8">
-        <f t="shared" si="141"/>
-        <v>782.114468694062</v>
+        <f t="shared" si="139"/>
+        <v>720.04719605989385</v>
       </c>
       <c r="AJ39" s="8">
-        <f t="shared" si="141"/>
-        <v>846.24995448216714</v>
+        <f t="shared" si="139"/>
+        <v>780.52551391199938</v>
       </c>
       <c r="AK39" s="8">
-        <f t="shared" si="141"/>
-        <v>904.68379739098759</v>
+        <f t="shared" si="139"/>
+        <v>835.47170950268992</v>
       </c>
       <c r="AL39" s="8">
-        <f t="shared" si="141"/>
-        <v>966.26306155530938</v>
+        <f t="shared" si="139"/>
+        <v>893.39537552037996</v>
       </c>
       <c r="AM39" s="8">
-        <f t="shared" si="141"/>
-        <v>1031.1485056421727</v>
+        <f t="shared" si="139"/>
+        <v>954.44910632186384</v>
       </c>
       <c r="AN39" s="8">
-        <f t="shared" si="141"/>
-        <v>1099.5089861342753</v>
+        <f t="shared" si="139"/>
+        <v>1018.7931915747107</v>
       </c>
     </row>
     <row r="40" spans="2:136" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5495,43 +5525,43 @@
         <v>9.9</v>
       </c>
       <c r="AE40" s="5">
-        <f t="shared" ref="AE40:AN40" si="142">AD40*1.1</f>
+        <f t="shared" ref="AE40:AN40" si="140">AD40*1.1</f>
         <v>10.89</v>
       </c>
       <c r="AF40" s="5">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>11.979000000000001</v>
       </c>
       <c r="AG40" s="5">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>13.176900000000002</v>
       </c>
       <c r="AH40" s="5">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>14.494590000000002</v>
       </c>
       <c r="AI40" s="5">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>15.944049000000003</v>
       </c>
       <c r="AJ40" s="5">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>17.538453900000004</v>
       </c>
       <c r="AK40" s="5">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>19.292299290000006</v>
       </c>
       <c r="AL40" s="5">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>21.221529219000008</v>
       </c>
       <c r="AM40" s="5">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>23.343682140900011</v>
       </c>
       <c r="AN40" s="5">
-        <f t="shared" si="142"/>
+        <f t="shared" si="140"/>
         <v>25.678050354990013</v>
       </c>
     </row>
@@ -5560,43 +5590,43 @@
         <v>13.31</v>
       </c>
       <c r="AE41" s="5">
-        <f t="shared" ref="AE41:AN41" si="143">AD41*1.1</f>
+        <f t="shared" ref="AE41:AN41" si="141">AD41*1.1</f>
         <v>14.641000000000002</v>
       </c>
       <c r="AF41" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>16.105100000000004</v>
       </c>
       <c r="AG41" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>17.715610000000005</v>
       </c>
       <c r="AH41" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>19.487171000000007</v>
       </c>
       <c r="AI41" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>21.43588810000001</v>
       </c>
       <c r="AJ41" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>23.579476910000015</v>
       </c>
       <c r="AK41" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>25.937424601000018</v>
       </c>
       <c r="AL41" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>28.531167061100021</v>
       </c>
       <c r="AM41" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>31.384283767210025</v>
       </c>
       <c r="AN41" s="5">
-        <f t="shared" si="143"/>
+        <f t="shared" si="141"/>
         <v>34.522712143931031</v>
       </c>
     </row>
@@ -5609,67 +5639,67 @@
         <v>5.3000000000000007</v>
       </c>
       <c r="Y42" s="5">
-        <f t="shared" ref="Y42:AD42" si="144">SUM(Y40:Y41)</f>
+        <f t="shared" ref="Y42:AD42" si="142">SUM(Y40:Y41)</f>
         <v>4</v>
       </c>
       <c r="Z42" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>6.2</v>
       </c>
       <c r="AA42" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>10.199999999999999</v>
       </c>
       <c r="AB42" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>13.7</v>
       </c>
       <c r="AC42" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>21.1</v>
       </c>
       <c r="AD42" s="5">
-        <f t="shared" si="144"/>
+        <f t="shared" si="142"/>
         <v>23.21</v>
       </c>
       <c r="AE42" s="5">
-        <f t="shared" ref="AE42:AN42" si="145">SUM(AE40:AE41)</f>
+        <f t="shared" ref="AE42:AN42" si="143">SUM(AE40:AE41)</f>
         <v>25.531000000000002</v>
       </c>
       <c r="AF42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>28.084100000000007</v>
       </c>
       <c r="AG42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>30.892510000000009</v>
       </c>
       <c r="AH42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>33.981761000000006</v>
       </c>
       <c r="AI42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>37.379937100000014</v>
       </c>
       <c r="AJ42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>41.117930810000018</v>
       </c>
       <c r="AK42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>45.22972389100002</v>
       </c>
       <c r="AL42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>49.752696280100025</v>
       </c>
       <c r="AM42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>54.727965908110036</v>
       </c>
       <c r="AN42" s="5">
-        <f t="shared" si="145"/>
+        <f t="shared" si="143"/>
         <v>60.200762498921044</v>
       </c>
     </row>
@@ -5681,488 +5711,488 @@
         <v>-3.1</v>
       </c>
       <c r="Y43" s="8">
-        <f t="shared" ref="Y43:AD43" si="146">Y39-Y42</f>
+        <f t="shared" ref="Y43:AD43" si="144">Y39-Y42</f>
         <v>13.700000000000003</v>
       </c>
       <c r="Z43" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>3.19999999999997</v>
       </c>
       <c r="AA43" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>43.400000000000048</v>
       </c>
       <c r="AB43" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>139.90000000000006</v>
       </c>
       <c r="AC43" s="8">
-        <f t="shared" si="146"/>
+        <f t="shared" si="144"/>
         <v>264.59999999999997</v>
       </c>
       <c r="AD43" s="8">
-        <f t="shared" si="146"/>
-        <v>268.10149999999987</v>
+        <f t="shared" si="144"/>
+        <v>260.36250000000013</v>
       </c>
       <c r="AE43" s="8">
-        <f t="shared" ref="AE43:AN43" si="147">AE39-AE42</f>
-        <v>354.58166550000004</v>
+        <f t="shared" ref="AE43:AN43" si="145">AE39-AE42</f>
+        <v>313.12616250000002</v>
       </c>
       <c r="AF43" s="8">
-        <f t="shared" si="147"/>
-        <v>475.66270324499988</v>
+        <f t="shared" si="145"/>
+        <v>408.40982374999999</v>
       </c>
       <c r="AG43" s="8">
-        <f t="shared" si="147"/>
-        <v>583.00252053824988</v>
+        <f t="shared" si="145"/>
+        <v>523.10429018749994</v>
       </c>
       <c r="AH43" s="8">
-        <f t="shared" si="147"/>
-        <v>673.56219381519725</v>
+        <f t="shared" si="145"/>
+        <v>616.03510445687493</v>
       </c>
       <c r="AI43" s="8">
-        <f t="shared" si="147"/>
-        <v>744.73453159406199</v>
+        <f t="shared" si="145"/>
+        <v>682.66725895989384</v>
       </c>
       <c r="AJ43" s="8">
-        <f t="shared" si="147"/>
-        <v>805.13202367216718</v>
+        <f t="shared" si="145"/>
+        <v>739.40758310199931</v>
       </c>
       <c r="AK43" s="8">
-        <f t="shared" si="147"/>
-        <v>859.45407349998754</v>
+        <f t="shared" si="145"/>
+        <v>790.24198561168987</v>
       </c>
       <c r="AL43" s="8">
-        <f t="shared" si="147"/>
-        <v>916.51036527520932</v>
+        <f t="shared" si="145"/>
+        <v>843.6426792402799</v>
       </c>
       <c r="AM43" s="8">
-        <f t="shared" si="147"/>
-        <v>976.42053973406269</v>
+        <f t="shared" si="145"/>
+        <v>899.7211404137538</v>
       </c>
       <c r="AN43" s="8">
-        <f t="shared" si="147"/>
-        <v>1039.3082236353544</v>
+        <f t="shared" si="145"/>
+        <v>958.59242907578971</v>
       </c>
       <c r="AO43" s="1">
         <f>AN43*(1+$AR$21)</f>
-        <v>1028.9151413990007</v>
+        <v>949.00650478503178</v>
       </c>
       <c r="AP43" s="1">
-        <f t="shared" ref="AP43:DA43" si="148">AO43*(1+$AR$21)</f>
-        <v>1018.6259899850107</v>
+        <f t="shared" ref="AP43:DA43" si="146">AO43*(1+$AR$21)</f>
+        <v>939.51643973718149</v>
       </c>
       <c r="AQ43" s="1">
-        <f t="shared" si="148"/>
-        <v>1008.4397300851606</v>
+        <f t="shared" si="146"/>
+        <v>930.1212753398097</v>
       </c>
       <c r="AR43" s="1">
-        <f t="shared" si="148"/>
-        <v>998.35533278430898</v>
+        <f t="shared" si="146"/>
+        <v>920.82006258641161</v>
       </c>
       <c r="AS43" s="1">
-        <f t="shared" si="148"/>
-        <v>988.3717794564659</v>
+        <f t="shared" si="146"/>
+        <v>911.61186196054746</v>
       </c>
       <c r="AT43" s="1">
-        <f t="shared" si="148"/>
-        <v>978.48806166190127</v>
+        <f t="shared" si="146"/>
+        <v>902.495743340942</v>
       </c>
       <c r="AU43" s="1">
-        <f t="shared" si="148"/>
-        <v>968.70318104528224</v>
+        <f t="shared" si="146"/>
+        <v>893.47078590753256</v>
       </c>
       <c r="AV43" s="1">
-        <f t="shared" si="148"/>
-        <v>959.01614923482941</v>
+        <f t="shared" si="146"/>
+        <v>884.53607804845717</v>
       </c>
       <c r="AW43" s="1">
-        <f t="shared" si="148"/>
-        <v>949.42598774248108</v>
+        <f t="shared" si="146"/>
+        <v>875.69071726797256</v>
       </c>
       <c r="AX43" s="1">
-        <f t="shared" si="148"/>
-        <v>939.93172786505625</v>
+        <f t="shared" si="146"/>
+        <v>866.93381009529287</v>
       </c>
       <c r="AY43" s="1">
-        <f t="shared" si="148"/>
-        <v>930.53241058640572</v>
+        <f t="shared" si="146"/>
+        <v>858.26447199433994</v>
       </c>
       <c r="AZ43" s="1">
-        <f t="shared" si="148"/>
-        <v>921.22708648054163</v>
+        <f t="shared" si="146"/>
+        <v>849.68182727439648</v>
       </c>
       <c r="BA43" s="1">
-        <f t="shared" si="148"/>
-        <v>912.01481561573621</v>
+        <f t="shared" si="146"/>
+        <v>841.18500900165247</v>
       </c>
       <c r="BB43" s="1">
-        <f t="shared" si="148"/>
-        <v>902.89466745957884</v>
+        <f t="shared" si="146"/>
+        <v>832.77315891163596</v>
       </c>
       <c r="BC43" s="1">
-        <f t="shared" si="148"/>
-        <v>893.86572078498307</v>
+        <f t="shared" si="146"/>
+        <v>824.44542732251955</v>
       </c>
       <c r="BD43" s="1">
-        <f t="shared" si="148"/>
-        <v>884.92706357713325</v>
+        <f t="shared" si="146"/>
+        <v>816.20097304929436</v>
       </c>
       <c r="BE43" s="1">
-        <f t="shared" si="148"/>
-        <v>876.07779294136196</v>
+        <f t="shared" si="146"/>
+        <v>808.03896331880139</v>
       </c>
       <c r="BF43" s="1">
-        <f t="shared" si="148"/>
-        <v>867.31701501194834</v>
+        <f t="shared" si="146"/>
+        <v>799.95857368561337</v>
       </c>
       <c r="BG43" s="1">
-        <f t="shared" si="148"/>
-        <v>858.64384486182882</v>
+        <f t="shared" si="146"/>
+        <v>791.95898794875723</v>
       </c>
       <c r="BH43" s="1">
-        <f t="shared" si="148"/>
-        <v>850.05740641321051</v>
+        <f t="shared" si="146"/>
+        <v>784.03939806926962</v>
       </c>
       <c r="BI43" s="1">
-        <f t="shared" si="148"/>
-        <v>841.55683234907838</v>
+        <f t="shared" si="146"/>
+        <v>776.19900408857688</v>
       </c>
       <c r="BJ43" s="1">
-        <f t="shared" si="148"/>
-        <v>833.14126402558759</v>
+        <f t="shared" si="146"/>
+        <v>768.43701404769115</v>
       </c>
       <c r="BK43" s="1">
-        <f t="shared" si="148"/>
-        <v>824.80985138533174</v>
+        <f t="shared" si="146"/>
+        <v>760.75264390721418</v>
       </c>
       <c r="BL43" s="1">
-        <f t="shared" si="148"/>
-        <v>816.56175287147846</v>
+        <f t="shared" si="146"/>
+        <v>753.14511746814208</v>
       </c>
       <c r="BM43" s="1">
-        <f t="shared" si="148"/>
-        <v>808.39613534276361</v>
+        <f t="shared" si="146"/>
+        <v>745.6136662934606</v>
       </c>
       <c r="BN43" s="1">
-        <f t="shared" si="148"/>
-        <v>800.31217398933597</v>
+        <f t="shared" si="146"/>
+        <v>738.15752963052603</v>
       </c>
       <c r="BO43" s="1">
-        <f t="shared" si="148"/>
-        <v>792.30905224944263</v>
+        <f t="shared" si="146"/>
+        <v>730.77595433422073</v>
       </c>
       <c r="BP43" s="1">
-        <f t="shared" si="148"/>
-        <v>784.38596172694815</v>
+        <f t="shared" si="146"/>
+        <v>723.46819479087856</v>
       </c>
       <c r="BQ43" s="1">
-        <f t="shared" si="148"/>
-        <v>776.54210210967869</v>
+        <f t="shared" si="146"/>
+        <v>716.23351284296973</v>
       </c>
       <c r="BR43" s="1">
-        <f t="shared" si="148"/>
-        <v>768.77668108858188</v>
+        <f t="shared" si="146"/>
+        <v>709.07117771454</v>
       </c>
       <c r="BS43" s="1">
-        <f t="shared" si="148"/>
-        <v>761.08891427769606</v>
+        <f t="shared" si="146"/>
+        <v>701.98046593739457</v>
       </c>
       <c r="BT43" s="1">
-        <f t="shared" si="148"/>
-        <v>753.47802513491911</v>
+        <f t="shared" si="146"/>
+        <v>694.96066127802067</v>
       </c>
       <c r="BU43" s="1">
-        <f t="shared" si="148"/>
-        <v>745.94324488356995</v>
+        <f t="shared" si="146"/>
+        <v>688.01105466524041</v>
       </c>
       <c r="BV43" s="1">
-        <f t="shared" si="148"/>
-        <v>738.4838124347342</v>
+        <f t="shared" si="146"/>
+        <v>681.13094411858799</v>
       </c>
       <c r="BW43" s="1">
-        <f t="shared" si="148"/>
-        <v>731.09897431038689</v>
+        <f t="shared" si="146"/>
+        <v>674.31963467740206</v>
       </c>
       <c r="BX43" s="1">
-        <f t="shared" si="148"/>
-        <v>723.78798456728305</v>
+        <f t="shared" si="146"/>
+        <v>667.57643833062809</v>
       </c>
       <c r="BY43" s="1">
-        <f t="shared" si="148"/>
-        <v>716.55010472161018</v>
+        <f t="shared" si="146"/>
+        <v>660.90067394732182</v>
       </c>
       <c r="BZ43" s="1">
-        <f t="shared" si="148"/>
-        <v>709.38460367439404</v>
+        <f t="shared" si="146"/>
+        <v>654.2916672078486</v>
       </c>
       <c r="CA43" s="1">
-        <f t="shared" si="148"/>
-        <v>702.29075763765013</v>
+        <f t="shared" si="146"/>
+        <v>647.74875053577011</v>
       </c>
       <c r="CB43" s="1">
-        <f t="shared" si="148"/>
-        <v>695.26785006127363</v>
+        <f t="shared" si="146"/>
+        <v>641.27126303041246</v>
       </c>
       <c r="CC43" s="1">
-        <f t="shared" si="148"/>
-        <v>688.31517156066093</v>
+        <f t="shared" si="146"/>
+        <v>634.85855040010836</v>
       </c>
       <c r="CD43" s="1">
-        <f t="shared" si="148"/>
-        <v>681.43201984505436</v>
+        <f t="shared" si="146"/>
+        <v>628.50996489610725</v>
       </c>
       <c r="CE43" s="1">
-        <f t="shared" si="148"/>
-        <v>674.6176996466038</v>
+        <f t="shared" si="146"/>
+        <v>622.22486524714623</v>
       </c>
       <c r="CF43" s="1">
-        <f t="shared" si="148"/>
-        <v>667.87152265013776</v>
+        <f t="shared" si="146"/>
+        <v>616.00261659467481</v>
       </c>
       <c r="CG43" s="1">
-        <f t="shared" si="148"/>
-        <v>661.1928074236364</v>
+        <f t="shared" si="146"/>
+        <v>609.84259042872804</v>
       </c>
       <c r="CH43" s="1">
-        <f t="shared" si="148"/>
-        <v>654.58087934939999</v>
+        <f t="shared" si="146"/>
+        <v>603.74416452444075</v>
       </c>
       <c r="CI43" s="1">
-        <f t="shared" si="148"/>
-        <v>648.03507055590603</v>
+        <f t="shared" si="146"/>
+        <v>597.70672287919638</v>
       </c>
       <c r="CJ43" s="1">
-        <f t="shared" si="148"/>
-        <v>641.55471985034694</v>
+        <f t="shared" si="146"/>
+        <v>591.72965565040442</v>
       </c>
       <c r="CK43" s="1">
-        <f t="shared" si="148"/>
-        <v>635.13917265184341</v>
+        <f t="shared" si="146"/>
+        <v>585.81235909390034</v>
       </c>
       <c r="CL43" s="1">
-        <f t="shared" si="148"/>
-        <v>628.78778092532502</v>
+        <f t="shared" si="146"/>
+        <v>579.9542355029613</v>
       </c>
       <c r="CM43" s="1">
-        <f t="shared" si="148"/>
-        <v>622.49990311607178</v>
+        <f t="shared" si="146"/>
+        <v>574.15469314793165</v>
       </c>
       <c r="CN43" s="1">
-        <f t="shared" si="148"/>
-        <v>616.2749040849111</v>
+        <f t="shared" si="146"/>
+        <v>568.41314621645233</v>
       </c>
       <c r="CO43" s="1">
-        <f t="shared" si="148"/>
-        <v>610.11215504406198</v>
+        <f t="shared" si="146"/>
+        <v>562.72901475428785</v>
       </c>
       <c r="CP43" s="1">
-        <f t="shared" si="148"/>
-        <v>604.01103349362131</v>
+        <f t="shared" si="146"/>
+        <v>557.10172460674494</v>
       </c>
       <c r="CQ43" s="1">
-        <f t="shared" si="148"/>
-        <v>597.97092315868508</v>
+        <f t="shared" si="146"/>
+        <v>551.53070736067752</v>
       </c>
       <c r="CR43" s="1">
-        <f t="shared" si="148"/>
-        <v>591.99121392709822</v>
+        <f t="shared" si="146"/>
+        <v>546.01540028707075</v>
       </c>
       <c r="CS43" s="1">
-        <f t="shared" si="148"/>
-        <v>586.07130178782722</v>
+        <f t="shared" si="146"/>
+        <v>540.55524628420005</v>
       </c>
       <c r="CT43" s="1">
-        <f t="shared" si="148"/>
-        <v>580.21058876994891</v>
+        <f t="shared" si="146"/>
+        <v>535.14969382135803</v>
       </c>
       <c r="CU43" s="1">
-        <f t="shared" si="148"/>
-        <v>574.40848288224947</v>
+        <f t="shared" si="146"/>
+        <v>529.79819688314444</v>
       </c>
       <c r="CV43" s="1">
-        <f t="shared" si="148"/>
-        <v>568.66439805342702</v>
+        <f t="shared" si="146"/>
+        <v>524.50021491431301</v>
       </c>
       <c r="CW43" s="1">
-        <f t="shared" si="148"/>
-        <v>562.97775407289271</v>
+        <f t="shared" si="146"/>
+        <v>519.25521276516986</v>
       </c>
       <c r="CX43" s="1">
-        <f t="shared" si="148"/>
-        <v>557.34797653216378</v>
+        <f t="shared" si="146"/>
+        <v>514.06266063751821</v>
       </c>
       <c r="CY43" s="1">
-        <f t="shared" si="148"/>
-        <v>551.77449676684216</v>
+        <f t="shared" si="146"/>
+        <v>508.92203403114303</v>
       </c>
       <c r="CZ43" s="1">
-        <f t="shared" si="148"/>
-        <v>546.25675179917368</v>
+        <f t="shared" si="146"/>
+        <v>503.83281369083159</v>
       </c>
       <c r="DA43" s="1">
-        <f t="shared" si="148"/>
-        <v>540.79418428118197</v>
+        <f t="shared" si="146"/>
+        <v>498.79448555392327</v>
       </c>
       <c r="DB43" s="1">
-        <f t="shared" ref="DB43:EF43" si="149">DA43*(1+$AR$21)</f>
-        <v>535.38624243837012</v>
+        <f t="shared" ref="DB43:EF43" si="147">DA43*(1+$AR$21)</f>
+        <v>493.80654069838403</v>
       </c>
       <c r="DC43" s="1">
-        <f t="shared" si="149"/>
-        <v>530.03238001398643</v>
+        <f t="shared" si="147"/>
+        <v>488.86847529140016</v>
       </c>
       <c r="DD43" s="1">
-        <f t="shared" si="149"/>
-        <v>524.73205621384659</v>
+        <f t="shared" si="147"/>
+        <v>483.97979053848616</v>
       </c>
       <c r="DE43" s="1">
-        <f t="shared" si="149"/>
-        <v>519.48473565170809</v>
+        <f t="shared" si="147"/>
+        <v>479.13999263310131</v>
       </c>
       <c r="DF43" s="1">
-        <f t="shared" si="149"/>
-        <v>514.28988829519096</v>
+        <f t="shared" si="147"/>
+        <v>474.34859270677032</v>
       </c>
       <c r="DG43" s="1">
-        <f t="shared" si="149"/>
-        <v>509.14698941223907</v>
+        <f t="shared" si="147"/>
+        <v>469.60510677970262</v>
       </c>
       <c r="DH43" s="1">
-        <f t="shared" si="149"/>
-        <v>504.05551951811668</v>
+        <f t="shared" si="147"/>
+        <v>464.90905571190558</v>
       </c>
       <c r="DI43" s="1">
-        <f t="shared" si="149"/>
-        <v>499.0149643229355</v>
+        <f t="shared" si="147"/>
+        <v>460.25996515478653</v>
       </c>
       <c r="DJ43" s="1">
-        <f t="shared" si="149"/>
-        <v>494.02481467970614</v>
+        <f t="shared" si="147"/>
+        <v>455.65736550323868</v>
       </c>
       <c r="DK43" s="1">
-        <f t="shared" si="149"/>
-        <v>489.08456653290909</v>
+        <f t="shared" si="147"/>
+        <v>451.10079184820631</v>
       </c>
       <c r="DL43" s="1">
-        <f t="shared" si="149"/>
-        <v>484.19372086758</v>
+        <f t="shared" si="147"/>
+        <v>446.58978392972426</v>
       </c>
       <c r="DM43" s="1">
-        <f t="shared" si="149"/>
-        <v>479.3517836589042</v>
+        <f t="shared" si="147"/>
+        <v>442.12388609042699</v>
       </c>
       <c r="DN43" s="1">
-        <f t="shared" si="149"/>
-        <v>474.55826582231515</v>
+        <f t="shared" si="147"/>
+        <v>437.70264722952271</v>
       </c>
       <c r="DO43" s="1">
-        <f t="shared" si="149"/>
-        <v>469.81268316409199</v>
+        <f t="shared" si="147"/>
+        <v>433.32562075722745</v>
       </c>
       <c r="DP43" s="1">
-        <f t="shared" si="149"/>
-        <v>465.11455633245106</v>
+        <f t="shared" si="147"/>
+        <v>428.99236454965518</v>
       </c>
       <c r="DQ43" s="1">
-        <f t="shared" si="149"/>
-        <v>460.46341076912654</v>
+        <f t="shared" si="147"/>
+        <v>424.70244090415861</v>
       </c>
       <c r="DR43" s="1">
-        <f t="shared" si="149"/>
-        <v>455.85877666143529</v>
+        <f t="shared" si="147"/>
+        <v>420.45541649511699</v>
       </c>
       <c r="DS43" s="1">
-        <f t="shared" si="149"/>
-        <v>451.30018889482091</v>
+        <f t="shared" si="147"/>
+        <v>416.25086233016583</v>
       </c>
       <c r="DT43" s="1">
-        <f t="shared" si="149"/>
-        <v>446.78718700587268</v>
+        <f t="shared" si="147"/>
+        <v>412.08835370686415</v>
       </c>
       <c r="DU43" s="1">
-        <f t="shared" si="149"/>
-        <v>442.31931513581395</v>
+        <f t="shared" si="147"/>
+        <v>407.96747016979549</v>
       </c>
       <c r="DV43" s="1">
-        <f t="shared" si="149"/>
-        <v>437.89612198445582</v>
+        <f t="shared" si="147"/>
+        <v>403.88779546809752</v>
       </c>
       <c r="DW43" s="1">
-        <f t="shared" si="149"/>
-        <v>433.51716076461128</v>
+        <f t="shared" si="147"/>
+        <v>399.84891751341655</v>
       </c>
       <c r="DX43" s="1">
-        <f t="shared" si="149"/>
-        <v>429.18198915696519</v>
+        <f t="shared" si="147"/>
+        <v>395.85042833828237</v>
       </c>
       <c r="DY43" s="1">
-        <f t="shared" si="149"/>
-        <v>424.89016926539551</v>
+        <f t="shared" si="147"/>
+        <v>391.89192405489956</v>
       </c>
       <c r="DZ43" s="1">
-        <f t="shared" si="149"/>
-        <v>420.64126757274158</v>
+        <f t="shared" si="147"/>
+        <v>387.97300481435059</v>
       </c>
       <c r="EA43" s="1">
-        <f t="shared" si="149"/>
-        <v>416.43485489701419</v>
+        <f t="shared" si="147"/>
+        <v>384.09327476620706</v>
       </c>
       <c r="EB43" s="1">
-        <f t="shared" si="149"/>
-        <v>412.27050634804402</v>
+        <f t="shared" si="147"/>
+        <v>380.25234201854499</v>
       </c>
       <c r="EC43" s="1">
-        <f t="shared" si="149"/>
-        <v>408.14780128456357</v>
+        <f t="shared" si="147"/>
+        <v>376.44981859835951</v>
       </c>
       <c r="ED43" s="1">
-        <f t="shared" si="149"/>
-        <v>404.06632327171792</v>
+        <f t="shared" si="147"/>
+        <v>372.68532041237592</v>
       </c>
       <c r="EE43" s="1">
-        <f t="shared" si="149"/>
-        <v>400.02566003900074</v>
+        <f t="shared" si="147"/>
+        <v>368.95846720825216</v>
       </c>
       <c r="EF43" s="1">
-        <f t="shared" si="149"/>
-        <v>396.02540343861074</v>
+        <f t="shared" si="147"/>
+        <v>365.26888253616966</v>
       </c>
     </row>
     <row r="46" spans="2:136" x14ac:dyDescent="0.3">
       <c r="AR46" s="5">
         <f>NPV(AR22,AD43:EF43)</f>
-        <v>9478.703973408552</v>
+        <v>8697.2743756524105</v>
       </c>
     </row>
     <row r="47" spans="2:136" x14ac:dyDescent="0.3">
       <c r="AR47" s="5">
         <f>Main!D8</f>
-        <v>1097.9000000000001</v>
+        <v>1121.4000000000001</v>
       </c>
     </row>
     <row r="48" spans="2:136" x14ac:dyDescent="0.3">
       <c r="AR48" s="5">
         <f>AR46+AR47</f>
-        <v>10576.603973408552</v>
+        <v>9818.6743756524102</v>
       </c>
     </row>
     <row r="49" spans="44:44" x14ac:dyDescent="0.3">
       <c r="AR49" s="4">
         <f>AR48/AN16</f>
-        <v>230.93021776001206</v>
+        <v>212.98642897293732</v>
       </c>
     </row>
     <row r="50" spans="44:44" x14ac:dyDescent="0.3">
       <c r="AR50" s="4">
         <f>Main!D3</f>
-        <v>278.74</v>
+        <v>195.41</v>
       </c>
     </row>
     <row r="51" spans="44:44" x14ac:dyDescent="0.3">
       <c r="AR51" s="10">
         <f>AR49/AR50-1</f>
-        <v>-0.17152106708756532</v>
+        <v>8.9946415091025633E-2</v>
       </c>
     </row>
   </sheetData>

--- a/Financial Analysis/DUOL.xlsx
+++ b/Financial Analysis/DUOL.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1FEDEF4-BBCB-4739-B675-9C858EB3253C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2679C305-67B9-4B29-9487-713D67189E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9EA5A098-45C5-472E-8765-EE9A7145AF0E}"/>
   </bookViews>
@@ -314,7 +314,7 @@
     <t>Consensus</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Slightly undervalued</t>
   </si>
 </sst>
 </file>
@@ -851,14 +851,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>195.41</v>
+        <v>120.6</v>
       </c>
       <c r="E3" s="3">
-        <v>45967</v>
+        <v>46057</v>
       </c>
       <c r="F3" s="3">
         <f ca="1">TODAY()</f>
-        <v>45967</v>
+        <v>46057</v>
       </c>
       <c r="G3" s="3">
         <v>46079</v>
@@ -882,7 +882,7 @@
       </c>
       <c r="D5" s="5">
         <f>D3*D4</f>
-        <v>9008.4009999999998</v>
+        <v>5559.66</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -923,7 +923,7 @@
       </c>
       <c r="D9" s="5">
         <f>D5-D8</f>
-        <v>7887.0010000000002</v>
+        <v>4438.26</v>
       </c>
     </row>
   </sheetData>
@@ -940,7 +940,7 @@
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="8.88671875" customWidth="1"/>
     <col min="43" max="43" width="12" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:139" x14ac:dyDescent="0.3">
@@ -4145,7 +4145,7 @@
         <v>68</v>
       </c>
       <c r="AR22" s="9">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="23" spans="2:44" x14ac:dyDescent="0.3">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AR23" s="5">
         <f>NPV(AR22,AD15:EI15)</f>
-        <v>6924.3696840620387</v>
+        <v>6032.1256089009439</v>
       </c>
     </row>
     <row r="24" spans="2:44" x14ac:dyDescent="0.3">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="AR25" s="5">
         <f>AR23+AR24</f>
-        <v>8045.7696840620392</v>
+        <v>7153.5256089009436</v>
       </c>
     </row>
     <row r="26" spans="2:44" x14ac:dyDescent="0.3">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AR26" s="4">
         <f>AR25/AN16</f>
-        <v>174.5286265523219</v>
+        <v>155.17409129936971</v>
       </c>
     </row>
     <row r="27" spans="2:44" x14ac:dyDescent="0.3">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="AR27" s="4">
         <f>Main!D3</f>
-        <v>195.41</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="28" spans="2:44" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="AR28" s="10">
         <f>AR26/AR27-1</f>
-        <v>-0.1068592878955944</v>
+        <v>0.28668400745746037</v>
       </c>
     </row>
     <row r="29" spans="2:44" x14ac:dyDescent="0.3">
@@ -6162,7 +6162,7 @@
     <row r="46" spans="2:136" x14ac:dyDescent="0.3">
       <c r="AR46" s="5">
         <f>NPV(AR22,AD43:EF43)</f>
-        <v>8697.2743756524105</v>
+        <v>7614.2027925018438</v>
       </c>
     </row>
     <row r="47" spans="2:136" x14ac:dyDescent="0.3">
@@ -6174,25 +6174,25 @@
     <row r="48" spans="2:136" x14ac:dyDescent="0.3">
       <c r="AR48" s="5">
         <f>AR46+AR47</f>
-        <v>9818.6743756524102</v>
+        <v>8735.6027925018443</v>
       </c>
     </row>
     <row r="49" spans="44:44" x14ac:dyDescent="0.3">
       <c r="AR49" s="4">
         <f>AR48/AN16</f>
-        <v>212.98642897293732</v>
+        <v>189.49246838398793</v>
       </c>
     </row>
     <row r="50" spans="44:44" x14ac:dyDescent="0.3">
       <c r="AR50" s="4">
         <f>Main!D3</f>
-        <v>195.41</v>
+        <v>120.6</v>
       </c>
     </row>
     <row r="51" spans="44:44" x14ac:dyDescent="0.3">
       <c r="AR51" s="10">
         <f>AR49/AR50-1</f>
-        <v>8.9946415091025633E-2</v>
+        <v>0.57124766487552181</v>
       </c>
     </row>
   </sheetData>
